--- a/BA_Financial_Model_FY2021-FY2030E_Statement_v1.0.xlsx
+++ b/BA_Financial_Model_FY2021-FY2030E_Statement_v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205FFFB6-6124-4225-BC64-76A79A613E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5034C3-F7D2-4E92-9F4A-CA7C03182DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{63A9B8CA-83BF-48D9-A8B6-530B504F47C6}"/>
   </bookViews>
@@ -70,6 +70,8 @@
     <author>tc={735ECB3F-6B00-471D-B528-CF78FA9D8DCB}</author>
     <author>tc={723A0937-6AEF-49F9-A01F-764A700BA8DF}</author>
     <author>tc={E020734A-44B8-41B1-9F60-59BA644A2BE0}</author>
+    <author>tc={4444B2F3-5D63-47A9-821B-BE774CC0C6CD}</author>
+    <author>tc={31FA1DCD-E8AF-4359-80DF-460D0C1B3788}</author>
     <author>tc={7EEE51B2-23C8-4486-A6A9-82B3A58CF94D}</author>
     <author>tc={BF7762D6-2D19-4E5A-A42F-48F1758CDBF9}</author>
     <author>tc={BD0AADAC-A367-4E56-B134-8D85E5D1F39A}</author>
@@ -81,6 +83,7 @@
     <author>tc={2A6522A2-ECFE-452E-9069-22BB49335B60}</author>
     <author>tc={73E334A0-593A-41CB-8659-C7F0D149AD28}</author>
     <author>tc={2C5DD1BA-6455-422A-8A06-F13DA0A1A21E}</author>
+    <author>tc={38546E84-2507-4C66-843D-B4E8B55CE5FC}</author>
     <author>tc={781018CE-9A74-4BD7-B24A-7BBD80AB89E7}</author>
     <author>tc={E3887C0E-50E1-411C-B626-EBECC05579F8}</author>
     <author>tc={42B21807-10EE-4681-9B99-E76C8B4F8F19}</author>
@@ -104,9 +107,43 @@
     <author>tc={31BB17E1-73EB-438A-A0DB-D6025F734539}</author>
     <author>tc={6B2DD525-3FDF-4831-9A1B-E82B4EACA719}</author>
     <author>tc={949B10D3-3C46-4F0B-BC2A-F0EB9AC0FE1F}</author>
+    <author>tc={48544A9C-5A13-48D1-917C-3108BF63C7D6}</author>
+    <author>tc={5A51DCBB-5374-41B9-A10B-D554B01E1BF6}</author>
+    <author>tc={E50A0D2D-3BE6-4CD1-9F5F-29554D1EAC8F}</author>
     <author>tc={DF0D4C79-7457-440F-B77D-C897944542A1}</author>
+    <author>tc={68DB4377-F52A-4AAF-83A8-BD591DFD5B88}</author>
+    <author>tc={BFF3F063-7346-4FA0-B987-FBA065DF5BF0}</author>
+    <author>tc={0006161D-3BC5-4E50-B74E-B622B762275E}</author>
+    <author>tc={F78C6349-BEDA-4712-A897-1FEB6ADCE4E6}</author>
+    <author>tc={BF5E9D82-25FE-470A-8E1E-5BE11EEA9DB7}</author>
+    <author>tc={812CA68D-79BF-4E4F-81F9-2C4068742389}</author>
+    <author>tc={809AE375-C473-4387-B29D-B0C30E437B93}</author>
+    <author>tc={9D7F316F-17BF-4FB3-B0FE-FC87EC6234D0}</author>
+    <author>tc={CEC400AD-C561-4A30-9BB2-CA4E9DB69447}</author>
+    <author>tc={4A83F404-C9A2-46C7-9506-E1EF1742A4DE}</author>
+    <author>tc={48A8B806-0B54-4F16-8A9B-5449EA0673F3}</author>
+    <author>tc={7FFEBBFF-5D9C-4BFD-9657-AA07CCCF1643}</author>
+    <author>tc={BC23432E-35D7-4C91-BB36-3B8971C0F0EF}</author>
+    <author>tc={C43B1633-B4E0-4CF6-9023-271AD363286E}</author>
     <author>tc={3406BCD8-C23B-47A2-8911-97DD0FF0B2D2}</author>
     <author>tc={6B97D321-1CD9-43E7-8CB5-8D4B80105B9D}</author>
+    <author>tc={4D3C0DCE-13AE-4FE3-9352-785F2D5EEE07}</author>
+    <author>tc={6BCFBAF5-47C0-476F-8B84-2B2FCEB0D212}</author>
+    <author>tc={C0D67968-DD41-4C7C-A6EC-F945E41037B8}</author>
+    <author>tc={8E6376C5-2961-4711-B206-F04555A70644}</author>
+    <author>tc={D4DAA8F8-ADD5-4E4C-9817-F0478F5E63A3}</author>
+    <author>tc={4700DE3E-E3F0-42B6-B9F2-C0D6D39111C3}</author>
+    <author>tc={76663011-AFEF-4E06-A983-640D69F7354B}</author>
+    <author>tc={E9384446-E2E6-4EAA-912C-AA254CC96811}</author>
+    <author>tc={B61385CD-4D45-43DD-A9B8-1F9A74DDBE7A}</author>
+    <author>tc={2688BE2C-FA58-404B-A32E-6069952950F1}</author>
+    <author>tc={7E2FEC11-F235-4343-9ED2-AC7B15839631}</author>
+    <author>tc={5C64ACA4-E29F-463F-B779-E9272719307F}</author>
+    <author>tc={9A9E8B3D-B775-48CF-9620-F2C10C0EC303}</author>
+    <author>tc={68D538B7-3B2D-4332-865D-5AD5BC490526}</author>
+    <author>tc={84FA0DD2-4274-4155-A7D5-B607DD46069A}</author>
+    <author>tc={0CF63F11-B143-4E7B-A7B4-DCEEDCB5A0BF}</author>
+    <author>tc={6D078522-323F-412D-9378-145142E98D7D}</author>
   </authors>
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0" xr:uid="{055D5F0C-0A02-43EA-950D-294DE5635375}">
@@ -314,15 +351,31 @@
     Using 3 Year Average</t>
       </text>
     </comment>
-    <comment ref="H44" authorId="25" shapeId="0" xr:uid="{7EEE51B2-23C8-4486-A6A9-82B3A58CF94D}">
+    <comment ref="H41" authorId="25" shapeId="0" xr:uid="{4444B2F3-5D63-47A9-821B-BE774CC0C6CD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
+    Using 3 Year Average</t>
+      </text>
+    </comment>
+    <comment ref="H42" authorId="26" shapeId="0" xr:uid="{31FA1DCD-E8AF-4359-80DF-460D0C1B3788}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    =Interest % of Debt * Total Debt</t>
+      </text>
+    </comment>
+    <comment ref="H44" authorId="27" shapeId="0" xr:uid="{7EEE51B2-23C8-4486-A6A9-82B3A58CF94D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     =EBT * Tax Rate</t>
       </text>
     </comment>
-    <comment ref="H48" authorId="26" shapeId="0" xr:uid="{BF7762D6-2D19-4E5A-A42F-48F1758CDBF9}">
+    <comment ref="H48" authorId="28" shapeId="0" xr:uid="{BF7762D6-2D19-4E5A-A42F-48F1758CDBF9}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -330,7 +383,7 @@
     "Fixed annual dividend of $345M based on Boeing's 6.00% Series A Mandatory Convertible Preferred Stock issued October 2024. Calculated as $5,750M liquidation preference × 6.00% dividend rate. Mandatory conversion to common shares on or about October 15, 2027. 2027E reflects approximately half year dividend (~$173M) and zero thereafter." </t>
       </text>
     </comment>
-    <comment ref="I48" authorId="27" shapeId="0" xr:uid="{BD0AADAC-A367-4E56-B134-8D85E5D1F39A}">
+    <comment ref="I48" authorId="29" shapeId="0" xr:uid="{BD0AADAC-A367-4E56-B134-8D85E5D1F39A}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -338,7 +391,7 @@
     "Fixed annual dividend of $345M based on Boeing's 6.00% Series A Mandatory Convertible Preferred Stock issued October 2024. Calculated as $5,750M liquidation preference × 6.00% dividend rate. Mandatory conversion to common shares on or about October 15, 2027. 2027E reflects approximately half year dividend (~$173M) and zero thereafter." </t>
       </text>
     </comment>
-    <comment ref="B50" authorId="28" shapeId="0" xr:uid="{8408FF94-C482-4CF7-B3B6-E64B1A7C83FA}">
+    <comment ref="B50" authorId="30" shapeId="0" xr:uid="{8408FF94-C482-4CF7-B3B6-E64B1A7C83FA}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -346,7 +399,7 @@
     Disclosed as basic weighted average common shares outstanding in the EPS footnote of the 10-K </t>
       </text>
     </comment>
-    <comment ref="B52" authorId="29" shapeId="0" xr:uid="{D28620DE-7806-4031-A94C-5A70B9745900}">
+    <comment ref="B52" authorId="31" shapeId="0" xr:uid="{D28620DE-7806-4031-A94C-5A70B9745900}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -355,7 +408,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="H57" authorId="30" shapeId="0" xr:uid="{A220A4AC-D09C-42CC-AAFF-A3D7CABEAF78}">
+    <comment ref="H57" authorId="32" shapeId="0" xr:uid="{A220A4AC-D09C-42CC-AAFF-A3D7CABEAF78}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -363,7 +416,7 @@
     Holding flat as I have no specific assumptions</t>
       </text>
     </comment>
-    <comment ref="H58" authorId="31" shapeId="0" xr:uid="{55835481-3D66-47BC-A0B4-92FC7117D04A}">
+    <comment ref="H58" authorId="33" shapeId="0" xr:uid="{55835481-3D66-47BC-A0B4-92FC7117D04A}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -372,7 +425,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="H59" authorId="32" shapeId="0" xr:uid="{F517D032-B01D-4DF2-B2E1-1155B2E900C9}">
+    <comment ref="H59" authorId="34" shapeId="0" xr:uid="{F517D032-B01D-4DF2-B2E1-1155B2E900C9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -380,7 +433,7 @@
     Using 5 Year Average</t>
       </text>
     </comment>
-    <comment ref="H61" authorId="33" shapeId="0" xr:uid="{2A6522A2-ECFE-452E-9069-22BB49335B60}">
+    <comment ref="H61" authorId="35" shapeId="0" xr:uid="{2A6522A2-ECFE-452E-9069-22BB49335B60}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -389,7 +442,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="H62" authorId="34" shapeId="0" xr:uid="{73E334A0-593A-41CB-8659-C7F0D149AD28}">
+    <comment ref="H62" authorId="36" shapeId="0" xr:uid="{73E334A0-593A-41CB-8659-C7F0D149AD28}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -397,7 +450,7 @@
     =2025 Other Current Assets * (1 + Revenue Growth Rate)</t>
       </text>
     </comment>
-    <comment ref="H64" authorId="35" shapeId="0" xr:uid="{2C5DD1BA-6455-422A-8A06-F13DA0A1A21E}">
+    <comment ref="H64" authorId="37" shapeId="0" xr:uid="{2C5DD1BA-6455-422A-8A06-F13DA0A1A21E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -405,7 +458,15 @@
     Declining portfolio; Boeing exiting customer financing. Linear run-off assumed.</t>
       </text>
     </comment>
-    <comment ref="H66" authorId="36" shapeId="0" xr:uid="{781018CE-9A74-4BD7-B24A-7BBD80AB89E7}">
+    <comment ref="H65" authorId="38" shapeId="0" xr:uid="{38546E84-2507-4C66-843D-B4E8B55CE5FC}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Prior Year PP&amp;E + CapEx - D&amp;A </t>
+      </text>
+    </comment>
+    <comment ref="H66" authorId="39" shapeId="0" xr:uid="{781018CE-9A74-4BD7-B24A-7BBD80AB89E7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -413,7 +474,7 @@
     Holding flat, no acquisitions acquired</t>
       </text>
     </comment>
-    <comment ref="H67" authorId="37" shapeId="0" xr:uid="{E3887C0E-50E1-411C-B626-EBECC05579F8}">
+    <comment ref="H67" authorId="40" shapeId="0" xr:uid="{E3887C0E-50E1-411C-B626-EBECC05579F8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -421,7 +482,7 @@
     Using a 5 Year Average (No amortization portion of D&amp;A)</t>
       </text>
     </comment>
-    <comment ref="H68" authorId="38" shapeId="0" xr:uid="{42B21807-10EE-4681-9B99-E76C8B4F8F19}">
+    <comment ref="H68" authorId="41" shapeId="0" xr:uid="{42B21807-10EE-4681-9B99-E76C8B4F8F19}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -429,7 +490,7 @@
     Holding Flat</t>
       </text>
     </comment>
-    <comment ref="H69" authorId="39" shapeId="0" xr:uid="{7ECBA987-631A-452A-B005-8DEB05A0D266}">
+    <comment ref="H69" authorId="42" shapeId="0" xr:uid="{7ECBA987-631A-452A-B005-8DEB05A0D266}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -437,7 +498,7 @@
     Holding Flat</t>
       </text>
     </comment>
-    <comment ref="H70" authorId="40" shapeId="0" xr:uid="{DBC35067-876F-4FAD-ADB1-8027CB5EB694}">
+    <comment ref="H70" authorId="43" shapeId="0" xr:uid="{DBC35067-876F-4FAD-ADB1-8027CB5EB694}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -447,7 +508,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="H72" authorId="41" shapeId="0" xr:uid="{814AF812-3628-4A3F-BBD1-C79B9FB72DB1}">
+    <comment ref="H72" authorId="44" shapeId="0" xr:uid="{814AF812-3628-4A3F-BBD1-C79B9FB72DB1}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -456,7 +517,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="H73" authorId="42" shapeId="0" xr:uid="{68022D32-F1F3-4230-804F-E42ACC6E65BC}">
+    <comment ref="H73" authorId="45" shapeId="0" xr:uid="{68022D32-F1F3-4230-804F-E42ACC6E65BC}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -465,7 +526,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="H74" authorId="43" shapeId="0" xr:uid="{0F4657DB-4F55-4126-9AA9-309AE70433C1}">
+    <comment ref="H74" authorId="46" shapeId="0" xr:uid="{0F4657DB-4F55-4126-9AA9-309AE70433C1}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -474,7 +535,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="H75" authorId="44" shapeId="0" xr:uid="{6F50CB29-681B-4273-A7E2-EC93B37B267D}">
+    <comment ref="H75" authorId="47" shapeId="0" xr:uid="{6F50CB29-681B-4273-A7E2-EC93B37B267D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -482,7 +543,7 @@
     Holding flat, no debt schedule…debt is volatile hence not using averages</t>
       </text>
     </comment>
-    <comment ref="H77" authorId="45" shapeId="0" xr:uid="{C8728A52-4B4C-4EE8-A0E5-D0AABDE46C6A}">
+    <comment ref="H77" authorId="48" shapeId="0" xr:uid="{C8728A52-4B4C-4EE8-A0E5-D0AABDE46C6A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -490,7 +551,7 @@
     Using 5 Year Average</t>
       </text>
     </comment>
-    <comment ref="H78" authorId="46" shapeId="0" xr:uid="{32311E65-3CCC-4F0B-8E2B-49A29C7C4C14}">
+    <comment ref="H78" authorId="49" shapeId="0" xr:uid="{32311E65-3CCC-4F0B-8E2B-49A29C7C4C14}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -498,7 +559,7 @@
     2026E Accrued Retiree Healthcare: Declining ~$190-200M/yr. Benefit obligation reducing through plan modifications and demographics. Trend: $3,528M (2021) → $2,091M (2025) → continuing decline.</t>
       </text>
     </comment>
-    <comment ref="H79" authorId="47" shapeId="0" xr:uid="{2CC4C517-5135-4741-BDCB-AACD715CD406}">
+    <comment ref="H79" authorId="50" shapeId="0" xr:uid="{2CC4C517-5135-4741-BDCB-AACD715CD406}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -506,7 +567,7 @@
     2026E Pension Liabilities: Declining ~$300M/yr. Continued de-risking of pension portfolio; annual cash contributions ~$300-400M. Trend: $9,104M (2021) → $4,287M (2025).</t>
       </text>
     </comment>
-    <comment ref="H80" authorId="48" shapeId="0" xr:uid="{ED508D21-4D41-4D7E-A2C6-47EBB330BC7F}">
+    <comment ref="H80" authorId="51" shapeId="0" xr:uid="{ED508D21-4D41-4D7E-A2C6-47EBB330BC7F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -514,7 +575,7 @@
     Holding Flat</t>
       </text>
     </comment>
-    <comment ref="H81" authorId="49" shapeId="0" xr:uid="{0EF33BA7-EA60-4068-A91B-07BCA37ADD16}">
+    <comment ref="H81" authorId="52" shapeId="0" xr:uid="{0EF33BA7-EA60-4068-A91B-07BCA37ADD16}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -522,7 +583,7 @@
     Holding Flat</t>
       </text>
     </comment>
-    <comment ref="H83" authorId="50" shapeId="0" xr:uid="{BF4AE64D-C9B3-4377-AA66-B017FC2C584D}">
+    <comment ref="H83" authorId="53" shapeId="0" xr:uid="{BF4AE64D-C9B3-4377-AA66-B017FC2C584D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -530,7 +591,7 @@
     Holding Flat</t>
       </text>
     </comment>
-    <comment ref="H84" authorId="51" shapeId="0" xr:uid="{411E2319-1AA4-4B9C-B4FE-BDB461FBF768}">
+    <comment ref="H84" authorId="54" shapeId="0" xr:uid="{411E2319-1AA4-4B9C-B4FE-BDB461FBF768}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -538,7 +599,7 @@
     =2025 Additional Paid-in Capital + Shared-Based Plans Expense</t>
       </text>
     </comment>
-    <comment ref="H85" authorId="52" shapeId="0" xr:uid="{83C8CD51-E80A-4656-9959-554450CFFE03}">
+    <comment ref="H85" authorId="55" shapeId="0" xr:uid="{83C8CD51-E80A-4656-9959-554450CFFE03}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -546,7 +607,7 @@
     =Treasury Stock + Treasury Shares Issued for 401(K) Contribution</t>
       </text>
     </comment>
-    <comment ref="H86" authorId="53" shapeId="0" xr:uid="{F5319C8C-F8F3-4693-ABB0-C77AE715A152}">
+    <comment ref="H86" authorId="56" shapeId="0" xr:uid="{F5319C8C-F8F3-4693-ABB0-C77AE715A152}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -554,7 +615,7 @@
     =Retained Earnings + Net Income</t>
       </text>
     </comment>
-    <comment ref="H87" authorId="54" shapeId="0" xr:uid="{FCB91F4A-21DD-4545-A98C-5E64EEF23ECD}">
+    <comment ref="H87" authorId="57" shapeId="0" xr:uid="{FCB91F4A-21DD-4545-A98C-5E64EEF23ECD}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -563,7 +624,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="H89" authorId="55" shapeId="0" xr:uid="{F849684E-55F3-45B7-A694-57CDAAB97F7C}">
+    <comment ref="H89" authorId="58" shapeId="0" xr:uid="{F849684E-55F3-45B7-A694-57CDAAB97F7C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -571,7 +632,7 @@
     2026E Mandatory Convertible Preferred: $6M. Converts to common equity in 2027</t>
       </text>
     </comment>
-    <comment ref="H97" authorId="56" shapeId="0" xr:uid="{31BB17E1-73EB-438A-A0DB-D6025F734539}">
+    <comment ref="H97" authorId="59" shapeId="0" xr:uid="{31BB17E1-73EB-438A-A0DB-D6025F734539}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -580,7 +641,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="H98" authorId="57" shapeId="0" xr:uid="{6B2DD525-3FDF-4831-9A1B-E82B4EACA719}">
+    <comment ref="H98" authorId="60" shapeId="0" xr:uid="{6B2DD525-3FDF-4831-9A1B-E82B4EACA719}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -588,36 +649,318 @@
     Using 5 Year Average</t>
       </text>
     </comment>
-    <comment ref="H99" authorId="58" shapeId="0" xr:uid="{949B10D3-3C46-4F0B-BC2A-F0EB9AC0FE1F}">
+    <comment ref="H99" authorId="61" shapeId="0" xr:uid="{949B10D3-3C46-4F0B-BC2A-F0EB9AC0FE1F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
+    =D%A % of Revenue * Revenue</t>
+      </text>
+    </comment>
+    <comment ref="H100" authorId="62" shapeId="0" xr:uid="{48544A9C-5A13-48D1-917C-3108BF63C7D6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Unpredictable</t>
+      </text>
+    </comment>
+    <comment ref="H101" authorId="63" shapeId="0" xr:uid="{5A51DCBB-5374-41B9-A10B-D554B01E1BF6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Holding as 0</t>
+      </text>
+    </comment>
+    <comment ref="H102" authorId="64" shapeId="0" xr:uid="{E50A0D2D-3BE6-4CD1-9F5F-29554D1EAC8F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    One time item</t>
+      </text>
+    </comment>
+    <comment ref="B103" authorId="65" shapeId="0" xr:uid="{DF0D4C79-7457-440F-B77D-C897944542A1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    777X and 787 Reach Forward Losses in 2021</t>
+      </text>
+    </comment>
+    <comment ref="H103" authorId="66" shapeId="0" xr:uid="{68DB4377-F52A-4AAF-83A8-BD591DFD5B88}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    0 as this is programme specific</t>
+      </text>
+    </comment>
+    <comment ref="H104" authorId="67" shapeId="0" xr:uid="{BFF3F063-7346-4FA0-B987-FBA065DF5BF0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Using 3 Year Average</t>
+      </text>
+    </comment>
+    <comment ref="H106" authorId="68" shapeId="0" xr:uid="{0006161D-3BC5-4E50-B74E-B622B762275E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Minus the change in AR
+(If there is an increase in assets, results in negative cash flow)</t>
+      </text>
+    </comment>
+    <comment ref="H107" authorId="69" shapeId="0" xr:uid="{F78C6349-BEDA-4712-A897-1FEB6ADCE4E6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Minus change in Unbilled Receivables
+(If there is an increase in assets, results in negative cash flow)</t>
+      </text>
+    </comment>
+    <comment ref="H108" authorId="70" shapeId="0" xr:uid="{BF5E9D82-25FE-470A-8E1E-5BE11EEA9DB7}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    =2026 Advances &amp; Progress Billings (BS) - 2025 Advances &amp; Progress Billings 
+(If there is an increase in liabilities, results in positive cash flow)
+</t>
+      </text>
+    </comment>
+    <comment ref="H109" authorId="71" shapeId="0" xr:uid="{812CA68D-79BF-4E4F-81F9-2C4068742389}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    = 2025 Inventory - 2026 Inventory 
+Inventory went up, negative in CFS</t>
+      </text>
+    </comment>
+    <comment ref="H110" authorId="72" shapeId="0" xr:uid="{809AE375-C473-4387-B29D-B0C30E437B93}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    = 2025 Other CA (BS) − 2026 Other CA (BS)
+(Increase in Assets result in negative cash flow) </t>
+      </text>
+    </comment>
+    <comment ref="H111" authorId="73" shapeId="0" xr:uid="{9D7F316F-17BF-4FB3-B0FE-FC87EC6234D0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    = 2026 AP (BS) − 2025 AP (BS) 
+(Increase in liabilities means positive cash flow)</t>
+      </text>
+    </comment>
+    <comment ref="H112" authorId="74" shapeId="0" xr:uid="{CEC400AD-C561-4A30-9BB2-CA4E9DB69447}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    = 2026 Liabilities - 2025 Liabilities
+(Increase in liabilities means positive cash flow)</t>
+      </text>
+    </comment>
+    <comment ref="H113" authorId="75" shapeId="0" xr:uid="{4A83F404-C9A2-46C7-9506-E1EF1742A4DE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    0 as forecast is held flat</t>
+      </text>
+    </comment>
+    <comment ref="H114" authorId="76" shapeId="0" xr:uid="{48A8B806-0B54-4F16-8A9B-5449EA0673F3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    0 as forecast is held flat</t>
+      </text>
+    </comment>
+    <comment ref="H115" authorId="77" shapeId="0" xr:uid="{7FFEBBFF-5D9C-4BFD-9657-AA07CCCF1643}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Using 3 Year Average</t>
+      </text>
+    </comment>
+    <comment ref="H116" authorId="78" shapeId="0" xr:uid="{BC23432E-35D7-4C91-BB36-3B8971C0F0EF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    = (2026 BS balance - 2025 BS balance)
+(A decrease in assets means positive cash flow)</t>
+      </text>
+    </comment>
+    <comment ref="H117" authorId="79" shapeId="0" xr:uid="{C43B1633-B4E0-4CF6-9023-271AD363286E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Using 3 Year Average</t>
+      </text>
+    </comment>
+    <comment ref="B119" authorId="80" shapeId="0" xr:uid="{3406BCD8-C23B-47A2-8911-97DD0FF0B2D2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Payments to Acquire Property, Plant and Equipment</t>
+      </text>
+    </comment>
+    <comment ref="H119" authorId="81" shapeId="0" xr:uid="{6B97D321-1CD9-43E7-8CB5-8D4B80105B9D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Using a 5 Year Average</t>
       </text>
     </comment>
-    <comment ref="B103" authorId="59" shapeId="0" xr:uid="{DF0D4C79-7457-440F-B77D-C897944542A1}">
+    <comment ref="H120" authorId="82" shapeId="0" xr:uid="{4D3C0DCE-13AE-4FE3-9352-785F2D5EEE07}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    777X and 787 Reach Forward Losses in 2021</t>
-      </text>
-    </comment>
-    <comment ref="B119" authorId="60" shapeId="0" xr:uid="{3406BCD8-C23B-47A2-8911-97DD0FF0B2D2}">
+    Using 5 Year Average</t>
+      </text>
+    </comment>
+    <comment ref="H121" authorId="83" shapeId="0" xr:uid="{6BCFBAF5-47C0-476F-8B84-2B2FCEB0D212}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Payments to Acquire Property, Plant and Equipment</t>
-      </text>
-    </comment>
-    <comment ref="H119" authorId="61" shapeId="0" xr:uid="{6B97D321-1CD9-43E7-8CB5-8D4B80105B9D}">
+    Holding Flat at Zero</t>
+      </text>
+    </comment>
+    <comment ref="H122" authorId="84" shapeId="0" xr:uid="{C0D67968-DD41-4C7C-A6EC-F945E41037B8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Using a 5 Year Average</t>
+    Holding Flat at Zero</t>
+      </text>
+    </comment>
+    <comment ref="H123" authorId="85" shapeId="0" xr:uid="{8E6376C5-2961-4711-B206-F04555A70644}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Using 5 Year Average</t>
+      </text>
+    </comment>
+    <comment ref="H124" authorId="86" shapeId="0" xr:uid="{D4DAA8F8-ADD5-4E4C-9817-F0478F5E63A3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Using 5 Year Average</t>
+      </text>
+    </comment>
+    <comment ref="H125" authorId="87" shapeId="0" xr:uid="{4700DE3E-E3F0-42B6-B9F2-C0D6D39111C3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Using 3 Year Average</t>
+      </text>
+    </comment>
+    <comment ref="H126" authorId="88" shapeId="0" xr:uid="{76663011-AFEF-4E06-A983-640D69F7354B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Holding Flat at Zero</t>
+      </text>
+    </comment>
+    <comment ref="H127" authorId="89" shapeId="0" xr:uid="{E9384446-E2E6-4EAA-912C-AA254CC96811}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Holding Flat at Zero</t>
+      </text>
+    </comment>
+    <comment ref="H128" authorId="90" shapeId="0" xr:uid="{B61385CD-4D45-43DD-A9B8-1F9A74DDBE7A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Using 5 Year Average</t>
+      </text>
+    </comment>
+    <comment ref="H130" authorId="91" shapeId="0" xr:uid="{2688BE2C-FA58-404B-A32E-6069952950F1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Holding flat due to volatile nature</t>
+      </text>
+    </comment>
+    <comment ref="H131" authorId="92" shapeId="0" xr:uid="{7E2FEC11-F235-4343-9ED2-AC7B15839631}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Holding flat due to volatile nature
+</t>
+      </text>
+    </comment>
+    <comment ref="H132" authorId="93" shapeId="0" xr:uid="{5C64ACA4-E29F-463F-B779-E9272719307F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Holding Flat at Zero, one off in 2024</t>
+      </text>
+    </comment>
+    <comment ref="H133" authorId="94" shapeId="0" xr:uid="{9A9E8B3D-B775-48CF-9620-F2C10C0EC303}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Holding Flat at Zero, one off in 2024</t>
+      </text>
+    </comment>
+    <comment ref="H134" authorId="95" shapeId="0" xr:uid="{68D538B7-3B2D-4332-865D-5AD5BC490526}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Holding Flat at Zero</t>
+      </text>
+    </comment>
+    <comment ref="H135" authorId="96" shapeId="0" xr:uid="{84FA0DD2-4274-4155-A7D5-B607DD46069A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Using 5 Year Average</t>
+      </text>
+    </comment>
+    <comment ref="H137" authorId="97" shapeId="0" xr:uid="{0CF63F11-B143-4E7B-A7B4-DCEEDCB5A0BF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Holding flat due to volatile nature</t>
+      </text>
+    </comment>
+    <comment ref="H139" authorId="98" shapeId="0" xr:uid="{6D078522-323F-412D-9378-145142E98D7D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Using 5 Year Average</t>
       </text>
     </comment>
   </commentList>
@@ -1044,7 +1387,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\(#,##0\)_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1137,18 +1480,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1170,7 +1501,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1332,21 +1663,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="37" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1472,22 +1794,24 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1499,7 +1823,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1981,6 +2304,12 @@
   <threadedComment ref="H39" dT="2026-04-22T11:42:26.59" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{E020734A-44B8-41B1-9F60-59BA644A2BE0}">
     <text>Using 3 Year Average</text>
   </threadedComment>
+  <threadedComment ref="H41" dT="2026-04-26T14:51:00.30" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{4444B2F3-5D63-47A9-821B-BE774CC0C6CD}">
+    <text>Using 3 Year Average</text>
+  </threadedComment>
+  <threadedComment ref="H42" dT="2026-04-26T14:50:35.99" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{31FA1DCD-E8AF-4359-80DF-460D0C1B3788}">
+    <text>=Interest % of Debt * Total Debt</text>
+  </threadedComment>
   <threadedComment ref="H44" dT="2026-04-26T01:47:47.12" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{7EEE51B2-23C8-4486-A6A9-82B3A58CF94D}">
     <text>=EBT * Tax Rate</text>
   </threadedComment>
@@ -2016,6 +2345,9 @@
   </threadedComment>
   <threadedComment ref="H64" dT="2026-04-26T01:47:04.90" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{2C5DD1BA-6455-422A-8A06-F13DA0A1A21E}">
     <text>Declining portfolio; Boeing exiting customer financing. Linear run-off assumed.</text>
+  </threadedComment>
+  <threadedComment ref="H65" dT="2026-04-27T07:12:33.63" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{38546E84-2507-4C66-843D-B4E8B55CE5FC}">
+    <text xml:space="preserve">Prior Year PP&amp;E + CapEx - D&amp;A </text>
   </threadedComment>
   <threadedComment ref="H66" dT="2026-04-26T01:36:10.97" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{781018CE-9A74-4BD7-B24A-7BBD80AB89E7}">
     <text>Holding flat, no acquisitions acquired</text>
@@ -2091,16 +2423,128 @@
     <text>Using 5 Year Average</text>
   </threadedComment>
   <threadedComment ref="H99" dT="2026-04-26T01:54:08.31" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{949B10D3-3C46-4F0B-BC2A-F0EB9AC0FE1F}">
-    <text>Using a 5 Year Average</text>
+    <text>=D%A % of Revenue * Revenue</text>
+  </threadedComment>
+  <threadedComment ref="H100" dT="2026-04-26T23:18:35.47" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{48544A9C-5A13-48D1-917C-3108BF63C7D6}">
+    <text>Unpredictable</text>
+  </threadedComment>
+  <threadedComment ref="H101" dT="2026-04-26T23:23:24.32" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{5A51DCBB-5374-41B9-A10B-D554B01E1BF6}">
+    <text>Holding as 0</text>
+  </threadedComment>
+  <threadedComment ref="H102" dT="2026-04-26T23:20:20.93" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{E50A0D2D-3BE6-4CD1-9F5F-29554D1EAC8F}">
+    <text>One time item</text>
   </threadedComment>
   <threadedComment ref="B103" dT="2026-04-20T03:26:43.70" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{DF0D4C79-7457-440F-B77D-C897944542A1}">
     <text>777X and 787 Reach Forward Losses in 2021</text>
   </threadedComment>
+  <threadedComment ref="H103" dT="2026-04-26T23:23:05.37" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{68DB4377-F52A-4AAF-83A8-BD591DFD5B88}">
+    <text>0 as this is programme specific</text>
+  </threadedComment>
+  <threadedComment ref="H104" dT="2026-04-26T23:21:13.04" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{BFF3F063-7346-4FA0-B987-FBA065DF5BF0}">
+    <text>Using 3 Year Average</text>
+  </threadedComment>
+  <threadedComment ref="H106" dT="2026-04-26T23:39:24.96" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{0006161D-3BC5-4E50-B74E-B622B762275E}">
+    <text>Minus the change in AR
+(If there is an increase in assets, results in negative cash flow)</text>
+  </threadedComment>
+  <threadedComment ref="H107" dT="2026-04-26T23:39:39.14" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{F78C6349-BEDA-4712-A897-1FEB6ADCE4E6}">
+    <text>Minus change in Unbilled Receivables
+(If there is an increase in assets, results in negative cash flow)</text>
+  </threadedComment>
+  <threadedComment ref="H108" dT="2026-04-27T06:14:00.09" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{BF5E9D82-25FE-470A-8E1E-5BE11EEA9DB7}">
+    <text xml:space="preserve">=2026 Advances &amp; Progress Billings (BS) - 2025 Advances &amp; Progress Billings 
+(If there is an increase in liabilities, results in positive cash flow)
+</text>
+  </threadedComment>
+  <threadedComment ref="H109" dT="2026-04-27T06:20:25.69" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{812CA68D-79BF-4E4F-81F9-2C4068742389}">
+    <text>= 2025 Inventory - 2026 Inventory 
+Inventory went up, negative in CFS</text>
+  </threadedComment>
+  <threadedComment ref="H110" dT="2026-04-27T06:31:41.17" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{809AE375-C473-4387-B29D-B0C30E437B93}">
+    <text xml:space="preserve">= 2025 Other CA (BS) − 2026 Other CA (BS)
+(Increase in Assets result in negative cash flow) </text>
+  </threadedComment>
+  <threadedComment ref="H111" dT="2026-04-27T06:32:29.43" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{9D7F316F-17BF-4FB3-B0FE-FC87EC6234D0}">
+    <text>= 2026 AP (BS) − 2025 AP (BS) 
+(Increase in liabilities means positive cash flow)</text>
+  </threadedComment>
+  <threadedComment ref="H112" dT="2026-04-27T06:33:59.63" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{CEC400AD-C561-4A30-9BB2-CA4E9DB69447}">
+    <text>= 2026 Liabilities - 2025 Liabilities
+(Increase in liabilities means positive cash flow)</text>
+  </threadedComment>
+  <threadedComment ref="H113" dT="2026-04-27T06:36:11.27" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{4A83F404-C9A2-46C7-9506-E1EF1742A4DE}">
+    <text>0 as forecast is held flat</text>
+  </threadedComment>
+  <threadedComment ref="H114" dT="2026-04-27T06:36:15.42" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{48A8B806-0B54-4F16-8A9B-5449EA0673F3}">
+    <text>0 as forecast is held flat</text>
+  </threadedComment>
+  <threadedComment ref="H115" dT="2026-04-26T23:41:31.74" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{7FFEBBFF-5D9C-4BFD-9657-AA07CCCF1643}">
+    <text>Using 3 Year Average</text>
+  </threadedComment>
+  <threadedComment ref="H116" dT="2026-04-27T06:39:21.47" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{BC23432E-35D7-4C91-BB36-3B8971C0F0EF}">
+    <text>= (2026 BS balance - 2025 BS balance)
+(A decrease in assets means positive cash flow)</text>
+  </threadedComment>
+  <threadedComment ref="H117" dT="2026-04-26T23:41:39.54" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{C43B1633-B4E0-4CF6-9023-271AD363286E}">
+    <text>Using 3 Year Average</text>
+  </threadedComment>
   <threadedComment ref="B119" dT="2026-04-20T08:39:06.63" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{3406BCD8-C23B-47A2-8911-97DD0FF0B2D2}">
     <text>Payments to Acquire Property, Plant and Equipment</text>
   </threadedComment>
   <threadedComment ref="H119" dT="2026-04-26T01:54:13.91" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{6B97D321-1CD9-43E7-8CB5-8D4B80105B9D}">
     <text>Using a 5 Year Average</text>
+  </threadedComment>
+  <threadedComment ref="H120" dT="2026-04-27T06:42:51.15" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{4D3C0DCE-13AE-4FE3-9352-785F2D5EEE07}">
+    <text>Using 5 Year Average</text>
+  </threadedComment>
+  <threadedComment ref="H121" dT="2026-04-27T06:43:26.06" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{6BCFBAF5-47C0-476F-8B84-2B2FCEB0D212}">
+    <text>Holding Flat at Zero</text>
+  </threadedComment>
+  <threadedComment ref="H122" dT="2026-04-27T06:43:43.62" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{C0D67968-DD41-4C7C-A6EC-F945E41037B8}">
+    <text>Holding Flat at Zero</text>
+  </threadedComment>
+  <threadedComment ref="H123" dT="2026-04-27T06:44:09.03" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{8E6376C5-2961-4711-B206-F04555A70644}">
+    <text>Using 5 Year Average</text>
+  </threadedComment>
+  <threadedComment ref="H124" dT="2026-04-27T06:44:30.47" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{D4DAA8F8-ADD5-4E4C-9817-F0478F5E63A3}">
+    <text>Using 5 Year Average</text>
+  </threadedComment>
+  <threadedComment ref="H125" dT="2026-04-27T06:45:33.14" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{4700DE3E-E3F0-42B6-B9F2-C0D6D39111C3}">
+    <text>Using 3 Year Average</text>
+  </threadedComment>
+  <threadedComment ref="H126" dT="2026-04-27T06:43:43.62" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{76663011-AFEF-4E06-A983-640D69F7354B}">
+    <text>Holding Flat at Zero</text>
+  </threadedComment>
+  <threadedComment ref="H127" dT="2026-04-27T06:43:43.62" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{E9384446-E2E6-4EAA-912C-AA254CC96811}">
+    <text>Holding Flat at Zero</text>
+  </threadedComment>
+  <threadedComment ref="H128" dT="2026-04-27T06:46:21.52" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{B61385CD-4D45-43DD-A9B8-1F9A74DDBE7A}">
+    <text>Using 5 Year Average</text>
+  </threadedComment>
+  <threadedComment ref="H130" dT="2026-04-27T06:47:38.84" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{2688BE2C-FA58-404B-A32E-6069952950F1}">
+    <text>Holding flat due to volatile nature</text>
+  </threadedComment>
+  <threadedComment ref="H131" dT="2026-04-27T06:47:54.99" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{7E2FEC11-F235-4343-9ED2-AC7B15839631}">
+    <text xml:space="preserve">Holding flat due to volatile nature
+</text>
+  </threadedComment>
+  <threadedComment ref="H132" dT="2026-04-27T06:43:43.62" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{5C64ACA4-E29F-463F-B779-E9272719307F}">
+    <text>Holding Flat at Zero, one off in 2024</text>
+  </threadedComment>
+  <threadedComment ref="H133" dT="2026-04-27T06:43:43.62" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{9A9E8B3D-B775-48CF-9620-F2C10C0EC303}">
+    <text>Holding Flat at Zero, one off in 2024</text>
+  </threadedComment>
+  <threadedComment ref="H134" dT="2026-04-27T06:48:52.00" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{68D538B7-3B2D-4332-865D-5AD5BC490526}">
+    <text>Holding Flat at Zero</text>
+  </threadedComment>
+  <threadedComment ref="H135" dT="2026-04-27T06:49:14.55" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{84FA0DD2-4274-4155-A7D5-B607DD46069A}">
+    <text>Using 5 Year Average</text>
+  </threadedComment>
+  <threadedComment ref="H137" dT="2026-04-27T06:47:38.84" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{0CF63F11-B143-4E7B-A7B4-DCEEDCB5A0BF}">
+    <text>Holding flat due to volatile nature</text>
+  </threadedComment>
+  <threadedComment ref="H139" dT="2026-04-27T06:53:05.01" personId="{C44259D0-522D-4E8B-A167-570A2D87A088}" id="{6D078522-323F-412D-9378-145142E98D7D}">
+    <text>Using 5 Year Average</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -2403,7 +2847,7 @@
         <v>0.95205839285514682</v>
       </c>
       <c r="H7" s="56">
-        <f t="shared" si="5"/>
+        <f>H32/H31</f>
         <v>0.95205839285514682</v>
       </c>
       <c r="I7" s="43">
@@ -2584,23 +3028,23 @@
       </c>
       <c r="H11" s="56">
         <f t="shared" si="9"/>
-        <v>-3.7834439949919807E-2</v>
+        <v>-5.9481594784354316E-2</v>
       </c>
       <c r="I11" s="43">
         <f t="shared" ref="I11:L11" si="10">I45/I31</f>
-        <v>-3.8836295262623728E-2</v>
+        <v>-5.883748592014601E-2</v>
       </c>
       <c r="J11" s="43">
         <f t="shared" si="10"/>
-        <v>-3.9689268613569931E-2</v>
+        <v>-5.8107712228253582E-2</v>
       </c>
       <c r="K11" s="43">
         <f t="shared" si="10"/>
-        <v>-4.0652924184757362E-2</v>
+        <v>-5.6562158148381017E-2</v>
       </c>
       <c r="L11" s="86">
         <f t="shared" si="10"/>
-        <v>-4.1377744912531003E-2</v>
+        <v>-5.5791594753644237E-2</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -2753,11 +3197,26 @@
         <f t="shared" si="13"/>
         <v>2.1830253847959492E-2</v>
       </c>
-      <c r="H17" s="56"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="86"/>
+      <c r="H17" s="56">
+        <f>AVERAGE(E17:G17)</f>
+        <v>2.4451457880666091E-2</v>
+      </c>
+      <c r="I17" s="43">
+        <f t="shared" ref="I17:L17" si="14">AVERAGE(F17:H17)</f>
+        <v>2.4627892714408784E-2</v>
+      </c>
+      <c r="J17" s="43">
+        <f t="shared" si="14"/>
+        <v>2.3636534814344787E-2</v>
+      </c>
+      <c r="K17" s="43">
+        <f t="shared" si="14"/>
+        <v>2.4238628469806553E-2</v>
+      </c>
+      <c r="L17" s="86">
+        <f t="shared" si="14"/>
+        <v>2.4167685332853375E-2</v>
+      </c>
     </row>
     <row r="18" spans="2:12" ht="17.25" x14ac:dyDescent="0.4">
       <c r="B18" s="82" t="s">
@@ -2783,19 +3242,19 @@
         <v>15.476431300773848</v>
       </c>
       <c r="D19" s="59">
-        <f t="shared" ref="D19:G19" si="14">D58/D31 * 365</f>
+        <f t="shared" ref="D19:G19" si="15">D58/D31 * 365</f>
         <v>13.792712587076627</v>
       </c>
       <c r="E19" s="59">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.428786281718386</v>
       </c>
       <c r="F19" s="59">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>14.437136371153239</v>
       </c>
       <c r="G19" s="59">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.917384840660384</v>
       </c>
       <c r="H19" s="62">
@@ -2803,19 +3262,19 @@
         <v>13.610490276276497</v>
       </c>
       <c r="I19" s="60">
-        <f t="shared" ref="I19:L19" si="15">AVERAGE(D19:H19)</f>
+        <f t="shared" ref="I19:L19" si="16">AVERAGE(D19:H19)</f>
         <v>13.237302071377027</v>
       </c>
       <c r="J19" s="60">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>13.126219968237105</v>
       </c>
       <c r="K19" s="60">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>13.26570670554085</v>
       </c>
       <c r="L19" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>13.031420772418375</v>
       </c>
     </row>
@@ -2828,19 +3287,19 @@
         <v>485.68285024562351</v>
       </c>
       <c r="D20" s="59">
-        <f t="shared" ref="D20:G20" si="16">D61/D32 *365</f>
+        <f t="shared" ref="D20:F20" si="17">D61/D32 *365</f>
         <v>452.21971210247631</v>
       </c>
       <c r="E20" s="59">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>415.37698016269445</v>
       </c>
       <c r="F20" s="59">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>466.45282302796755</v>
       </c>
       <c r="G20" s="59">
-        <f t="shared" si="16"/>
+        <f>G61/G32 *365</f>
         <v>362.87875407988355</v>
       </c>
       <c r="H20" s="61">
@@ -2848,19 +3307,19 @@
         <v>414.90285242351518</v>
       </c>
       <c r="I20" s="59">
-        <f t="shared" ref="I20:L20" si="17">AVERAGE(F20:H20)</f>
+        <f t="shared" ref="I20:L20" si="18">AVERAGE(F20:H20)</f>
         <v>414.74480984378874</v>
       </c>
       <c r="J20" s="59">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>397.50880544906249</v>
       </c>
       <c r="K20" s="59">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>409.05215590545549</v>
       </c>
       <c r="L20" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>407.10192373276891</v>
       </c>
     </row>
@@ -2873,39 +3332,39 @@
         <v>57.063406316997828</v>
       </c>
       <c r="D21" s="59">
-        <f t="shared" ref="D21:G21" si="18">D72/D32 *365</f>
+        <f t="shared" ref="D21:G21" si="19">D72/D32 *365</f>
         <v>59.022163036240848</v>
       </c>
       <c r="E21" s="59">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>62.321392892821464</v>
       </c>
       <c r="F21" s="59">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>60.545629707479421</v>
       </c>
       <c r="G21" s="59">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>56.176591448094491</v>
       </c>
       <c r="H21" s="61">
-        <f t="shared" ref="H21:L21" si="19">AVERAGE(C21:G21)</f>
+        <f t="shared" ref="H21:L21" si="20">AVERAGE(C21:G21)</f>
         <v>59.025836680326805</v>
       </c>
       <c r="I21" s="59">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>59.418322752992609</v>
       </c>
       <c r="J21" s="59">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>59.497554696342959</v>
       </c>
       <c r="K21" s="59">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>58.932787057047257</v>
       </c>
       <c r="L21" s="91">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>58.610218526960828</v>
       </c>
     </row>
@@ -2918,19 +3377,19 @@
         <v>0.85059242847509875</v>
       </c>
       <c r="D22" s="43">
-        <f t="shared" ref="D22:G22" si="20">D74/D31</f>
+        <f t="shared" ref="D22:G22" si="21">D74/D31</f>
         <v>0.79691628633197209</v>
       </c>
       <c r="E22" s="43">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.72406612335141529</v>
       </c>
       <c r="F22" s="43">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.90703128523535337</v>
       </c>
       <c r="G22" s="43">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.66400634899343858</v>
       </c>
       <c r="H22" s="56"/>
@@ -2963,19 +3422,19 @@
         <v>41858</v>
       </c>
       <c r="D24" s="46">
-        <f t="shared" ref="D24:G24" si="21">D81+D75-D56-D57</f>
+        <f t="shared" ref="D24:G24" si="22">D81+D75-D56-D57</f>
         <v>39781</v>
       </c>
       <c r="E24" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>36342</v>
       </c>
       <c r="F24" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>27582</v>
       </c>
       <c r="G24" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>24698</v>
       </c>
       <c r="H24" s="65">
@@ -2983,19 +3442,19 @@
         <v>29540.666666666668</v>
       </c>
       <c r="I24" s="46">
-        <f t="shared" ref="I24:L24" si="22">AVERAGE(F24:H24)</f>
+        <f t="shared" ref="I24:L24" si="23">AVERAGE(F24:H24)</f>
         <v>27273.555555555558</v>
       </c>
       <c r="J24" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>27170.740740740745</v>
       </c>
       <c r="K24" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>27994.987654320994</v>
       </c>
       <c r="L24" s="92">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>27479.761316872435</v>
       </c>
     </row>
@@ -3004,11 +3463,11 @@
         <v>108</v>
       </c>
       <c r="C25" s="47" t="str">
-        <f t="shared" ref="C25:D25" si="23">IF(C24/(C38+C99)&lt;0,"nm",C24/(C38+C99))</f>
+        <f t="shared" ref="C25:D25" si="24">IF(C24/(C38+C99)&lt;0,"nm",C24/(C38+C99))</f>
         <v>nm</v>
       </c>
       <c r="D25" s="47" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>nm</v>
       </c>
       <c r="E25" s="47">
@@ -3016,11 +3475,11 @@
         <v>34.944230769230771</v>
       </c>
       <c r="F25" s="47" t="str">
-        <f t="shared" ref="F25" si="24">IF(F24/(F38+F99)&lt;0,"nm",F24/(F38+F99))</f>
+        <f t="shared" ref="F25" si="25">IF(F24/(F38+F99)&lt;0,"nm",F24/(F38+F99))</f>
         <v>nm</v>
       </c>
       <c r="G25" s="47" t="str">
-        <f t="shared" ref="G25" si="25">IF(G24/(G38+G99)&lt;0,"nm",G24/(G38+G99))</f>
+        <f t="shared" ref="G25" si="26">IF(G24/(G38+G99)&lt;0,"nm",G24/(G38+G99))</f>
         <v>nm</v>
       </c>
       <c r="H25" s="78"/>
@@ -3038,19 +3497,19 @@
         <v>nm</v>
       </c>
       <c r="D26" s="47" t="str">
-        <f t="shared" ref="D26:G26" si="26">IF(D42/(D81+D75)&lt;0,"nm",D42/(D81+D75))</f>
+        <f t="shared" ref="D26:G26" si="27">IF(D42/(D81+D75)&lt;0,"nm",D42/(D81+D75))</f>
         <v>nm</v>
       </c>
       <c r="E26" s="47" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>nm</v>
       </c>
       <c r="F26" s="47" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>nm</v>
       </c>
       <c r="G26" s="47" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>nm</v>
       </c>
       <c r="H26" s="56"/>
@@ -3068,19 +3527,19 @@
         <v>-4.6710956593576811E-2</v>
       </c>
       <c r="D27" s="52">
-        <f t="shared" ref="D27:G27" si="27">D42/(D75+D81)</f>
+        <f t="shared" ref="D27:G27" si="28">D42/(D75+D81)</f>
         <v>-4.4929036332695918E-2</v>
       </c>
       <c r="E27" s="52">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-4.7010916320951307E-2</v>
       </c>
       <c r="F27" s="52">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-5.0590375761176296E-2</v>
       </c>
       <c r="G27" s="52">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-5.1221856630559358E-2</v>
       </c>
       <c r="H27" s="63">
@@ -3088,19 +3547,19 @@
         <v>-4.960771623756232E-2</v>
       </c>
       <c r="I27" s="52">
-        <f t="shared" ref="I27:L27" si="28">AVERAGE(F27:H27)</f>
+        <f t="shared" ref="I27:L27" si="29">AVERAGE(F27:H27)</f>
         <v>-5.0473316209765993E-2</v>
       </c>
       <c r="J27" s="52">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-5.0434296359295888E-2</v>
       </c>
       <c r="K27" s="52">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-5.0171776268874736E-2</v>
       </c>
       <c r="L27" s="95">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-5.0359796279312204E-2</v>
       </c>
     </row>
@@ -3134,23 +3593,23 @@
         <v>2025</v>
       </c>
       <c r="H30" s="2">
-        <f t="shared" ref="H30" si="29">+G30+1</f>
+        <f t="shared" ref="H30" si="30">+G30+1</f>
         <v>2026</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" ref="I30" si="30">+H30+1</f>
+        <f t="shared" ref="I30" si="31">+H30+1</f>
         <v>2027</v>
       </c>
       <c r="J30" s="2">
-        <f t="shared" ref="J30" si="31">+I30+1</f>
+        <f t="shared" ref="J30" si="32">+I30+1</f>
         <v>2028</v>
       </c>
       <c r="K30" s="2">
-        <f t="shared" ref="K30" si="32">+J30+1</f>
+        <f t="shared" ref="K30" si="33">+J30+1</f>
         <v>2029</v>
       </c>
       <c r="L30" s="2">
-        <f t="shared" ref="L30" si="33">+K30+1</f>
+        <f t="shared" ref="L30" si="34">+K30+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -3178,19 +3637,19 @@
         <v>97939.235908870192</v>
       </c>
       <c r="I31" s="42">
-        <f t="shared" ref="I31:L31" si="34">H31*(1+I4)</f>
+        <f t="shared" ref="I31:L31" si="35">H31*(1+I4)</f>
         <v>107848.54514840148</v>
       </c>
       <c r="J31" s="42">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>117025.72437734834</v>
       </c>
       <c r="K31" s="42">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>134777.84533508398</v>
       </c>
       <c r="L31" s="42">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>149318.03705658542</v>
       </c>
     </row>
@@ -3218,19 +3677,19 @@
         <v>93243.871536860039</v>
       </c>
       <c r="I32" s="98">
-        <f t="shared" ref="I32:L32" si="35">I31*H7</f>
+        <f t="shared" ref="I32:L32" si="36">I31*H7</f>
         <v>102678.11256575285</v>
       </c>
       <c r="J32" s="98">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>111415.32307340764</v>
       </c>
       <c r="K32" s="98">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>128316.37882219961</v>
       </c>
       <c r="L32" s="98">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>142159.49038437798</v>
       </c>
     </row>
@@ -3259,23 +3718,23 @@
         <v>4289</v>
       </c>
       <c r="H33" s="97">
-        <f t="shared" ref="H33:L33" si="36">SUM(H31-H32)</f>
+        <f t="shared" ref="H33:L33" si="37">SUM(H31-H32)</f>
         <v>4695.3643720101536</v>
       </c>
       <c r="I33" s="71">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5170.4325826486311</v>
       </c>
       <c r="J33" s="71">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5610.4013039407</v>
       </c>
       <c r="K33" s="71">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>6461.4665128843772</v>
       </c>
       <c r="L33" s="71">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>7158.5466722074489</v>
       </c>
     </row>
@@ -3318,15 +3777,15 @@
         <v>7341.5561735439787</v>
       </c>
       <c r="J35" s="42">
-        <f t="shared" ref="J35:L35" si="37">J31*I8</f>
+        <f t="shared" ref="J35:L35" si="38">J31*I8</f>
         <v>7966.2727771039572</v>
       </c>
       <c r="K35" s="42">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>9174.7099704979864</v>
       </c>
       <c r="L35" s="42">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>10164.502036312277</v>
       </c>
     </row>
@@ -3354,19 +3813,19 @@
         <v>3957.5057600411988</v>
       </c>
       <c r="I36" s="98">
-        <f t="shared" ref="I36:L36" si="38">I31*H9</f>
+        <f t="shared" ref="I36:L36" si="39">I31*H9</f>
         <v>4357.918812374628</v>
       </c>
       <c r="J36" s="98">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>4728.7481263104773</v>
       </c>
       <c r="K36" s="98">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>5446.0716819951112</v>
       </c>
       <c r="L36" s="98">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6033.6083516040853</v>
       </c>
     </row>
@@ -3379,39 +3838,39 @@
         <v>6406</v>
       </c>
       <c r="D37" s="7">
-        <f t="shared" ref="D37:L37" si="39">SUM(D35:D36)</f>
+        <f t="shared" ref="D37:L37" si="40">SUM(D35:D36)</f>
         <v>7039</v>
       </c>
       <c r="E37" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>8545</v>
       </c>
       <c r="F37" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>8833</v>
       </c>
       <c r="G37" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>9705</v>
       </c>
       <c r="H37" s="97">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>10624.507164923882</v>
       </c>
       <c r="I37" s="71">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11699.474985918607</v>
       </c>
       <c r="J37" s="71">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12695.020903414435</v>
       </c>
       <c r="K37" s="71">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>14620.781652493097</v>
       </c>
       <c r="L37" s="71">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>16198.110387916362</v>
       </c>
     </row>
@@ -3420,43 +3879,43 @@
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <f t="shared" ref="C38:H38" si="40">SUM(C33-C37)</f>
+        <f t="shared" ref="C38:H38" si="41">SUM(C33-C37)</f>
         <v>-3357</v>
       </c>
       <c r="D38" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>-3509</v>
       </c>
       <c r="E38" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>-821</v>
       </c>
       <c r="F38" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>-10824</v>
       </c>
       <c r="G38" s="29">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>-5416</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>-5929.142792913728</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" ref="I38:L38" si="41">SUM(I33-I37)</f>
+        <f t="shared" ref="I38:L38" si="42">SUM(I33-I37)</f>
         <v>-6529.0424032699757</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-7084.6195994737354</v>
       </c>
       <c r="K38" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-8159.3151396087196</v>
       </c>
       <c r="L38" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-9039.5637157089132</v>
       </c>
     </row>
@@ -3484,19 +3943,19 @@
         <v>47.333333333333336</v>
       </c>
       <c r="I39" s="68">
-        <f t="shared" ref="I39:L39" si="42">AVERAGE(F39:H39)</f>
+        <f t="shared" ref="I39:L39" si="43">AVERAGE(F39:H39)</f>
         <v>47.777777777777779</v>
       </c>
       <c r="J39" s="68">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>40.037037037037038</v>
       </c>
       <c r="K39" s="68">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>45.049382716049386</v>
       </c>
       <c r="L39" s="68">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>44.288065843621403</v>
       </c>
     </row>
@@ -3559,19 +4018,19 @@
         <v>1191.3333333333333</v>
       </c>
       <c r="I41" s="68">
-        <f t="shared" ref="I41:L41" si="43">AVERAGE(F41:H41)</f>
+        <f t="shared" ref="I41:L41" si="44">AVERAGE(F41:H41)</f>
         <v>1179.4444444444443</v>
       </c>
       <c r="J41" s="68">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1165.2592592592591</v>
       </c>
       <c r="K41" s="68">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1178.6790123456788</v>
       </c>
       <c r="L41" s="68">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1174.4609053497941</v>
       </c>
     </row>
@@ -3595,7 +4054,26 @@
       <c r="G42" s="5">
         <v>-2771</v>
       </c>
-      <c r="H42" s="19"/>
+      <c r="H42" s="66">
+        <f>H27*(H75+H81)</f>
+        <v>-2683.6782330196465</v>
+      </c>
+      <c r="I42" s="98">
+        <f t="shared" ref="I42:L42" si="45">I27*(I75+I81)</f>
+        <v>-2730.5054603159206</v>
+      </c>
+      <c r="J42" s="98">
+        <f t="shared" si="45"/>
+        <v>-2728.3945644451887</v>
+      </c>
+      <c r="K42" s="98">
+        <f t="shared" si="45"/>
+        <v>-2714.1927525935853</v>
+      </c>
+      <c r="L42" s="98">
+        <f t="shared" si="45"/>
+        <v>-2724.3642591182315</v>
+      </c>
     </row>
     <row r="43" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B43" s="6" t="s">
@@ -3606,40 +4084,40 @@
         <v>-5033</v>
       </c>
       <c r="D43" s="7">
-        <f t="shared" ref="D43:F43" si="44">SUM(D38:D42)</f>
+        <f t="shared" ref="D43:F43" si="46">SUM(D38:D42)</f>
         <v>-5022</v>
       </c>
       <c r="E43" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-2005</v>
       </c>
       <c r="F43" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-12210</v>
       </c>
       <c r="G43" s="7">
         <f>SUM(G38:G42)</f>
         <v>2635</v>
       </c>
-      <c r="H43" s="99">
+      <c r="H43" s="108">
         <f>SUM(H38:H42)</f>
-        <v>-4690.476126247062</v>
-      </c>
-      <c r="I43" s="100">
-        <f t="shared" ref="I43:L43" si="45">SUM(I38:I42)</f>
-        <v>-5301.820181047754</v>
-      </c>
-      <c r="J43" s="100">
-        <f t="shared" si="45"/>
-        <v>-5879.3233031774389</v>
-      </c>
-      <c r="K43" s="100">
-        <f t="shared" si="45"/>
-        <v>-6935.5867445469921</v>
-      </c>
-      <c r="L43" s="100">
-        <f t="shared" si="45"/>
-        <v>-7820.8147445154982</v>
+        <v>-7374.1543592667085</v>
+      </c>
+      <c r="I43" s="109">
+        <f t="shared" ref="I43:L43" si="47">SUM(I38:I42)</f>
+        <v>-8032.3256413636745</v>
+      </c>
+      <c r="J43" s="109">
+        <f t="shared" si="47"/>
+        <v>-8607.7178676226285</v>
+      </c>
+      <c r="K43" s="109">
+        <f t="shared" si="47"/>
+        <v>-9649.7794971405783</v>
+      </c>
+      <c r="L43" s="109">
+        <f t="shared" si="47"/>
+        <v>-10545.17900363373</v>
       </c>
     </row>
     <row r="44" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -3663,23 +4141,23 @@
       </c>
       <c r="H44" s="67">
         <f>H43*H13</f>
-        <v>-984.99998651188298</v>
+        <v>-1548.5724154460088</v>
       </c>
       <c r="I44" s="68">
-        <f t="shared" ref="I44:L44" si="46">I43*I13</f>
-        <v>-1113.3822380200284</v>
+        <f t="shared" ref="I44:L44" si="48">I43*I13</f>
+        <v>-1686.7883846863715</v>
       </c>
       <c r="J44" s="68">
-        <f t="shared" si="46"/>
-        <v>-1234.6578936672622</v>
+        <f t="shared" si="48"/>
+        <v>-1807.6207522007519</v>
       </c>
       <c r="K44" s="68">
-        <f t="shared" si="46"/>
-        <v>-1456.4732163548683</v>
+        <f t="shared" si="48"/>
+        <v>-2026.4536943995213</v>
       </c>
       <c r="L44" s="68">
-        <f t="shared" si="46"/>
-        <v>-1642.3710963482545</v>
+        <f t="shared" si="48"/>
+        <v>-2214.4875907630831</v>
       </c>
     </row>
     <row r="45" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -3687,44 +4165,44 @@
         <v>50</v>
       </c>
       <c r="C45" s="13">
-        <f t="shared" ref="C45:L45" si="47">SUM(C43-C44)</f>
+        <f t="shared" ref="C45:L45" si="49">SUM(C43-C44)</f>
         <v>-4290</v>
       </c>
       <c r="D45" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-5053</v>
       </c>
       <c r="E45" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-2242</v>
       </c>
       <c r="F45" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-11829</v>
       </c>
       <c r="G45" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>2238</v>
       </c>
       <c r="H45" s="75">
-        <f t="shared" si="47"/>
-        <v>-3705.476139735179</v>
+        <f t="shared" si="49"/>
+        <v>-5825.5819438207</v>
       </c>
       <c r="I45" s="13">
-        <f t="shared" si="47"/>
-        <v>-4188.4379430277259</v>
+        <f t="shared" si="49"/>
+        <v>-6345.537256677303</v>
       </c>
       <c r="J45" s="13">
-        <f t="shared" si="47"/>
-        <v>-4644.6654095101767</v>
+        <f t="shared" si="49"/>
+        <v>-6800.0971154218769</v>
       </c>
       <c r="K45" s="13">
-        <f t="shared" si="47"/>
-        <v>-5479.1135281921233</v>
+        <f t="shared" si="49"/>
+        <v>-7623.3258027410575</v>
       </c>
       <c r="L45" s="13">
-        <f t="shared" si="47"/>
-        <v>-6178.4436481672437</v>
+        <f t="shared" si="49"/>
+        <v>-8330.6914128706467</v>
       </c>
     </row>
     <row r="46" spans="2:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.3">
@@ -3751,19 +4229,19 @@
         <v>-9.6666666666666661</v>
       </c>
       <c r="I46" s="68">
-        <f t="shared" ref="I46:L46" si="48">AVERAGE(F46:H46)</f>
+        <f t="shared" ref="I46:L46" si="50">AVERAGE(F46:H46)</f>
         <v>-6.2222222222222214</v>
       </c>
       <c r="J46" s="68">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>-4.2962962962962958</v>
       </c>
       <c r="K46" s="68">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>-6.7283950617283947</v>
       </c>
       <c r="L46" s="68">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>-5.7489711934156373</v>
       </c>
     </row>
@@ -3772,19 +4250,19 @@
         <v>118</v>
       </c>
       <c r="C47" s="17">
-        <f t="shared" ref="C47:F47" si="49">SUM(C45-C46)</f>
+        <f t="shared" ref="C47:F47" si="51">SUM(C45-C46)</f>
         <v>-4202</v>
       </c>
       <c r="D47" s="17">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-4935</v>
       </c>
       <c r="E47" s="17">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-2222</v>
       </c>
       <c r="F47" s="17">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-11817</v>
       </c>
       <c r="G47" s="17">
@@ -3792,24 +4270,24 @@
         <v>2235</v>
       </c>
       <c r="H47" s="72">
-        <f t="shared" ref="H47:L47" si="50">SUM(H45-H46)</f>
-        <v>-3695.8094730685125</v>
+        <f t="shared" ref="H47:L47" si="52">SUM(H45-H46)</f>
+        <v>-5815.915277154033</v>
       </c>
       <c r="I47" s="17">
         <f>SUM(I45-I46)</f>
-        <v>-4182.2157208055032</v>
+        <v>-6339.3150344550804</v>
       </c>
       <c r="J47" s="17">
-        <f t="shared" si="50"/>
-        <v>-4640.3691132138802</v>
+        <f t="shared" si="52"/>
+        <v>-6795.8008191255803</v>
       </c>
       <c r="K47" s="17">
-        <f t="shared" si="50"/>
-        <v>-5472.3851331303949</v>
+        <f t="shared" si="52"/>
+        <v>-7616.5974076793291</v>
       </c>
       <c r="L47" s="17">
-        <f t="shared" si="50"/>
-        <v>-6172.6946769738279</v>
+        <f t="shared" si="52"/>
+        <v>-8324.9424416772308</v>
       </c>
     </row>
     <row r="48" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -3852,15 +4330,15 @@
         <v>120</v>
       </c>
       <c r="C49" s="17">
-        <f t="shared" ref="C49:E49" si="51">SUM(C47-C48)</f>
+        <f t="shared" ref="C49:E49" si="53">SUM(C47-C48)</f>
         <v>-4202</v>
       </c>
       <c r="D49" s="17">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-4935</v>
       </c>
       <c r="E49" s="17">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-2222</v>
       </c>
       <c r="F49" s="17">
@@ -3872,24 +4350,24 @@
         <v>1890</v>
       </c>
       <c r="H49" s="71">
-        <f t="shared" ref="H49:L49" si="52">SUM(H47:H48)</f>
-        <v>-4040.8094730685125</v>
+        <f t="shared" ref="H49:L49" si="54">SUM(H47:H48)</f>
+        <v>-6160.915277154033</v>
       </c>
       <c r="I49" s="71">
-        <f t="shared" si="52"/>
-        <v>-4355.2157208055032</v>
+        <f t="shared" si="54"/>
+        <v>-6512.3150344550804</v>
       </c>
       <c r="J49" s="71">
-        <f t="shared" si="52"/>
-        <v>-4640.3691132138802</v>
+        <f t="shared" si="54"/>
+        <v>-6795.8008191255803</v>
       </c>
       <c r="K49" s="71">
-        <f t="shared" si="52"/>
-        <v>-5472.3851331303949</v>
+        <f t="shared" si="54"/>
+        <v>-7616.5974076793291</v>
       </c>
       <c r="L49" s="71">
-        <f t="shared" si="52"/>
-        <v>-6172.6946769738279</v>
+        <f t="shared" si="54"/>
+        <v>-8324.9424416772308</v>
       </c>
     </row>
     <row r="50" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -3916,19 +4394,19 @@
         <v>670.83333333333326</v>
       </c>
       <c r="I50" s="70">
-        <f t="shared" ref="I50:L50" si="53">AVERAGE(F50:H50)</f>
+        <f t="shared" ref="I50:L50" si="55">AVERAGE(F50:H50)</f>
         <v>692.51111111111095</v>
       </c>
       <c r="J50" s="70">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>707.71481481481476</v>
       </c>
       <c r="K50" s="70">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>690.35308641975291</v>
       </c>
       <c r="L50" s="70">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>696.85967078189287</v>
       </c>
     </row>
@@ -3941,15 +4419,15 @@
         <v>-7.1511232130701154</v>
       </c>
       <c r="D51" s="50">
-        <f t="shared" ref="D51:L51" si="54">D49/D50</f>
+        <f t="shared" ref="D51:L51" si="56">D49/D50</f>
         <v>-8.2955118507312164</v>
       </c>
       <c r="E51" s="50">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>-3.6678771871904923</v>
       </c>
       <c r="F51" s="50">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>-18.356778481991036</v>
       </c>
       <c r="G51" s="50">
@@ -3958,23 +4436,23 @@
       </c>
       <c r="H51" s="73">
         <f>H49/H50</f>
-        <v>-6.0235669163754233</v>
+        <v>-9.1839730839563227</v>
       </c>
       <c r="I51" s="50">
-        <f t="shared" si="54"/>
-        <v>-6.2890192676009269</v>
+        <f t="shared" si="56"/>
+        <v>-9.4039141465994511</v>
       </c>
       <c r="J51" s="50">
-        <f t="shared" si="54"/>
-        <v>-6.5568347815752723</v>
+        <f t="shared" si="56"/>
+        <v>-9.6024566348859235</v>
       </c>
       <c r="K51" s="50">
-        <f t="shared" si="54"/>
-        <v>-7.9269365789480082</v>
+        <f t="shared" si="56"/>
+        <v>-11.032901217520214</v>
       </c>
       <c r="L51" s="50">
-        <f t="shared" si="54"/>
-        <v>-8.8578733076171847</v>
+        <f t="shared" si="56"/>
+        <v>-11.946368531179958</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -4001,19 +4479,19 @@
         <v>671.66666666666663</v>
       </c>
       <c r="I52" s="68">
-        <f t="shared" ref="I52:L52" si="55">AVERAGE(F52:H52)</f>
+        <f t="shared" ref="I52:L52" si="57">AVERAGE(F52:H52)</f>
         <v>693.62222222222215</v>
       </c>
       <c r="J52" s="68">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>709.19629629629628</v>
       </c>
       <c r="K52" s="68">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>691.49506172839494</v>
       </c>
       <c r="L52" s="68">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>698.10452674897113</v>
       </c>
     </row>
@@ -4026,40 +4504,40 @@
         <v>-7.1511232130701154</v>
       </c>
       <c r="D53" s="51">
-        <f t="shared" ref="D53:L53" si="56">D49/D52</f>
+        <f t="shared" ref="D53:L53" si="58">D49/D52</f>
         <v>-8.2955118507312164</v>
       </c>
       <c r="E53" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>-3.6678771871904923</v>
       </c>
       <c r="F53" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>-18.356778481991036</v>
       </c>
       <c r="G53" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>2.4793388429752068</v>
       </c>
       <c r="H53" s="74">
-        <f t="shared" si="56"/>
-        <v>-6.0160935082905898</v>
+        <f t="shared" si="58"/>
+        <v>-9.1725785764079895</v>
       </c>
       <c r="I53" s="51">
-        <f t="shared" si="56"/>
-        <v>-6.2789449087318641</v>
+        <f t="shared" si="58"/>
+        <v>-9.3888500480722339</v>
       </c>
       <c r="J53" s="51">
-        <f t="shared" si="56"/>
-        <v>-6.5431378272104972</v>
+        <f t="shared" si="58"/>
+        <v>-9.5823975035063516</v>
       </c>
       <c r="K53" s="51">
-        <f t="shared" si="56"/>
-        <v>-7.9138455731732114</v>
+        <f t="shared" si="58"/>
+        <v>-11.014680840441015</v>
       </c>
       <c r="L53" s="51">
-        <f t="shared" si="56"/>
-        <v>-8.8420779990063654</v>
+        <f t="shared" si="58"/>
+        <v>-11.925065835693637</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -4070,15 +4548,15 @@
         <v>2021</v>
       </c>
       <c r="D55" s="2">
-        <f t="shared" ref="D55:E55" si="57">+C55+1</f>
+        <f t="shared" ref="D55:E55" si="59">+C55+1</f>
         <v>2022</v>
       </c>
       <c r="E55" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>2023</v>
       </c>
       <c r="F55" s="2">
-        <f t="shared" ref="F55" si="58">+E55+1</f>
+        <f t="shared" ref="F55" si="60">+E55+1</f>
         <v>2024</v>
       </c>
       <c r="G55" s="2">
@@ -4086,23 +4564,23 @@
         <v>2025</v>
       </c>
       <c r="H55" s="2">
-        <f t="shared" ref="H55:L55" si="59">+G55+1</f>
+        <f t="shared" ref="H55:L55" si="61">+G55+1</f>
         <v>2026</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>2027</v>
       </c>
       <c r="J55" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>2028</v>
       </c>
       <c r="K55" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>2029</v>
       </c>
       <c r="L55" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>2030</v>
       </c>
     </row>
@@ -4125,6 +4603,26 @@
       <c r="G56" s="49">
         <v>10921</v>
       </c>
+      <c r="H56" s="68">
+        <f>H144</f>
+        <v>-7771.6140994320704</v>
+      </c>
+      <c r="I56" s="68">
+        <f t="shared" ref="I56:L56" si="62">I144</f>
+        <v>-17843.033783791336</v>
+      </c>
+      <c r="J56" s="68">
+        <f t="shared" si="62"/>
+        <v>-24749.5122860181</v>
+      </c>
+      <c r="K56" s="68">
+        <f t="shared" si="62"/>
+        <v>-41729.38729102887</v>
+      </c>
+      <c r="L56" s="68">
+        <f t="shared" si="62"/>
+        <v>-53543.353101821362</v>
+      </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B57" s="14" t="s">
@@ -4150,19 +4648,19 @@
         <v>18479</v>
       </c>
       <c r="I57" s="42">
-        <f t="shared" ref="I57:L57" si="60">H57</f>
+        <f t="shared" ref="I57:L57" si="63">H57</f>
         <v>18479</v>
       </c>
       <c r="J57" s="42">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>18479</v>
       </c>
       <c r="K57" s="42">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>18479</v>
       </c>
       <c r="L57" s="42">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>18479</v>
       </c>
     </row>
@@ -4190,19 +4688,19 @@
         <v>3652.0575835715831</v>
       </c>
       <c r="I58" s="42">
-        <f t="shared" ref="I58:L58" si="61">(I19/365)*I31</f>
+        <f t="shared" ref="I58:L58" si="64">(I19/365)*I31</f>
         <v>3911.2980002409145</v>
       </c>
       <c r="J58" s="42">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>4208.5079455324976</v>
       </c>
       <c r="K58" s="42">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>4898.4201825204691</v>
       </c>
       <c r="L58" s="42">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>5331.0306021806136</v>
       </c>
     </row>
@@ -4230,19 +4728,19 @@
         <v>8618.4</v>
       </c>
       <c r="I59" s="42">
-        <f t="shared" ref="I59:L59" si="62">AVERAGE(D59:H59)</f>
+        <f t="shared" ref="I59:L59" si="65">AVERAGE(D59:H59)</f>
         <v>8618.08</v>
       </c>
       <c r="J59" s="42">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>8614.8960000000006</v>
       </c>
       <c r="K59" s="42">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>8674.4752000000008</v>
       </c>
       <c r="L59" s="42">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>8736.7702400000016</v>
       </c>
     </row>
@@ -4265,24 +4763,24 @@
       <c r="G60" s="18">
         <v>0</v>
       </c>
-      <c r="H60" s="104">
+      <c r="H60" s="100">
         <f>G60</f>
         <v>0</v>
       </c>
-      <c r="I60" s="105">
+      <c r="I60" s="101">
         <f>H60</f>
         <v>0</v>
       </c>
-      <c r="J60" s="105">
-        <f t="shared" ref="J60:L60" si="63">I60</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="105">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="L60" s="105">
-        <f t="shared" si="63"/>
+      <c r="J60" s="101">
+        <f t="shared" ref="J60:L60" si="66">I60</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="101">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="L60" s="101">
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
     </row>
@@ -4310,19 +4808,19 @@
         <v>105992.18704563027</v>
       </c>
       <c r="I61" s="42">
-        <f t="shared" ref="I61:L61" si="64">(I20/365)*I32</f>
+        <f t="shared" ref="I61:L61" si="67">(I20/365)*I32</f>
         <v>116671.81992110219</v>
       </c>
       <c r="J61" s="42">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>121338.55337981271</v>
       </c>
       <c r="K61" s="42">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>143802.99012384078</v>
       </c>
       <c r="L61" s="42">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>158557.26578726122</v>
       </c>
     </row>
@@ -4345,24 +4843,24 @@
       <c r="G62" s="5">
         <v>2301</v>
       </c>
-      <c r="H62" s="107">
+      <c r="H62" s="111">
         <f>G62*(1+H4)</f>
         <v>2519.0098904162651</v>
       </c>
-      <c r="I62" s="108">
-        <f t="shared" ref="I62:L62" si="65">H62*(1+I4)</f>
+      <c r="I62" s="112">
+        <f t="shared" ref="I62:L62" si="68">H62*(1+I4)</f>
         <v>2773.8786133538088</v>
       </c>
-      <c r="J62" s="108">
-        <f t="shared" si="65"/>
+      <c r="J62" s="112">
+        <f t="shared" si="68"/>
         <v>3009.9168571619389</v>
       </c>
-      <c r="K62" s="108">
-        <f t="shared" si="65"/>
+      <c r="K62" s="112">
+        <f t="shared" si="68"/>
         <v>3466.5037179172205</v>
       </c>
-      <c r="L62" s="108">
-        <f t="shared" si="65"/>
+      <c r="L62" s="112">
+        <f t="shared" si="68"/>
         <v>3840.4793408135556</v>
       </c>
     </row>
@@ -4383,32 +4881,32 @@
         <v>109275</v>
       </c>
       <c r="F63" s="7">
-        <f t="shared" ref="F63" si="66">SUM(F56:F62)</f>
+        <f t="shared" ref="F63" si="69">SUM(F56:F62)</f>
         <v>127998</v>
       </c>
       <c r="G63" s="7">
         <f>SUM(G56:G62)</f>
         <v>128459</v>
       </c>
-      <c r="H63" s="109">
-        <f t="shared" ref="H63:L63" si="67">SUM(H56:H62)</f>
-        <v>139260.65451961811</v>
+      <c r="H63" s="102">
+        <f>SUM(H56:H62)</f>
+        <v>131489.04042018604</v>
       </c>
       <c r="I63" s="7">
-        <f t="shared" si="67"/>
-        <v>150454.07653469691</v>
+        <f t="shared" ref="H63:L63" si="70">SUM(I56:I62)</f>
+        <v>132611.04275090556</v>
       </c>
       <c r="J63" s="7">
-        <f t="shared" si="67"/>
-        <v>155650.87418250713</v>
+        <f t="shared" si="70"/>
+        <v>130901.36189648905</v>
       </c>
       <c r="K63" s="7">
-        <f t="shared" si="67"/>
-        <v>179321.38922427848</v>
+        <f t="shared" si="70"/>
+        <v>137592.00193324959</v>
       </c>
       <c r="L63" s="7">
-        <f t="shared" si="67"/>
-        <v>194944.54597025539</v>
+        <f t="shared" si="70"/>
+        <v>141401.19286843404</v>
       </c>
     </row>
     <row r="64" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -4430,19 +4928,19 @@
       <c r="G64" s="18">
         <v>241</v>
       </c>
-      <c r="H64" s="110">
+      <c r="H64" s="103">
         <v>191</v>
       </c>
-      <c r="I64" s="111">
+      <c r="I64" s="104">
         <v>141</v>
       </c>
-      <c r="J64" s="111">
+      <c r="J64" s="104">
         <v>91</v>
       </c>
-      <c r="K64" s="111">
+      <c r="K64" s="104">
         <v>41</v>
       </c>
-      <c r="L64" s="111">
+      <c r="L64" s="104">
         <v>0</v>
       </c>
     </row>
@@ -4465,25 +4963,25 @@
       <c r="G65" s="5">
         <v>15361</v>
       </c>
-      <c r="H65" s="102">
+      <c r="H65" s="67">
         <f>G65 - H119 - H99</f>
-        <v>15186.6</v>
-      </c>
-      <c r="I65" s="106">
-        <f t="shared" ref="I65:L65" si="68">H65 - I119 - I99</f>
-        <v>15210.12</v>
-      </c>
-      <c r="J65" s="106">
-        <f t="shared" si="68"/>
-        <v>15389.744000000002</v>
-      </c>
-      <c r="K65" s="106">
-        <f t="shared" si="68"/>
-        <v>15672.0928</v>
-      </c>
-      <c r="L65" s="106">
-        <f t="shared" si="68"/>
-        <v>15932.111360000001</v>
+        <v>14746.44289830964</v>
+      </c>
+      <c r="I65" s="68">
+        <f t="shared" ref="I65:L65" si="71">H65 - I119 - I99</f>
+        <v>14030.600498989737</v>
+      </c>
+      <c r="J65" s="68">
+        <f t="shared" si="71"/>
+        <v>13348.405890570626</v>
+      </c>
+      <c r="K65" s="68">
+        <f t="shared" si="71"/>
+        <v>12276.841371532475</v>
+      </c>
+      <c r="L65" s="68">
+        <f t="shared" si="71"/>
+        <v>10856.488757429579</v>
       </c>
     </row>
     <row r="66" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -4505,24 +5003,24 @@
       <c r="G66" s="18">
         <v>17275</v>
       </c>
-      <c r="H66" s="102">
+      <c r="H66" s="99">
         <f>G66</f>
         <v>17275</v>
       </c>
-      <c r="I66" s="106">
-        <f>H66</f>
+      <c r="I66" s="18">
+        <f t="shared" ref="I66:L66" si="72">H66</f>
         <v>17275</v>
       </c>
-      <c r="J66" s="106">
-        <f t="shared" ref="J66:L66" si="69">I66</f>
+      <c r="J66" s="18">
+        <f t="shared" si="72"/>
         <v>17275</v>
       </c>
-      <c r="K66" s="106">
-        <f t="shared" si="69"/>
+      <c r="K66" s="18">
+        <f t="shared" si="72"/>
         <v>17275</v>
       </c>
-      <c r="L66" s="106">
-        <f t="shared" si="69"/>
+      <c r="L66" s="18">
+        <f t="shared" si="72"/>
         <v>17275</v>
       </c>
     </row>
@@ -4545,24 +5043,24 @@
       <c r="G67" s="5">
         <v>1567</v>
       </c>
-      <c r="H67" s="102">
+      <c r="H67" s="67">
         <f>AVERAGE(C67:G67)</f>
         <v>2098.1999999999998</v>
       </c>
-      <c r="I67" s="106">
-        <f t="shared" ref="I67:L67" si="70">AVERAGE(D67:H67)</f>
+      <c r="I67" s="68">
+        <f t="shared" ref="I67:L67" si="73">AVERAGE(D67:H67)</f>
         <v>2005.44</v>
       </c>
-      <c r="J67" s="106">
-        <f t="shared" si="70"/>
+      <c r="J67" s="68">
+        <f t="shared" si="73"/>
         <v>1944.328</v>
       </c>
-      <c r="K67" s="106">
-        <f t="shared" si="70"/>
+      <c r="K67" s="68">
+        <f t="shared" si="73"/>
         <v>1914.3935999999999</v>
       </c>
-      <c r="L67" s="106">
-        <f t="shared" si="70"/>
+      <c r="L67" s="68">
+        <f t="shared" si="73"/>
         <v>1905.8723199999997</v>
       </c>
     </row>
@@ -4585,24 +5083,24 @@
       <c r="G68" s="18">
         <v>107</v>
       </c>
-      <c r="H68" s="102">
+      <c r="H68" s="67">
         <f>G68</f>
         <v>107</v>
       </c>
-      <c r="I68" s="106">
+      <c r="I68" s="68">
         <f>H68</f>
         <v>107</v>
       </c>
-      <c r="J68" s="106">
-        <f t="shared" ref="J68:L68" si="71">I68</f>
+      <c r="J68" s="68">
+        <f t="shared" ref="J68:L68" si="74">I68</f>
         <v>107</v>
       </c>
-      <c r="K68" s="106">
-        <f t="shared" si="71"/>
+      <c r="K68" s="68">
+        <f t="shared" si="74"/>
         <v>107</v>
       </c>
-      <c r="L68" s="106">
-        <f t="shared" si="71"/>
+      <c r="L68" s="68">
+        <f t="shared" si="74"/>
         <v>107</v>
       </c>
     </row>
@@ -4625,24 +5123,24 @@
       <c r="G69" s="18">
         <v>1048</v>
       </c>
-      <c r="H69" s="102">
+      <c r="H69" s="67">
         <f>G69</f>
         <v>1048</v>
       </c>
-      <c r="I69" s="106">
+      <c r="I69" s="68">
         <f>H69</f>
         <v>1048</v>
       </c>
-      <c r="J69" s="106">
-        <f t="shared" ref="J69:L69" si="72">I69</f>
+      <c r="J69" s="68">
+        <f t="shared" ref="J69:L69" si="75">I69</f>
         <v>1048</v>
       </c>
-      <c r="K69" s="106">
-        <f t="shared" si="72"/>
+      <c r="K69" s="68">
+        <f t="shared" si="75"/>
         <v>1048</v>
       </c>
-      <c r="L69" s="106">
-        <f t="shared" si="72"/>
+      <c r="L69" s="68">
+        <f t="shared" si="75"/>
         <v>1048</v>
       </c>
     </row>
@@ -4665,24 +5163,24 @@
       <c r="G70" s="18">
         <v>4177</v>
       </c>
-      <c r="H70" s="107">
+      <c r="H70" s="111">
         <f>G70*(1+H4)</f>
         <v>4572.7528519203561</v>
       </c>
-      <c r="I70" s="108">
-        <f t="shared" ref="I70:L70" si="73">H70*(1+I4)</f>
+      <c r="I70" s="112">
+        <f t="shared" ref="I70:L70" si="76">H70*(1+I4)</f>
         <v>5035.4154576179308</v>
       </c>
-      <c r="J70" s="108">
-        <f t="shared" si="73"/>
+      <c r="J70" s="112">
+        <f t="shared" si="76"/>
         <v>5463.8951379249966</v>
       </c>
-      <c r="K70" s="108">
-        <f t="shared" si="73"/>
+      <c r="K70" s="112">
+        <f t="shared" si="76"/>
         <v>6292.73621457637</v>
       </c>
-      <c r="L70" s="108">
-        <f t="shared" si="73"/>
+      <c r="L70" s="112">
+        <f t="shared" si="76"/>
         <v>6971.6133014246934</v>
       </c>
     </row>
@@ -4695,40 +5193,40 @@
         <v>138552</v>
       </c>
       <c r="D71" s="25">
-        <f t="shared" ref="D71:L71" si="74">SUM(D63:D70)</f>
+        <f t="shared" ref="D71:L71" si="77">SUM(D63:D70)</f>
         <v>137100</v>
       </c>
       <c r="E71" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>137012</v>
       </c>
       <c r="F71" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>156363</v>
       </c>
       <c r="G71" s="26">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>168235</v>
       </c>
       <c r="H71" s="71">
-        <f t="shared" si="74"/>
-        <v>179739.20737153848</v>
+        <f t="shared" si="77"/>
+        <v>171527.43617041604</v>
       </c>
       <c r="I71" s="71">
-        <f t="shared" si="74"/>
-        <v>191276.05199231484</v>
+        <f t="shared" si="77"/>
+        <v>172253.49870751324</v>
       </c>
       <c r="J71" s="71">
-        <f t="shared" si="74"/>
-        <v>196969.84132043214</v>
+        <f t="shared" si="77"/>
+        <v>170178.99092498468</v>
       </c>
       <c r="K71" s="71">
-        <f t="shared" si="74"/>
-        <v>221671.61183885488</v>
+        <f t="shared" si="77"/>
+        <v>176546.97311935844</v>
       </c>
       <c r="L71" s="71">
-        <f t="shared" si="74"/>
-        <v>238184.14295168009</v>
+        <f t="shared" si="77"/>
+        <v>179565.16724728831</v>
       </c>
     </row>
     <row r="72" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -4755,19 +5253,19 @@
         <v>15078.897350071435</v>
       </c>
       <c r="I72" s="46">
-        <f t="shared" ref="I72:L72" si="75">(I21/365) *I32</f>
+        <f t="shared" ref="I72:L72" si="78">(I21/365) *I32</f>
         <v>16714.962279726053</v>
       </c>
       <c r="J72" s="46">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>18161.47747553642</v>
       </c>
       <c r="K72" s="46">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>20717.922819342733</v>
       </c>
       <c r="L72" s="46">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>22827.393964684325</v>
       </c>
     </row>
@@ -4795,19 +5293,19 @@
         <v>29712.493453188981</v>
       </c>
       <c r="I73" s="42">
-        <f t="shared" ref="I73:L73" si="76">H73*(1+I4)</f>
+        <f t="shared" ref="I73:L73" si="79">H73*(1+I4)</f>
         <v>32718.748129089839</v>
       </c>
       <c r="J73" s="42">
-        <f t="shared" si="76"/>
+        <f t="shared" si="79"/>
         <v>35502.891534216506</v>
       </c>
       <c r="K73" s="42">
-        <f t="shared" si="76"/>
+        <f t="shared" si="79"/>
         <v>40888.473449800644</v>
       </c>
       <c r="L73" s="42">
-        <f t="shared" si="76"/>
+        <f t="shared" si="79"/>
         <v>45299.630503703047</v>
       </c>
     </row>
@@ -4835,19 +5333,19 @@
         <v>65032.274459055974</v>
       </c>
       <c r="I74" s="42">
-        <f t="shared" ref="I74:L74" si="77">H74*(1+I4)</f>
+        <f t="shared" ref="I74:L74" si="80">H74*(1+I4)</f>
         <v>71612.118708244088</v>
       </c>
       <c r="J74" s="42">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>77705.823982115515</v>
       </c>
       <c r="K74" s="42">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>89493.345006151474</v>
       </c>
       <c r="L74" s="42">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>99148.124624810269</v>
       </c>
     </row>
@@ -4870,24 +5368,24 @@
       <c r="G75" s="18">
         <v>8461</v>
       </c>
-      <c r="H75" s="112">
+      <c r="H75" s="105">
         <f>G75</f>
         <v>8461</v>
       </c>
-      <c r="I75" s="113">
+      <c r="I75" s="106">
         <f>H75</f>
         <v>8461</v>
       </c>
-      <c r="J75" s="113">
-        <f t="shared" ref="J75:L75" si="78">I75</f>
+      <c r="J75" s="106">
+        <f t="shared" ref="J75:L75" si="81">I75</f>
         <v>8461</v>
       </c>
-      <c r="K75" s="113">
-        <f t="shared" si="78"/>
+      <c r="K75" s="106">
+        <f t="shared" si="81"/>
         <v>8461</v>
       </c>
-      <c r="L75" s="113">
-        <f t="shared" si="78"/>
+      <c r="L75" s="106">
+        <f t="shared" si="81"/>
         <v>8461</v>
       </c>
     </row>
@@ -4896,19 +5394,19 @@
         <v>23</v>
       </c>
       <c r="C76" s="7">
-        <f t="shared" ref="C76:F76" si="79">SUM(C72:C75)</f>
+        <f t="shared" ref="C76:F76" si="82">SUM(C72:C75)</f>
         <v>81992</v>
       </c>
       <c r="D76" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>90052</v>
       </c>
       <c r="E76" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>95827</v>
       </c>
       <c r="F76" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>97078</v>
       </c>
       <c r="G76" s="7">
@@ -4916,23 +5414,23 @@
         <v>108115</v>
       </c>
       <c r="H76" s="97">
-        <f t="shared" ref="H76:L76" si="80">SUM(H72:H75)</f>
+        <f t="shared" ref="H76:L76" si="83">SUM(H72:H75)</f>
         <v>118284.66526231638</v>
       </c>
       <c r="I76" s="71">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>129506.82911705998</v>
       </c>
       <c r="J76" s="71">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>139831.19299186845</v>
       </c>
       <c r="K76" s="71">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>159560.74127529486</v>
       </c>
       <c r="L76" s="71">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>175736.14909319766</v>
       </c>
     </row>
@@ -4955,24 +5453,24 @@
       <c r="G77" s="18">
         <v>216</v>
       </c>
-      <c r="H77" s="102">
+      <c r="H77" s="67">
         <f>AVERAGE(C77:G77)</f>
         <v>203</v>
       </c>
-      <c r="I77" s="106">
-        <f t="shared" ref="I77:L77" si="81">AVERAGE(D77:H77)</f>
+      <c r="I77" s="68">
+        <f t="shared" ref="I77:L77" si="84">AVERAGE(D77:H77)</f>
         <v>200</v>
       </c>
-      <c r="J77" s="106">
-        <f t="shared" si="81"/>
+      <c r="J77" s="68">
+        <f t="shared" si="84"/>
         <v>194</v>
       </c>
-      <c r="K77" s="106">
-        <f t="shared" si="81"/>
+      <c r="K77" s="68">
+        <f t="shared" si="84"/>
         <v>187</v>
       </c>
-      <c r="L77" s="106">
-        <f t="shared" si="81"/>
+      <c r="L77" s="68">
+        <f t="shared" si="84"/>
         <v>200</v>
       </c>
     </row>
@@ -4995,7 +5493,7 @@
       <c r="G78" s="18">
         <v>2091</v>
       </c>
-      <c r="H78" s="103">
+      <c r="H78" s="99">
         <v>1900</v>
       </c>
       <c r="I78" s="18">
@@ -5030,7 +5528,7 @@
       <c r="G79" s="18">
         <v>4287</v>
       </c>
-      <c r="H79" s="103">
+      <c r="H79" s="99">
         <v>3990</v>
       </c>
       <c r="I79" s="18">
@@ -5065,24 +5563,24 @@
       <c r="G80" s="18">
         <v>2432</v>
       </c>
-      <c r="H80" s="102">
+      <c r="H80" s="67">
         <f>G80</f>
         <v>2432</v>
       </c>
-      <c r="I80" s="106">
+      <c r="I80" s="68">
         <f>H80</f>
         <v>2432</v>
       </c>
-      <c r="J80" s="106">
-        <f t="shared" ref="J80:L80" si="82">I80</f>
+      <c r="J80" s="68">
+        <f t="shared" ref="J80:L80" si="85">I80</f>
         <v>2432</v>
       </c>
-      <c r="K80" s="106">
-        <f t="shared" si="82"/>
+      <c r="K80" s="68">
+        <f t="shared" si="85"/>
         <v>2432</v>
       </c>
-      <c r="L80" s="106">
-        <f t="shared" si="82"/>
+      <c r="L80" s="68">
+        <f t="shared" si="85"/>
         <v>2432</v>
       </c>
     </row>
@@ -5105,24 +5603,24 @@
       <c r="G81" s="18">
         <v>45637</v>
       </c>
-      <c r="H81" s="102">
+      <c r="H81" s="67">
         <f>G81</f>
         <v>45637</v>
       </c>
-      <c r="I81" s="106">
+      <c r="I81" s="68">
         <f>H81</f>
         <v>45637</v>
       </c>
-      <c r="J81" s="106">
-        <f t="shared" ref="J81:L81" si="83">I81</f>
+      <c r="J81" s="68">
+        <f t="shared" ref="J81:L81" si="86">I81</f>
         <v>45637</v>
       </c>
-      <c r="K81" s="106">
-        <f t="shared" si="83"/>
+      <c r="K81" s="68">
+        <f t="shared" si="86"/>
         <v>45637</v>
       </c>
-      <c r="L81" s="106">
-        <f t="shared" si="83"/>
+      <c r="L81" s="68">
+        <f t="shared" si="86"/>
         <v>45637</v>
       </c>
     </row>
@@ -5131,15 +5629,15 @@
         <v>22</v>
       </c>
       <c r="C82" s="25">
-        <f t="shared" ref="C82:E82" si="84">SUM(C76:C81)</f>
+        <f t="shared" ref="C82:E82" si="87">SUM(C76:C81)</f>
         <v>153398</v>
       </c>
       <c r="D82" s="25">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>152948</v>
       </c>
       <c r="E82" s="25">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>154240</v>
       </c>
       <c r="F82" s="25">
@@ -5151,23 +5649,23 @@
         <v>162778</v>
       </c>
       <c r="H82" s="25">
-        <f t="shared" ref="H82:L82" si="85">SUM(H76:H81)</f>
+        <f t="shared" ref="H82:L82" si="88">SUM(H76:H81)</f>
         <v>172446.66526231638</v>
       </c>
       <c r="I82" s="25">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>183165.82911706</v>
       </c>
       <c r="J82" s="25">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>192984.19299186845</v>
       </c>
       <c r="K82" s="25">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>212206.74127529486</v>
       </c>
       <c r="L82" s="25">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>227895.14909319766</v>
       </c>
     </row>
@@ -5190,7 +5688,7 @@
       <c r="G83" s="18">
         <v>5061</v>
       </c>
-      <c r="H83" s="114">
+      <c r="H83" s="107">
         <f>G83</f>
         <v>5061</v>
       </c>
@@ -5199,15 +5697,15 @@
         <v>5061</v>
       </c>
       <c r="J83" s="5">
-        <f t="shared" ref="J83:L83" si="86">I83</f>
+        <f t="shared" ref="J83:L83" si="89">I83</f>
         <v>5061</v>
       </c>
       <c r="K83" s="5">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>5061</v>
       </c>
       <c r="L83" s="5">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>5061</v>
       </c>
     </row>
@@ -5230,24 +5728,24 @@
       <c r="G84" s="5">
         <v>21441</v>
       </c>
-      <c r="H84" s="102">
+      <c r="H84" s="67">
         <f>G84+H97</f>
         <v>22057.200000000001</v>
       </c>
-      <c r="I84" s="120">
-        <f t="shared" ref="I84:L84" si="87">H84+I97</f>
+      <c r="I84" s="68">
+        <f t="shared" ref="I84:L84" si="90">H84+I97</f>
         <v>22630.04</v>
       </c>
-      <c r="J84" s="120">
-        <f t="shared" si="87"/>
+      <c r="J84" s="68">
+        <f t="shared" si="90"/>
         <v>23172.448</v>
       </c>
-      <c r="K84" s="120">
-        <f t="shared" si="87"/>
+      <c r="K84" s="68">
+        <f t="shared" si="90"/>
         <v>23685.337599999999</v>
       </c>
-      <c r="L84" s="120">
-        <f t="shared" si="87"/>
+      <c r="L84" s="68">
+        <f t="shared" si="90"/>
         <v>24219.405119999999</v>
       </c>
     </row>
@@ -5270,24 +5768,24 @@
       <c r="G85" s="5">
         <v>-28029</v>
       </c>
-      <c r="H85" s="102">
+      <c r="H85" s="67">
         <f>G85+H98</f>
         <v>-26610.2</v>
       </c>
-      <c r="I85" s="120">
-        <f t="shared" ref="I85:L85" si="88">H85+I98</f>
+      <c r="I85" s="68">
+        <f t="shared" ref="I85:L85" si="91">H85+I98</f>
         <v>-25154.240000000002</v>
       </c>
-      <c r="J85" s="120">
-        <f t="shared" si="88"/>
+      <c r="J85" s="68">
+        <f t="shared" si="91"/>
         <v>-23650.088000000003</v>
       </c>
-      <c r="K85" s="120">
-        <f t="shared" si="88"/>
+      <c r="K85" s="68">
+        <f t="shared" si="91"/>
         <v>-22148.105600000003</v>
       </c>
-      <c r="L85" s="120">
-        <f t="shared" si="88"/>
+      <c r="L85" s="68">
+        <f t="shared" si="91"/>
         <v>-20665.926720000003</v>
       </c>
     </row>
@@ -5310,25 +5808,25 @@
       <c r="G86" s="5">
         <v>17252</v>
       </c>
-      <c r="H86" s="102">
+      <c r="H86" s="67">
         <f>G86+H45</f>
-        <v>13546.523860264821</v>
-      </c>
-      <c r="I86" s="106">
-        <f t="shared" ref="I86:L86" si="89">H86+I45</f>
-        <v>9358.0859172370947</v>
-      </c>
-      <c r="J86" s="106">
-        <f t="shared" si="89"/>
-        <v>4713.420507726918</v>
-      </c>
-      <c r="K86" s="106">
-        <f t="shared" si="89"/>
-        <v>-765.69302046520534</v>
-      </c>
-      <c r="L86" s="106">
-        <f t="shared" si="89"/>
-        <v>-6944.1366686324491</v>
+        <v>11426.4180561793</v>
+      </c>
+      <c r="I86" s="68">
+        <f t="shared" ref="I86:L86" si="92">H86+I45</f>
+        <v>5080.880799501997</v>
+      </c>
+      <c r="J86" s="68">
+        <f t="shared" si="92"/>
+        <v>-1719.2163159198799</v>
+      </c>
+      <c r="K86" s="68">
+        <f t="shared" si="92"/>
+        <v>-9342.5421186609383</v>
+      </c>
+      <c r="L86" s="68">
+        <f t="shared" si="92"/>
+        <v>-17673.233531531587</v>
       </c>
     </row>
     <row r="87" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -5359,15 +5857,15 @@
         <v>-10277</v>
       </c>
       <c r="J87" s="5">
-        <f t="shared" ref="J87:L87" si="90">H87</f>
+        <f t="shared" ref="J87:L87" si="93">H87</f>
         <v>-10277</v>
       </c>
       <c r="K87" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>-10277</v>
       </c>
       <c r="L87" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>-10277</v>
       </c>
     </row>
@@ -5396,24 +5894,24 @@
         <v>5448</v>
       </c>
       <c r="H88" s="7">
-        <f t="shared" ref="H88:L88" si="91">SUM(H83:H87)</f>
-        <v>3777.5238602648205</v>
+        <f t="shared" ref="H88:L88" si="94">SUM(H83:H87)</f>
+        <v>1657.4180561793</v>
       </c>
       <c r="I88" s="7">
-        <f t="shared" si="91"/>
-        <v>1617.885917237094</v>
+        <f t="shared" si="94"/>
+        <v>-2659.3192004980037</v>
       </c>
       <c r="J88" s="7">
-        <f t="shared" si="91"/>
-        <v>-980.21949227308505</v>
+        <f t="shared" si="94"/>
+        <v>-7412.8563159198829</v>
       </c>
       <c r="K88" s="7">
-        <f t="shared" si="91"/>
-        <v>-4444.461020465209</v>
+        <f t="shared" si="94"/>
+        <v>-13021.310118660942</v>
       </c>
       <c r="L88" s="7">
-        <f t="shared" si="91"/>
-        <v>-8606.6582686324527</v>
+        <f t="shared" si="94"/>
+        <v>-19335.75513153159</v>
       </c>
     </row>
     <row r="89" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -5435,7 +5933,7 @@
       <c r="G89" s="5">
         <v>6</v>
       </c>
-      <c r="H89" s="102">
+      <c r="H89" s="67">
         <f>G89</f>
         <v>6</v>
       </c>
@@ -5471,7 +5969,7 @@
       <c r="G90" s="18">
         <v>3</v>
       </c>
-      <c r="H90" s="112">
+      <c r="H90" s="105">
         <f>G90</f>
         <v>3</v>
       </c>
@@ -5480,15 +5978,15 @@
         <v>3</v>
       </c>
       <c r="J90" s="18">
-        <f t="shared" ref="J90:L90" si="92">I90</f>
+        <f t="shared" ref="J90:L90" si="95">I90</f>
         <v>3</v>
       </c>
       <c r="K90" s="18">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>3</v>
       </c>
       <c r="L90" s="18">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>3</v>
       </c>
     </row>
@@ -5501,40 +5999,40 @@
         <v>-14846</v>
       </c>
       <c r="D91" s="25">
-        <f t="shared" ref="D91:L91" si="93">SUM(D88:D90)</f>
+        <f t="shared" ref="D91:L91" si="96">SUM(D88:D90)</f>
         <v>-15848</v>
       </c>
       <c r="E91" s="25">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>-17228</v>
       </c>
       <c r="F91" s="25">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>-3914</v>
       </c>
       <c r="G91" s="29">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>5457</v>
       </c>
       <c r="H91" s="7">
-        <f t="shared" si="93"/>
-        <v>3786.5238602648205</v>
+        <f t="shared" si="96"/>
+        <v>1666.4180561793</v>
       </c>
       <c r="I91" s="7">
-        <f t="shared" si="93"/>
-        <v>1620.885917237094</v>
+        <f t="shared" si="96"/>
+        <v>-2656.3192004980037</v>
       </c>
       <c r="J91" s="7">
-        <f t="shared" si="93"/>
-        <v>-977.21949227308505</v>
+        <f t="shared" si="96"/>
+        <v>-7409.8563159198829</v>
       </c>
       <c r="K91" s="7">
-        <f t="shared" si="93"/>
-        <v>-4441.461020465209</v>
+        <f t="shared" si="96"/>
+        <v>-13018.310118660942</v>
       </c>
       <c r="L91" s="7">
-        <f t="shared" si="93"/>
-        <v>-8603.6582686324527</v>
+        <f t="shared" si="96"/>
+        <v>-19332.75513153159</v>
       </c>
     </row>
     <row r="92" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -5542,44 +6040,44 @@
         <v>44</v>
       </c>
       <c r="C92" s="13">
-        <f>SUM(C82+C91)</f>
+        <f t="shared" ref="C92:H92" si="97">SUM(C82+C91)</f>
         <v>138552</v>
       </c>
       <c r="D92" s="13">
-        <f>SUM(D82+D91)</f>
+        <f t="shared" si="97"/>
         <v>137100</v>
       </c>
       <c r="E92" s="13">
-        <f>SUM(E82+E91)</f>
+        <f t="shared" si="97"/>
         <v>137012</v>
       </c>
       <c r="F92" s="13">
-        <f>SUM(F82+F91)</f>
+        <f t="shared" si="97"/>
         <v>156363</v>
       </c>
       <c r="G92" s="13">
-        <f>SUM(G82+G91)</f>
+        <f t="shared" si="97"/>
         <v>168235</v>
       </c>
       <c r="H92" s="75">
-        <f t="shared" ref="H92:L92" si="94">SUM(H82+H91)</f>
-        <v>176233.18912258121</v>
+        <f t="shared" si="97"/>
+        <v>174113.08331849569</v>
       </c>
       <c r="I92" s="13">
-        <f t="shared" si="94"/>
-        <v>184786.71503429709</v>
+        <f t="shared" ref="I92:L92" si="98">SUM(I82+I91)</f>
+        <v>180509.509916562</v>
       </c>
       <c r="J92" s="13">
-        <f t="shared" si="94"/>
-        <v>192006.97349959536</v>
+        <f t="shared" si="98"/>
+        <v>185574.33667594855</v>
       </c>
       <c r="K92" s="13">
-        <f t="shared" si="94"/>
-        <v>207765.28025482965</v>
+        <f t="shared" si="98"/>
+        <v>199188.43115663392</v>
       </c>
       <c r="L92" s="13">
-        <f t="shared" si="94"/>
-        <v>219291.4908245652</v>
+        <f t="shared" si="98"/>
+        <v>208562.39396166606</v>
       </c>
     </row>
     <row r="93" spans="2:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.3">
@@ -5591,44 +6089,49 @@
         <v>✓</v>
       </c>
       <c r="D93" s="39" t="str">
-        <f t="shared" ref="D93:L93" si="95">IF(D92=D71, "✓", "✗")</f>
+        <f t="shared" ref="D93:L93" si="99">IF(D92=D71, "✓", "✗")</f>
         <v>✓</v>
       </c>
       <c r="E93" s="39" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>✓</v>
       </c>
       <c r="F93" s="39" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>✓</v>
       </c>
       <c r="G93" s="39" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>✓</v>
       </c>
-      <c r="H93" s="39" t="str">
-        <f t="shared" si="95"/>
+      <c r="H93" s="113" t="str">
+        <f t="shared" si="99"/>
         <v>✗</v>
       </c>
-      <c r="I93" s="39" t="str">
-        <f t="shared" si="95"/>
+      <c r="I93" s="113" t="str">
+        <f t="shared" si="99"/>
         <v>✗</v>
       </c>
-      <c r="J93" s="39" t="str">
-        <f t="shared" si="95"/>
+      <c r="J93" s="113" t="str">
+        <f t="shared" si="99"/>
         <v>✗</v>
       </c>
-      <c r="K93" s="39" t="str">
-        <f t="shared" si="95"/>
+      <c r="K93" s="113" t="str">
+        <f t="shared" si="99"/>
         <v>✗</v>
       </c>
-      <c r="L93" s="39" t="str">
-        <f t="shared" si="95"/>
+      <c r="L93" s="113" t="str">
+        <f t="shared" si="99"/>
         <v>✗</v>
       </c>
     </row>
     <row r="94" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B94" s="10"/>
+      <c r="H94" s="110"/>
+      <c r="I94" s="110"/>
+      <c r="J94" s="110"/>
+      <c r="K94" s="110"/>
+      <c r="L94" s="110"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
@@ -5638,15 +6141,15 @@
         <v>2021</v>
       </c>
       <c r="D95" s="2">
-        <f t="shared" ref="D95" si="96">+C95+1</f>
+        <f t="shared" ref="D95" si="100">+C95+1</f>
         <v>2022</v>
       </c>
       <c r="E95" s="2">
-        <f t="shared" ref="E95" si="97">+D95+1</f>
+        <f t="shared" ref="E95" si="101">+D95+1</f>
         <v>2023</v>
       </c>
       <c r="F95" s="2">
-        <f t="shared" ref="F95" si="98">+E95+1</f>
+        <f t="shared" ref="F95" si="102">+E95+1</f>
         <v>2024</v>
       </c>
       <c r="G95" s="2">
@@ -5654,23 +6157,23 @@
         <v>2025</v>
       </c>
       <c r="H95" s="2">
-        <f t="shared" ref="H95" si="99">+G95+1</f>
+        <f t="shared" ref="H95" si="103">+G95+1</f>
         <v>2026</v>
       </c>
       <c r="I95" s="2">
-        <f t="shared" ref="I95" si="100">+H95+1</f>
+        <f t="shared" ref="I95" si="104">+H95+1</f>
         <v>2027</v>
       </c>
       <c r="J95" s="2">
-        <f t="shared" ref="J95" si="101">+I95+1</f>
+        <f t="shared" ref="J95" si="105">+I95+1</f>
         <v>2028</v>
       </c>
       <c r="K95" s="2">
-        <f t="shared" ref="K95" si="102">+J95+1</f>
+        <f t="shared" ref="K95" si="106">+J95+1</f>
         <v>2029</v>
       </c>
       <c r="L95" s="2">
-        <f t="shared" ref="L95" si="103">+K95+1</f>
+        <f t="shared" ref="L95" si="107">+K95+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -5699,24 +6202,24 @@
         <v>2238</v>
       </c>
       <c r="H96" s="20">
-        <f t="shared" ref="H96:L96" si="104">H45</f>
-        <v>-3705.476139735179</v>
+        <f t="shared" ref="H96:L96" si="108">H45</f>
+        <v>-5825.5819438207</v>
       </c>
       <c r="I96" s="5">
-        <f t="shared" si="104"/>
-        <v>-4188.4379430277259</v>
+        <f t="shared" si="108"/>
+        <v>-6345.537256677303</v>
       </c>
       <c r="J96" s="5">
-        <f t="shared" si="104"/>
-        <v>-4644.6654095101767</v>
+        <f t="shared" si="108"/>
+        <v>-6800.0971154218769</v>
       </c>
       <c r="K96" s="5">
-        <f t="shared" si="104"/>
-        <v>-5479.1135281921233</v>
+        <f t="shared" si="108"/>
+        <v>-7623.3258027410575</v>
       </c>
       <c r="L96" s="5">
-        <f t="shared" si="104"/>
-        <v>-6178.4436481672437</v>
+        <f t="shared" si="108"/>
+        <v>-8330.6914128706467</v>
       </c>
     </row>
     <row r="97" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -5738,24 +6241,24 @@
       <c r="G97" s="5">
         <v>426</v>
       </c>
-      <c r="H97" s="102">
+      <c r="H97" s="67">
         <f>AVERAGE(C97:G97)</f>
         <v>616.20000000000005</v>
       </c>
-      <c r="I97" s="120">
-        <f t="shared" ref="I97:L97" si="105">AVERAGE(D97:H97)</f>
+      <c r="I97" s="68">
+        <f t="shared" ref="I97:L97" si="109">AVERAGE(D97:H97)</f>
         <v>572.83999999999992</v>
       </c>
-      <c r="J97" s="120">
-        <f t="shared" si="105"/>
+      <c r="J97" s="68">
+        <f t="shared" si="109"/>
         <v>542.40800000000002</v>
       </c>
-      <c r="K97" s="120">
-        <f t="shared" si="105"/>
+      <c r="K97" s="68">
+        <f t="shared" si="109"/>
         <v>512.88959999999997</v>
       </c>
-      <c r="L97" s="120">
-        <f t="shared" si="105"/>
+      <c r="L97" s="68">
+        <f t="shared" si="109"/>
         <v>534.06751999999994</v>
       </c>
     </row>
@@ -5778,24 +6281,24 @@
       <c r="G98" s="5">
         <v>1530</v>
       </c>
-      <c r="H98" s="102">
+      <c r="H98" s="67">
         <f>AVERAGE(C98:G98)</f>
         <v>1418.8</v>
       </c>
-      <c r="I98" s="120">
-        <f t="shared" ref="I98:L98" si="106">AVERAGE(D98:H98)</f>
+      <c r="I98" s="68">
+        <f t="shared" ref="I98:L98" si="110">AVERAGE(D98:H98)</f>
         <v>1455.96</v>
       </c>
-      <c r="J98" s="120">
-        <f t="shared" si="106"/>
+      <c r="J98" s="68">
+        <f t="shared" si="110"/>
         <v>1504.152</v>
       </c>
-      <c r="K98" s="120">
-        <f t="shared" si="106"/>
+      <c r="K98" s="68">
+        <f t="shared" si="110"/>
         <v>1501.9824000000001</v>
       </c>
-      <c r="L98" s="120">
-        <f t="shared" si="106"/>
+      <c r="L98" s="68">
+        <f t="shared" si="110"/>
         <v>1482.1788799999999</v>
       </c>
     </row>
@@ -5818,25 +6321,25 @@
       <c r="G99" s="5">
         <v>1953</v>
       </c>
-      <c r="H99" s="102">
-        <f>AVERAGE(C99:G99)</f>
-        <v>1954.6</v>
-      </c>
-      <c r="I99" s="106">
-        <f t="shared" ref="I99:L99" si="107">AVERAGE(D99:H99)</f>
-        <v>1916.72</v>
-      </c>
-      <c r="J99" s="106">
-        <f t="shared" si="107"/>
-        <v>1904.2639999999999</v>
-      </c>
-      <c r="K99" s="106">
-        <f t="shared" si="107"/>
-        <v>1912.9168000000002</v>
-      </c>
-      <c r="L99" s="106">
-        <f t="shared" si="107"/>
-        <v>1928.30016</v>
+      <c r="H99" s="67">
+        <f>H17*H31</f>
+        <v>2394.7571016903594</v>
+      </c>
+      <c r="I99" s="68">
+        <f t="shared" ref="I99:L99" si="111">I17*I31</f>
+        <v>2656.0823993199037</v>
+      </c>
+      <c r="J99" s="68">
+        <f t="shared" si="111"/>
+        <v>2766.0826084191112</v>
+      </c>
+      <c r="K99" s="68">
+        <f t="shared" si="111"/>
+        <v>3266.8301190381508</v>
+      </c>
+      <c r="L99" s="68">
+        <f t="shared" si="111"/>
+        <v>3608.6713341028963</v>
       </c>
     </row>
     <row r="100" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -5858,7 +6361,21 @@
       <c r="G100" s="5">
         <v>45</v>
       </c>
-      <c r="H100" s="19"/>
+      <c r="H100" s="20">
+        <v>0</v>
+      </c>
+      <c r="I100" s="5">
+        <v>0</v>
+      </c>
+      <c r="J100" s="5">
+        <v>0</v>
+      </c>
+      <c r="K100" s="5">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B101" s="14" t="s">
@@ -5879,7 +6396,21 @@
       <c r="G101" s="5">
         <v>0</v>
       </c>
-      <c r="H101" s="19"/>
+      <c r="H101" s="20">
+        <v>0</v>
+      </c>
+      <c r="I101" s="5">
+        <v>0</v>
+      </c>
+      <c r="J101" s="5">
+        <v>0</v>
+      </c>
+      <c r="K101" s="5">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="102" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B102" s="16" t="s">
@@ -5900,7 +6431,21 @@
       <c r="G102" s="5">
         <v>-9672</v>
       </c>
-      <c r="H102" s="19"/>
+      <c r="H102" s="20">
+        <v>0</v>
+      </c>
+      <c r="I102" s="5">
+        <v>0</v>
+      </c>
+      <c r="J102" s="5">
+        <v>0</v>
+      </c>
+      <c r="K102" s="5">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="103" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B103" s="14" t="s">
@@ -5921,7 +6466,21 @@
       <c r="G103" s="5">
         <v>5283</v>
       </c>
-      <c r="H103" s="19"/>
+      <c r="H103" s="20">
+        <v>0</v>
+      </c>
+      <c r="I103" s="5">
+        <v>0</v>
+      </c>
+      <c r="J103" s="5">
+        <v>0</v>
+      </c>
+      <c r="K103" s="5">
+        <v>0</v>
+      </c>
+      <c r="L103" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="104" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B104" s="16" t="s">
@@ -5942,7 +6501,26 @@
       <c r="G104" s="5">
         <v>264</v>
       </c>
-      <c r="H104" s="19"/>
+      <c r="H104" s="111">
+        <f>AVERAGE(E104:G104)</f>
+        <v>265</v>
+      </c>
+      <c r="I104" s="112">
+        <f t="shared" ref="I104:L104" si="112">AVERAGE(F104:H104)</f>
+        <v>352.33333333333331</v>
+      </c>
+      <c r="J104" s="112">
+        <f t="shared" si="112"/>
+        <v>293.77777777777777</v>
+      </c>
+      <c r="K104" s="112">
+        <f t="shared" si="112"/>
+        <v>303.7037037037037</v>
+      </c>
+      <c r="L104" s="112">
+        <f t="shared" si="112"/>
+        <v>316.60493827160491</v>
+      </c>
     </row>
     <row r="105" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B105" s="31" t="s">
@@ -5953,6 +6531,11 @@
       <c r="E105" s="27"/>
       <c r="F105" s="27"/>
       <c r="G105" s="32"/>
+      <c r="H105" s="110"/>
+      <c r="I105" s="110"/>
+      <c r="J105" s="110"/>
+      <c r="K105" s="110"/>
+      <c r="L105" s="110"/>
     </row>
     <row r="106" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B106" s="14" t="s">
@@ -5970,8 +6553,28 @@
       <c r="F106" s="18">
         <v>-37</v>
       </c>
-      <c r="G106" s="33">
+      <c r="G106" s="18">
         <v>-95</v>
+      </c>
+      <c r="H106" s="67">
+        <f>-(H58-G58)</f>
+        <v>-731.05758357158311</v>
+      </c>
+      <c r="I106" s="68">
+        <f t="shared" ref="I106:L106" si="113">-(I58-H58)</f>
+        <v>-259.24041666933135</v>
+      </c>
+      <c r="J106" s="68">
+        <f t="shared" si="113"/>
+        <v>-297.20994529158315</v>
+      </c>
+      <c r="K106" s="68">
+        <f t="shared" si="113"/>
+        <v>-689.91223698797148</v>
+      </c>
+      <c r="L106" s="68">
+        <f t="shared" si="113"/>
+        <v>-432.61041966014454</v>
       </c>
     </row>
     <row r="107" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -5990,8 +6593,28 @@
       <c r="F107" s="18">
         <v>-60</v>
       </c>
-      <c r="G107" s="33">
+      <c r="G107" s="18">
         <v>-677</v>
+      </c>
+      <c r="H107" s="67">
+        <f>-(H59-G59)</f>
+        <v>539.60000000000036</v>
+      </c>
+      <c r="I107" s="68">
+        <f t="shared" ref="I107:L107" si="114">-(I59-H59)</f>
+        <v>0.31999999999970896</v>
+      </c>
+      <c r="J107" s="68">
+        <f t="shared" si="114"/>
+        <v>3.183999999999287</v>
+      </c>
+      <c r="K107" s="68">
+        <f t="shared" si="114"/>
+        <v>-59.579200000000128</v>
+      </c>
+      <c r="L107" s="68">
+        <f t="shared" si="114"/>
+        <v>-62.295040000000881</v>
       </c>
     </row>
     <row r="108" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -6010,8 +6633,28 @@
       <c r="F108" s="18">
         <v>4069</v>
       </c>
-      <c r="G108" s="33">
+      <c r="G108" s="18">
         <v>-723</v>
+      </c>
+      <c r="H108" s="67">
+        <f>H74-G74</f>
+        <v>5628.2744590559741</v>
+      </c>
+      <c r="I108" s="68">
+        <f t="shared" ref="I108:L108" si="115">I74-H74</f>
+        <v>6579.8442491881142</v>
+      </c>
+      <c r="J108" s="68">
+        <f t="shared" si="115"/>
+        <v>6093.7052738714265</v>
+      </c>
+      <c r="K108" s="68">
+        <f t="shared" si="115"/>
+        <v>11787.521024035959</v>
+      </c>
+      <c r="L108" s="68">
+        <f t="shared" si="115"/>
+        <v>9654.7796186587948</v>
       </c>
     </row>
     <row r="109" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -6033,6 +6676,26 @@
       <c r="G109" s="33">
         <v>-1501</v>
       </c>
+      <c r="H109" s="68">
+        <f>(G61-H61)</f>
+        <v>-21313.187045630271</v>
+      </c>
+      <c r="I109" s="68">
+        <f t="shared" ref="I109:L109" si="116">(H61-I61)</f>
+        <v>-10679.632875471914</v>
+      </c>
+      <c r="J109" s="68">
+        <f t="shared" si="116"/>
+        <v>-4666.7334587105288</v>
+      </c>
+      <c r="K109" s="68">
+        <f t="shared" si="116"/>
+        <v>-22464.436744028062</v>
+      </c>
+      <c r="L109" s="68">
+        <f t="shared" si="116"/>
+        <v>-14754.275663420442</v>
+      </c>
     </row>
     <row r="110" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B110" s="14" t="s">
@@ -6053,6 +6716,26 @@
       <c r="G110" s="33">
         <v>155</v>
       </c>
+      <c r="H110" s="68">
+        <f>(G62-H62)</f>
+        <v>-218.00989041626508</v>
+      </c>
+      <c r="I110" s="68">
+        <f t="shared" ref="I110:L110" si="117">(H62-I62)</f>
+        <v>-254.86872293754368</v>
+      </c>
+      <c r="J110" s="68">
+        <f t="shared" si="117"/>
+        <v>-236.03824380813012</v>
+      </c>
+      <c r="K110" s="68">
+        <f t="shared" si="117"/>
+        <v>-456.58686075528158</v>
+      </c>
+      <c r="L110" s="68">
+        <f t="shared" si="117"/>
+        <v>-373.97562289633515</v>
+      </c>
     </row>
     <row r="111" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B111" s="14" t="s">
@@ -6073,6 +6756,26 @@
       <c r="G111" s="33">
         <v>724</v>
       </c>
+      <c r="H111" s="68">
+        <f>(H72-G72)</f>
+        <v>1969.8973500714346</v>
+      </c>
+      <c r="I111" s="68">
+        <f>(I72-H72)</f>
+        <v>1636.064929654618</v>
+      </c>
+      <c r="J111" s="68">
+        <f t="shared" ref="J111:L111" si="118">(J72-I72)</f>
+        <v>1446.515195810367</v>
+      </c>
+      <c r="K111" s="68">
+        <f t="shared" si="118"/>
+        <v>2556.4453438063138</v>
+      </c>
+      <c r="L111" s="68">
+        <f t="shared" si="118"/>
+        <v>2109.4711453415912</v>
+      </c>
     </row>
     <row r="112" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B112" s="14" t="s">
@@ -6093,6 +6796,26 @@
       <c r="G112" s="33">
         <v>1341</v>
       </c>
+      <c r="H112" s="68">
+        <f>H73-G73</f>
+        <v>2571.4934531889812</v>
+      </c>
+      <c r="I112" s="68">
+        <f t="shared" ref="I112:L112" si="119">I73-H73</f>
+        <v>3006.2546759008583</v>
+      </c>
+      <c r="J112" s="68">
+        <f t="shared" si="119"/>
+        <v>2784.143405126666</v>
+      </c>
+      <c r="K112" s="68">
+        <f t="shared" si="119"/>
+        <v>5385.5819155841382</v>
+      </c>
+      <c r="L112" s="68">
+        <f t="shared" si="119"/>
+        <v>4411.1570539024033</v>
+      </c>
     </row>
     <row r="113" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B113" s="14" t="s">
@@ -6110,8 +6833,28 @@
       <c r="F113" s="18">
         <v>-567</v>
       </c>
-      <c r="G113" s="33">
+      <c r="G113" s="18">
         <v>115</v>
+      </c>
+      <c r="H113" s="67">
+        <f>H68-G68</f>
+        <v>0</v>
+      </c>
+      <c r="I113" s="68">
+        <f t="shared" ref="I113:L113" si="120">I68-H68</f>
+        <v>0</v>
+      </c>
+      <c r="J113" s="68">
+        <f t="shared" si="120"/>
+        <v>0</v>
+      </c>
+      <c r="K113" s="68">
+        <f t="shared" si="120"/>
+        <v>0</v>
+      </c>
+      <c r="L113" s="68">
+        <f t="shared" si="120"/>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -6133,6 +6876,26 @@
       <c r="G114" s="33">
         <v>-346</v>
       </c>
+      <c r="H114" s="68">
+        <f>H80-G80</f>
+        <v>0</v>
+      </c>
+      <c r="I114" s="68">
+        <f t="shared" ref="I114:L114" si="121">I80-H80</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="68">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
+      <c r="K114" s="68">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
+      <c r="L114" s="68">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="115" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B115" s="14" t="s">
@@ -6150,8 +6913,28 @@
       <c r="F115" s="18">
         <v>-959</v>
       </c>
-      <c r="G115" s="33">
+      <c r="G115" s="18">
         <v>-593</v>
+      </c>
+      <c r="H115" s="67">
+        <f>AVERAGE(E115:G115)</f>
+        <v>-867</v>
+      </c>
+      <c r="I115" s="68">
+        <f t="shared" ref="I115:L115" si="122">AVERAGE(F115:H115)</f>
+        <v>-806.33333333333337</v>
+      </c>
+      <c r="J115" s="68">
+        <f t="shared" si="122"/>
+        <v>-755.44444444444446</v>
+      </c>
+      <c r="K115" s="68">
+        <f t="shared" si="122"/>
+        <v>-809.59259259259261</v>
+      </c>
+      <c r="L115" s="68">
+        <f t="shared" si="122"/>
+        <v>-790.45679012345681</v>
       </c>
     </row>
     <row r="116" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -6173,6 +6956,26 @@
       <c r="G116" s="33">
         <v>274</v>
       </c>
+      <c r="H116" s="68">
+        <f>-(H64-G64)</f>
+        <v>50</v>
+      </c>
+      <c r="I116" s="68">
+        <f t="shared" ref="I116:L116" si="123">-(I64-H64)</f>
+        <v>50</v>
+      </c>
+      <c r="J116" s="68">
+        <f t="shared" si="123"/>
+        <v>50</v>
+      </c>
+      <c r="K116" s="68">
+        <f t="shared" si="123"/>
+        <v>50</v>
+      </c>
+      <c r="L116" s="68">
+        <f t="shared" si="123"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="117" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B117" s="14" t="s">
@@ -6193,6 +6996,26 @@
       <c r="G117" s="33">
         <v>324</v>
       </c>
+      <c r="H117" s="68">
+        <f>AVERAGE(E117:G117)</f>
+        <v>215</v>
+      </c>
+      <c r="I117" s="68">
+        <f t="shared" ref="I117:L117" si="124">AVERAGE(F117:H117)</f>
+        <v>247</v>
+      </c>
+      <c r="J117" s="68">
+        <f t="shared" si="124"/>
+        <v>262</v>
+      </c>
+      <c r="K117" s="68">
+        <f t="shared" si="124"/>
+        <v>241.33333333333334</v>
+      </c>
+      <c r="L117" s="68">
+        <f t="shared" si="124"/>
+        <v>250.11111111111111</v>
+      </c>
     </row>
     <row r="118" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B118" s="30" t="s">
@@ -6219,24 +7042,24 @@
         <v>1065</v>
       </c>
       <c r="H118" s="25">
-        <f t="shared" ref="H118:L118" si="108">SUM(H96:H117)</f>
-        <v>284.12386026482113</v>
+        <f t="shared" ref="H118:L118" si="125">SUM(H96:H117)</f>
+        <v>-13285.814099432071</v>
       </c>
       <c r="I118" s="25">
-        <f t="shared" si="108"/>
-        <v>-242.91794302772564</v>
+        <f t="shared" si="125"/>
+        <v>-1788.9130176925987</v>
       </c>
       <c r="J118" s="25">
-        <f t="shared" si="108"/>
-        <v>-693.84140951017639</v>
+        <f t="shared" si="125"/>
+        <v>2990.445053328785</v>
       </c>
       <c r="K118" s="25">
-        <f t="shared" si="108"/>
-        <v>-1551.3247281921228</v>
+        <f t="shared" si="125"/>
+        <v>-6497.1459976033684</v>
       </c>
       <c r="L118" s="25">
-        <f t="shared" si="108"/>
-        <v>-2233.897088167244</v>
+        <f t="shared" si="125"/>
+        <v>-2336.2633475826224</v>
       </c>
     </row>
     <row r="119" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -6258,24 +7081,24 @@
       <c r="G119" s="18">
         <v>-2942</v>
       </c>
-      <c r="H119" s="102">
+      <c r="H119" s="67">
         <f>AVERAGE(C119:G119)</f>
         <v>-1780.2</v>
       </c>
-      <c r="I119" s="106">
-        <f t="shared" ref="I119:L119" si="109">AVERAGE(D119:H119)</f>
+      <c r="I119" s="68">
+        <f t="shared" ref="I119:L119" si="126">AVERAGE(D119:H119)</f>
         <v>-1940.2400000000002</v>
       </c>
-      <c r="J119" s="106">
-        <f t="shared" si="109"/>
+      <c r="J119" s="68">
+        <f t="shared" si="126"/>
         <v>-2083.8879999999999</v>
       </c>
-      <c r="K119" s="106">
-        <f t="shared" si="109"/>
+      <c r="K119" s="68">
+        <f t="shared" si="126"/>
         <v>-2195.2656000000002</v>
       </c>
-      <c r="L119" s="106">
-        <f t="shared" si="109"/>
+      <c r="L119" s="68">
+        <f t="shared" si="126"/>
         <v>-2188.3187200000002</v>
       </c>
     </row>
@@ -6298,6 +7121,26 @@
       <c r="G120" s="33">
         <v>82</v>
       </c>
+      <c r="H120" s="68">
+        <f>AVERAGE(C120:G120)</f>
+        <v>144.4</v>
+      </c>
+      <c r="I120" s="68">
+        <f t="shared" ref="I120:L120" si="127">AVERAGE(F120:H120)</f>
+        <v>91.8</v>
+      </c>
+      <c r="J120" s="68">
+        <f t="shared" si="127"/>
+        <v>106.06666666666666</v>
+      </c>
+      <c r="K120" s="68">
+        <f t="shared" si="127"/>
+        <v>114.08888888888889</v>
+      </c>
+      <c r="L120" s="68">
+        <f t="shared" si="127"/>
+        <v>103.98518518518519</v>
+      </c>
     </row>
     <row r="121" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B121" s="14" t="s">
@@ -6318,6 +7161,21 @@
       <c r="G121" s="33">
         <v>-1248</v>
       </c>
+      <c r="H121" s="68">
+        <v>0</v>
+      </c>
+      <c r="I121" s="68">
+        <v>0</v>
+      </c>
+      <c r="J121" s="68">
+        <v>0</v>
+      </c>
+      <c r="K121" s="68">
+        <v>0</v>
+      </c>
+      <c r="L121" s="68">
+        <v>0</v>
+      </c>
     </row>
     <row r="122" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B122" s="14" t="s">
@@ -6338,6 +7196,21 @@
       <c r="G122" s="33">
         <v>10585</v>
       </c>
+      <c r="H122" s="68">
+        <v>0</v>
+      </c>
+      <c r="I122" s="68">
+        <v>0</v>
+      </c>
+      <c r="J122" s="68">
+        <v>0</v>
+      </c>
+      <c r="K122" s="68">
+        <v>0</v>
+      </c>
+      <c r="L122" s="68">
+        <v>0</v>
+      </c>
     </row>
     <row r="123" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B123" s="14" t="s">
@@ -6358,6 +7231,26 @@
       <c r="G123" s="33">
         <v>-51938</v>
       </c>
+      <c r="H123" s="68">
+        <f>AVERAGE(C123:G123)</f>
+        <v>-24601.200000000001</v>
+      </c>
+      <c r="I123" s="68">
+        <f t="shared" ref="I123:L123" si="128">AVERAGE(D123:H123)</f>
+        <v>-22378.84</v>
+      </c>
+      <c r="J123" s="68">
+        <f t="shared" si="128"/>
+        <v>-25844.407999999999</v>
+      </c>
+      <c r="K123" s="68">
+        <f t="shared" si="128"/>
+        <v>-27723.689600000002</v>
+      </c>
+      <c r="L123" s="68">
+        <f t="shared" si="128"/>
+        <v>-30497.227519999997</v>
+      </c>
     </row>
     <row r="124" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B124" s="14" t="s">
@@ -6378,6 +7271,26 @@
       <c r="G124" s="33">
         <v>46628</v>
       </c>
+      <c r="H124" s="68">
+        <f>AVERAGE(C124:G124)</f>
+        <v>24643.599999999999</v>
+      </c>
+      <c r="I124" s="68">
+        <f t="shared" ref="I124:L124" si="129">AVERAGE(D124:H124)</f>
+        <v>20474.52</v>
+      </c>
+      <c r="J124" s="68">
+        <f t="shared" si="129"/>
+        <v>22445.624000000003</v>
+      </c>
+      <c r="K124" s="68">
+        <f t="shared" si="129"/>
+        <v>23786.948800000002</v>
+      </c>
+      <c r="L124" s="68">
+        <f t="shared" si="129"/>
+        <v>27595.738560000005</v>
+      </c>
     </row>
     <row r="125" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B125" s="14" t="s">
@@ -6399,6 +7312,26 @@
       <c r="G125" s="33">
         <v>-662</v>
       </c>
+      <c r="H125" s="68">
+        <f>AVERAGE(E125:G125)</f>
+        <v>-506</v>
+      </c>
+      <c r="I125" s="68">
+        <f t="shared" ref="I125:L125" si="130">AVERAGE(F125:H125)</f>
+        <v>-620.66666666666663</v>
+      </c>
+      <c r="J125" s="68">
+        <f t="shared" si="130"/>
+        <v>-596.22222222222217</v>
+      </c>
+      <c r="K125" s="68">
+        <f t="shared" si="130"/>
+        <v>-574.29629629629619</v>
+      </c>
+      <c r="L125" s="68">
+        <f t="shared" si="130"/>
+        <v>-597.06172839506155</v>
+      </c>
     </row>
     <row r="126" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B126" s="14" t="s">
@@ -6417,6 +7350,21 @@
       <c r="G126" s="33">
         <v>2</v>
       </c>
+      <c r="H126" s="68">
+        <v>0</v>
+      </c>
+      <c r="I126" s="68">
+        <v>0</v>
+      </c>
+      <c r="J126" s="68">
+        <v>0</v>
+      </c>
+      <c r="K126" s="68">
+        <v>0</v>
+      </c>
+      <c r="L126" s="68">
+        <v>0</v>
+      </c>
     </row>
     <row r="127" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B127" s="16" t="s">
@@ -6435,6 +7383,21 @@
       <c r="G127" s="33">
         <v>-9</v>
       </c>
+      <c r="H127" s="68">
+        <v>0</v>
+      </c>
+      <c r="I127" s="68">
+        <v>0</v>
+      </c>
+      <c r="J127" s="68">
+        <v>0</v>
+      </c>
+      <c r="K127" s="68">
+        <v>0</v>
+      </c>
+      <c r="L127" s="68">
+        <v>0</v>
+      </c>
     </row>
     <row r="128" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B128" s="16" t="s">
@@ -6455,6 +7418,26 @@
       <c r="G128" s="35">
         <v>1</v>
       </c>
+      <c r="H128" s="68">
+        <f>AVERAGE(C128:G128)</f>
+        <v>-2.4</v>
+      </c>
+      <c r="I128" s="68">
+        <f t="shared" ref="I128:L128" si="131">AVERAGE(D128:H128)</f>
+        <v>-3.88</v>
+      </c>
+      <c r="J128" s="68">
+        <f t="shared" si="131"/>
+        <v>-2.4560000000000004</v>
+      </c>
+      <c r="K128" s="68">
+        <f t="shared" si="131"/>
+        <v>-3.7472000000000003</v>
+      </c>
+      <c r="L128" s="68">
+        <f t="shared" si="131"/>
+        <v>-2.29664</v>
+      </c>
     </row>
     <row r="129" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B129" s="30" t="s">
@@ -6465,20 +7448,40 @@
         <v>9324</v>
       </c>
       <c r="D129" s="25">
-        <f t="shared" ref="D129:G129" si="110">SUM(D119:D128)</f>
+        <f t="shared" ref="D129:L129" si="132">SUM(D119:D128)</f>
         <v>4370</v>
       </c>
       <c r="E129" s="25">
-        <f t="shared" si="110"/>
+        <f t="shared" si="132"/>
         <v>-2437</v>
       </c>
       <c r="F129" s="25">
-        <f t="shared" si="110"/>
+        <f t="shared" si="132"/>
         <v>-11973</v>
       </c>
       <c r="G129" s="26">
-        <f t="shared" si="110"/>
+        <f t="shared" si="132"/>
         <v>499</v>
+      </c>
+      <c r="H129" s="25">
+        <f t="shared" si="132"/>
+        <v>-2101.8000000000015</v>
+      </c>
+      <c r="I129" s="25">
+        <f t="shared" si="132"/>
+        <v>-4377.3066666666655</v>
+      </c>
+      <c r="J129" s="25">
+        <f t="shared" si="132"/>
+        <v>-5975.2835555555521</v>
+      </c>
+      <c r="K129" s="25">
+        <f t="shared" si="132"/>
+        <v>-6595.9610074074071</v>
+      </c>
+      <c r="L129" s="25">
+        <f t="shared" si="132"/>
+        <v>-5585.1808632098664</v>
       </c>
     </row>
     <row r="130" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
@@ -6500,6 +7503,26 @@
       <c r="G130" s="33">
         <v>165</v>
       </c>
+      <c r="H130" s="68">
+        <f>G130</f>
+        <v>165</v>
+      </c>
+      <c r="I130" s="68">
+        <f t="shared" ref="I130:L130" si="133">H130</f>
+        <v>165</v>
+      </c>
+      <c r="J130" s="68">
+        <f t="shared" si="133"/>
+        <v>165</v>
+      </c>
+      <c r="K130" s="68">
+        <f t="shared" si="133"/>
+        <v>165</v>
+      </c>
+      <c r="L130" s="68">
+        <f t="shared" si="133"/>
+        <v>165</v>
+      </c>
     </row>
     <row r="131" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B131" s="14" t="s">
@@ -6520,6 +7543,26 @@
       <c r="G131" s="33">
         <v>-3621</v>
       </c>
+      <c r="H131" s="68">
+        <f>G131</f>
+        <v>-3621</v>
+      </c>
+      <c r="I131" s="68">
+        <f t="shared" ref="I131:L131" si="134">H131</f>
+        <v>-3621</v>
+      </c>
+      <c r="J131" s="68">
+        <f t="shared" si="134"/>
+        <v>-3621</v>
+      </c>
+      <c r="K131" s="68">
+        <f t="shared" si="134"/>
+        <v>-3621</v>
+      </c>
+      <c r="L131" s="68">
+        <f t="shared" si="134"/>
+        <v>-3621</v>
+      </c>
     </row>
     <row r="132" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B132" s="14" t="s">
@@ -6540,6 +7583,21 @@
       <c r="G132" s="33">
         <v>0</v>
       </c>
+      <c r="H132" s="68">
+        <v>0</v>
+      </c>
+      <c r="I132" s="68">
+        <v>0</v>
+      </c>
+      <c r="J132" s="68">
+        <v>0</v>
+      </c>
+      <c r="K132" s="68">
+        <v>0</v>
+      </c>
+      <c r="L132" s="68">
+        <v>0</v>
+      </c>
     </row>
     <row r="133" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B133" s="14" t="s">
@@ -6560,6 +7618,21 @@
       <c r="G133" s="33">
         <v>0</v>
       </c>
+      <c r="H133" s="68">
+        <v>0</v>
+      </c>
+      <c r="I133" s="68">
+        <v>0</v>
+      </c>
+      <c r="J133" s="68">
+        <v>0</v>
+      </c>
+      <c r="K133" s="68">
+        <v>0</v>
+      </c>
+      <c r="L133" s="68">
+        <v>0</v>
+      </c>
     </row>
     <row r="134" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B134" s="16" t="s">
@@ -6580,6 +7653,26 @@
       <c r="G134" s="33">
         <v>0</v>
       </c>
+      <c r="H134" s="68">
+        <f>G134</f>
+        <v>0</v>
+      </c>
+      <c r="I134" s="68">
+        <f t="shared" ref="I134:L134" si="135">H134</f>
+        <v>0</v>
+      </c>
+      <c r="J134" s="68">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="K134" s="68">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="L134" s="68">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="135" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B135" s="16" t="s">
@@ -6600,6 +7693,26 @@
       <c r="G135" s="33">
         <v>-34</v>
       </c>
+      <c r="H135" s="68">
+        <f>AVERAGE(C135:G135)</f>
+        <v>-126.2</v>
+      </c>
+      <c r="I135" s="68">
+        <f t="shared" ref="I135:L135" si="136">AVERAGE(D135:H135)</f>
+        <v>-138.24</v>
+      </c>
+      <c r="J135" s="68">
+        <f t="shared" si="136"/>
+        <v>-157.88800000000001</v>
+      </c>
+      <c r="K135" s="68">
+        <f t="shared" si="136"/>
+        <v>-107.8656</v>
+      </c>
+      <c r="L135" s="68">
+        <f t="shared" si="136"/>
+        <v>-112.83872</v>
+      </c>
     </row>
     <row r="136" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B136" s="16" t="s">
@@ -6620,6 +7733,26 @@
       <c r="G136" s="33">
         <v>-331</v>
       </c>
+      <c r="H136" s="68">
+        <f>G136</f>
+        <v>-331</v>
+      </c>
+      <c r="I136" s="68">
+        <f t="shared" ref="I136:L137" si="137">H136</f>
+        <v>-331</v>
+      </c>
+      <c r="J136" s="68">
+        <f t="shared" si="137"/>
+        <v>-331</v>
+      </c>
+      <c r="K136" s="68">
+        <f t="shared" si="137"/>
+        <v>-331</v>
+      </c>
+      <c r="L136" s="68">
+        <f t="shared" si="137"/>
+        <v>-331</v>
+      </c>
     </row>
     <row r="137" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B137" s="16" t="s">
@@ -6640,21 +7773,41 @@
       <c r="G137" s="33">
         <v>58</v>
       </c>
+      <c r="H137" s="111">
+        <f>G137</f>
+        <v>58</v>
+      </c>
+      <c r="I137" s="68">
+        <f t="shared" si="137"/>
+        <v>58</v>
+      </c>
+      <c r="J137" s="68">
+        <f t="shared" si="137"/>
+        <v>58</v>
+      </c>
+      <c r="K137" s="68">
+        <f t="shared" si="137"/>
+        <v>58</v>
+      </c>
+      <c r="L137" s="68">
+        <f t="shared" si="137"/>
+        <v>58</v>
+      </c>
     </row>
     <row r="138" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B138" s="36" t="s">
         <v>58</v>
       </c>
       <c r="C138" s="25">
-        <f t="shared" ref="C138:E138" si="111">SUM(C130:C137)</f>
+        <f t="shared" ref="C138:E138" si="138">SUM(C130:C137)</f>
         <v>-5600</v>
       </c>
       <c r="D138" s="25">
-        <f t="shared" si="111"/>
+        <f t="shared" si="138"/>
         <v>-1266</v>
       </c>
       <c r="E138" s="25">
-        <f t="shared" si="111"/>
+        <f t="shared" si="138"/>
         <v>-5487</v>
       </c>
       <c r="F138" s="25">
@@ -6665,6 +7818,26 @@
         <f>SUM(G130:G137)</f>
         <v>-3763</v>
       </c>
+      <c r="H138" s="25">
+        <f t="shared" ref="H138:L138" si="139">SUM(H130:H137)</f>
+        <v>-3855.2</v>
+      </c>
+      <c r="I138" s="25">
+        <f t="shared" si="139"/>
+        <v>-3867.24</v>
+      </c>
+      <c r="J138" s="25">
+        <f t="shared" si="139"/>
+        <v>-3886.8879999999999</v>
+      </c>
+      <c r="K138" s="25">
+        <f t="shared" si="139"/>
+        <v>-3836.8656000000001</v>
+      </c>
+      <c r="L138" s="25">
+        <f t="shared" si="139"/>
+        <v>-3841.8387200000002</v>
+      </c>
     </row>
     <row r="139" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B139" s="16" t="s">
@@ -6685,6 +7858,26 @@
       <c r="G139" s="34">
         <v>40</v>
       </c>
+      <c r="H139" s="114">
+        <f>AVERAGE(C139:G139)</f>
+        <v>-17.8</v>
+      </c>
+      <c r="I139" s="70">
+        <f t="shared" ref="I139:L139" si="140">AVERAGE(D139:H139)</f>
+        <v>-13.559999999999999</v>
+      </c>
+      <c r="J139" s="70">
+        <f t="shared" si="140"/>
+        <v>-1.6719999999999999</v>
+      </c>
+      <c r="K139" s="70">
+        <f t="shared" si="140"/>
+        <v>-8.0063999999999993</v>
+      </c>
+      <c r="L139" s="70">
+        <f t="shared" si="140"/>
+        <v>-0.2076799999999997</v>
+      </c>
     </row>
     <row r="140" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B140" s="28" t="s">
@@ -6710,6 +7903,26 @@
         <f>SUM(G138,G129,G118,G139)</f>
         <v>-2159</v>
       </c>
+      <c r="H140" s="13">
+        <f t="shared" ref="H140:L140" si="141">SUM(H138,H129,H118,H139)</f>
+        <v>-19260.61409943207</v>
+      </c>
+      <c r="I140" s="13">
+        <f t="shared" si="141"/>
+        <v>-10047.019684359264</v>
+      </c>
+      <c r="J140" s="13">
+        <f t="shared" si="141"/>
+        <v>-6873.3985022267671</v>
+      </c>
+      <c r="K140" s="13">
+        <f t="shared" si="141"/>
+        <v>-16937.979005010773</v>
+      </c>
+      <c r="L140" s="13">
+        <f t="shared" si="141"/>
+        <v>-11763.490610792489</v>
+      </c>
     </row>
     <row r="141" spans="2:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B141" s="16" t="s">
@@ -6730,6 +7943,26 @@
       <c r="G141" s="33">
         <v>13822</v>
       </c>
+      <c r="H141" s="68">
+        <f>G142</f>
+        <v>11663</v>
+      </c>
+      <c r="I141" s="68">
+        <f t="shared" ref="I141:L141" si="142">H142</f>
+        <v>-7597.6140994320704</v>
+      </c>
+      <c r="J141" s="68">
+        <f t="shared" si="142"/>
+        <v>-17644.633783791334</v>
+      </c>
+      <c r="K141" s="68">
+        <f t="shared" si="142"/>
+        <v>-24518.0322860181</v>
+      </c>
+      <c r="L141" s="68">
+        <f t="shared" si="142"/>
+        <v>-41456.011291028874</v>
+      </c>
     </row>
     <row r="142" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B142" s="16" t="s">
@@ -6750,6 +7983,26 @@
       <c r="G142" s="33">
         <v>11663</v>
       </c>
+      <c r="H142" s="68">
+        <f>H141+H140</f>
+        <v>-7597.6140994320704</v>
+      </c>
+      <c r="I142" s="68">
+        <f t="shared" ref="I142:L142" si="143">I141+I140</f>
+        <v>-17644.633783791334</v>
+      </c>
+      <c r="J142" s="68">
+        <f t="shared" si="143"/>
+        <v>-24518.0322860181</v>
+      </c>
+      <c r="K142" s="68">
+        <f t="shared" si="143"/>
+        <v>-41456.011291028874</v>
+      </c>
+      <c r="L142" s="68">
+        <f t="shared" si="143"/>
+        <v>-53219.501901821364</v>
+      </c>
     </row>
     <row r="143" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B143" s="16" t="s">
@@ -6770,6 +8023,26 @@
       <c r="G143" s="33">
         <v>742</v>
       </c>
+      <c r="H143" s="111">
+        <f>AVERAGE(C143:G143)</f>
+        <v>174</v>
+      </c>
+      <c r="I143" s="68">
+        <f t="shared" ref="I143:L143" si="144">AVERAGE(D143:H143)</f>
+        <v>198.4</v>
+      </c>
+      <c r="J143" s="68">
+        <f t="shared" si="144"/>
+        <v>231.48000000000002</v>
+      </c>
+      <c r="K143" s="68">
+        <f t="shared" si="144"/>
+        <v>273.37600000000003</v>
+      </c>
+      <c r="L143" s="68">
+        <f t="shared" si="144"/>
+        <v>323.85120000000001</v>
+      </c>
     </row>
     <row r="144" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B144" s="28" t="s">
@@ -6795,11 +8068,26 @@
         <f>SUM(G142-G143)</f>
         <v>10921</v>
       </c>
-      <c r="H144" s="101"/>
-      <c r="I144" s="101"/>
-      <c r="J144" s="101"/>
-      <c r="K144" s="101"/>
-      <c r="L144" s="101"/>
+      <c r="H144" s="37">
+        <f t="shared" ref="H144:L144" si="145">SUM(H142-H143)</f>
+        <v>-7771.6140994320704</v>
+      </c>
+      <c r="I144" s="37">
+        <f t="shared" si="145"/>
+        <v>-17843.033783791336</v>
+      </c>
+      <c r="J144" s="37">
+        <f t="shared" si="145"/>
+        <v>-24749.5122860181</v>
+      </c>
+      <c r="K144" s="37">
+        <f t="shared" si="145"/>
+        <v>-41729.38729102887</v>
+      </c>
+      <c r="L144" s="37">
+        <f t="shared" si="145"/>
+        <v>-53543.353101821362</v>
+      </c>
     </row>
     <row r="145" spans="2:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B145" s="16" t="s">
@@ -6810,19 +8098,19 @@
         <v>✓</v>
       </c>
       <c r="D145" s="39" t="str">
-        <f t="shared" ref="D145:L145" si="112">IF(D144=D56, "✓", "✗")</f>
+        <f t="shared" ref="D145:L145" si="146">IF(D144=D56, "✓", "✗")</f>
         <v>✓</v>
       </c>
       <c r="E145" s="39" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="146"/>
         <v>✓</v>
       </c>
       <c r="F145" s="39" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="146"/>
         <v>✓</v>
       </c>
       <c r="G145" s="39" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="146"/>
         <v>✓</v>
       </c>
       <c r="H145" s="39" t="str">
@@ -6830,19 +8118,19 @@
         <v>✓</v>
       </c>
       <c r="I145" s="39" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="146"/>
         <v>✓</v>
       </c>
       <c r="J145" s="39" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="146"/>
         <v>✓</v>
       </c>
       <c r="K145" s="39" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="146"/>
         <v>✓</v>
       </c>
       <c r="L145" s="39" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="146"/>
         <v>✓</v>
       </c>
     </row>
@@ -6850,8 +8138,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C63 C118 H46 H41 H39 H52 H50" formulaRange="1"/>
+    <ignoredError sqref="C63 C118 H46 H41 H39 H52 H50 H104 H115:L115 H117:L117" formulaRange="1"/>
     <ignoredError sqref="H51 I51:L51" formula="1"/>
+    <ignoredError sqref="H116 I116:L116" formula="1" formulaRange="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/BA_Financial_Model_FY2021-FY2030E_Statement_v1.0.xlsx
+++ b/BA_Financial_Model_FY2021-FY2030E_Statement_v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5034C3-F7D2-4E92-9F4A-CA7C03182DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869FCCA9-F6D5-4CF3-8B62-6FE31FAB2E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{63A9B8CA-83BF-48D9-A8B6-530B504F47C6}"/>
   </bookViews>
@@ -1668,7 +1668,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="37" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1765,9 +1765,6 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2561,53 +2558,53 @@
     <row r="1" spans="2:8" s="55" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" s="55" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:8" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="119" t="s">
+      <c r="B3" s="118" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="118"/>
     </row>
     <row r="4" spans="2:8" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
     </row>
     <row r="5" spans="2:8" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
     </row>
     <row r="6" spans="2:8" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="119"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
     </row>
     <row r="7" spans="2:8" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="118" t="s">
+      <c r="B7" s="117" t="s">
         <v>127</v>
       </c>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
     </row>
     <row r="8" spans="2:8" s="53" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="54"/>
@@ -2619,25 +2616,25 @@
       <c r="H8" s="54"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="114" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115" t="s">
+      <c r="C10" s="114"/>
+      <c r="D10" s="114" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="115"/>
+      <c r="E10" s="114"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="115" t="s">
+      <c r="B11" s="114" t="s">
         <v>130</v>
       </c>
-      <c r="C11" s="115"/>
-      <c r="D11" s="116">
+      <c r="C11" s="114"/>
+      <c r="D11" s="115">
         <f ca="1">TODAY()</f>
         <v>46139</v>
       </c>
-      <c r="E11" s="117"/>
+      <c r="E11" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2664,51 +2661,51 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="80">
+      <c r="C2" s="79">
         <v>2021</v>
       </c>
-      <c r="D2" s="80">
+      <c r="D2" s="79">
         <f>+C2+1</f>
         <v>2022</v>
       </c>
-      <c r="E2" s="80">
+      <c r="E2" s="79">
         <f>+D2+1</f>
         <v>2023</v>
       </c>
-      <c r="F2" s="80">
+      <c r="F2" s="79">
         <f>+E2+1</f>
         <v>2024</v>
       </c>
-      <c r="G2" s="81">
+      <c r="G2" s="80">
         <f>+F2+1</f>
         <v>2025</v>
       </c>
-      <c r="H2" s="81">
+      <c r="H2" s="80">
         <f t="shared" ref="H2:L2" si="0">+G2+1</f>
         <v>2026</v>
       </c>
-      <c r="I2" s="81">
+      <c r="I2" s="80">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="J2" s="81">
+      <c r="J2" s="80">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="K2" s="81">
+      <c r="K2" s="80">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="L2" s="81">
+      <c r="L2" s="80">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="81" t="s">
         <v>91</v>
       </c>
       <c r="C3" s="22"/>
@@ -2716,10 +2713,10 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="23"/>
-      <c r="L3" s="83"/>
+      <c r="L3" s="82"/>
     </row>
     <row r="4" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B4" s="84" t="s">
+      <c r="B4" s="83" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="42">
@@ -2757,13 +2754,13 @@
         <f t="shared" si="2"/>
         <v>0.15169417708959537</v>
       </c>
-      <c r="L4" s="85">
+      <c r="L4" s="84">
         <f t="shared" si="2"/>
         <v>0.1078826544922996</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="81" t="s">
         <v>93</v>
       </c>
       <c r="C5" s="17"/>
@@ -2775,10 +2772,10 @@
       <c r="I5" s="43"/>
       <c r="J5" s="43"/>
       <c r="K5" s="43"/>
-      <c r="L5" s="86"/>
+      <c r="L5" s="85"/>
     </row>
     <row r="6" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="86" t="s">
         <v>94</v>
       </c>
       <c r="C6" s="43">
@@ -2817,13 +2814,13 @@
         <f t="shared" si="4"/>
         <v>4.7941607144853168E-2</v>
       </c>
-      <c r="L6" s="85">
+      <c r="L6" s="84">
         <f t="shared" si="4"/>
         <v>4.7941607144853189E-2</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="86" t="s">
         <v>95</v>
       </c>
       <c r="C7" s="43">
@@ -2862,13 +2859,13 @@
         <f t="shared" si="5"/>
         <v>0.95205839285514682</v>
       </c>
-      <c r="L7" s="86">
+      <c r="L7" s="85">
         <f t="shared" si="5"/>
         <v>0.95205839285514682</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B8" s="87" t="s">
+      <c r="B8" s="86" t="s">
         <v>97</v>
       </c>
       <c r="C8" s="43">
@@ -2907,13 +2904,13 @@
         <f t="shared" si="6"/>
         <v>6.8072834579658625E-2</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="85">
         <f t="shared" si="6"/>
         <v>6.8072834579658625E-2</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="86" t="s">
         <v>96</v>
       </c>
       <c r="C9" s="43">
@@ -2952,13 +2949,13 @@
         <f t="shared" si="7"/>
         <v>4.0407766339156971E-2</v>
       </c>
-      <c r="L9" s="86">
+      <c r="L9" s="85">
         <f t="shared" si="7"/>
         <v>4.0407766339156971E-2</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="86" t="s">
         <v>98</v>
       </c>
       <c r="C10" s="43">
@@ -2997,13 +2994,13 @@
         <f t="shared" si="8"/>
         <v>-6.0538993773962421E-2</v>
       </c>
-      <c r="L10" s="86">
+      <c r="L10" s="85">
         <f t="shared" si="8"/>
         <v>-6.0538993773962407E-2</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="86" t="s">
         <v>99</v>
       </c>
       <c r="C11" s="43">
@@ -3042,13 +3039,13 @@
         <f t="shared" si="10"/>
         <v>-5.6562158148381017E-2</v>
       </c>
-      <c r="L11" s="86">
+      <c r="L11" s="85">
         <f t="shared" si="10"/>
         <v>-5.5791594753644237E-2</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B12" s="82" t="s">
+      <c r="B12" s="81" t="s">
         <v>100</v>
       </c>
       <c r="C12" s="44"/>
@@ -3060,10 +3057,10 @@
       <c r="I12" s="43"/>
       <c r="J12" s="43"/>
       <c r="K12" s="43"/>
-      <c r="L12" s="86"/>
+      <c r="L12" s="85"/>
     </row>
     <row r="13" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B13" s="87" t="s">
+      <c r="B13" s="86" t="s">
         <v>101</v>
       </c>
       <c r="C13" s="42">
@@ -3094,12 +3091,12 @@
       <c r="K13" s="76">
         <v>0.21</v>
       </c>
-      <c r="L13" s="88">
+      <c r="L13" s="87">
         <v>0.21</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B14" s="82" t="s">
+      <c r="B14" s="81" t="s">
         <v>56</v>
       </c>
       <c r="C14" s="44"/>
@@ -3111,10 +3108,10 @@
       <c r="I14" s="43"/>
       <c r="J14" s="43"/>
       <c r="K14" s="43"/>
-      <c r="L14" s="86"/>
+      <c r="L14" s="85"/>
     </row>
     <row r="15" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="86" t="s">
         <v>102</v>
       </c>
       <c r="C15" s="43">
@@ -3137,14 +3134,29 @@
         <f t="shared" si="11"/>
         <v>-3.2885103338810458E-2</v>
       </c>
-      <c r="H15" s="58"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="85"/>
+      <c r="H15" s="58">
+        <f>H119/H31</f>
+        <v>-1.8176576358594709E-2</v>
+      </c>
+      <c r="I15" s="57">
+        <f t="shared" ref="I15:L15" si="12">I119/I31</f>
+        <v>-1.7990414217736513E-2</v>
+      </c>
+      <c r="J15" s="57">
+        <f t="shared" si="12"/>
+        <v>-1.7807093364195063E-2</v>
+      </c>
+      <c r="K15" s="57">
+        <f t="shared" si="12"/>
+        <v>-1.6288030087898663E-2</v>
+      </c>
+      <c r="L15" s="84">
+        <f t="shared" si="12"/>
+        <v>-1.4655421161012965E-2</v>
+      </c>
     </row>
     <row r="16" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="86" t="s">
         <v>103</v>
       </c>
       <c r="C16" s="43">
@@ -3152,29 +3164,44 @@
         <v>-8.9760029309397332E-2</v>
       </c>
       <c r="D16" s="43">
-        <f t="shared" ref="D16:G16" si="12">D119/D65</f>
+        <f t="shared" ref="D16:G16" si="13">D119/D65</f>
         <v>-0.11582938388625592</v>
       </c>
       <c r="E16" s="43">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.14323234218178407</v>
       </c>
       <c r="F16" s="43">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.19540834209603924</v>
       </c>
       <c r="G16" s="43">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.19152398932361175</v>
       </c>
-      <c r="H16" s="56"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="86"/>
+      <c r="H16" s="56">
+        <f>H119/H65</f>
+        <v>-0.12072063834486223</v>
+      </c>
+      <c r="I16" s="43">
+        <f t="shared" ref="I16:L16" si="14">I119/I65</f>
+        <v>-0.13828631213180831</v>
+      </c>
+      <c r="J16" s="43">
+        <f t="shared" si="14"/>
+        <v>-0.1561151209427987</v>
+      </c>
+      <c r="K16" s="43">
+        <f t="shared" si="14"/>
+        <v>-0.17881355094237672</v>
+      </c>
+      <c r="L16" s="85">
+        <f t="shared" si="14"/>
+        <v>-0.20156781523882997</v>
+      </c>
     </row>
     <row r="17" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="86" t="s">
         <v>104</v>
       </c>
       <c r="C17" s="43">
@@ -3182,19 +3209,19 @@
         <v>3.4421860450181418E-2</v>
       </c>
       <c r="D17" s="43">
-        <f t="shared" ref="D17:G17" si="13">D99/D31</f>
+        <f t="shared" ref="D17:G17" si="15">D99/D31</f>
         <v>2.9711145808311315E-2</v>
       </c>
       <c r="E17" s="43">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.3922153379438003E-2</v>
       </c>
       <c r="F17" s="43">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.7601966414600779E-2</v>
       </c>
       <c r="G17" s="43">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.1830253847959492E-2</v>
       </c>
       <c r="H17" s="56">
@@ -3202,24 +3229,24 @@
         <v>2.4451457880666091E-2</v>
       </c>
       <c r="I17" s="43">
-        <f t="shared" ref="I17:L17" si="14">AVERAGE(F17:H17)</f>
+        <f t="shared" ref="I17:L17" si="16">AVERAGE(F17:H17)</f>
         <v>2.4627892714408784E-2</v>
       </c>
       <c r="J17" s="43">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>2.3636534814344787E-2</v>
       </c>
       <c r="K17" s="43">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>2.4238628469806553E-2</v>
       </c>
-      <c r="L17" s="86">
-        <f t="shared" si="14"/>
+      <c r="L17" s="85">
+        <f t="shared" si="16"/>
         <v>2.4167685332853375E-2</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="17.25" x14ac:dyDescent="0.4">
-      <c r="B18" s="82" t="s">
+      <c r="B18" s="81" t="s">
         <v>105</v>
       </c>
       <c r="C18" s="45"/>
@@ -3231,10 +3258,10 @@
       <c r="I18" s="43"/>
       <c r="J18" s="43"/>
       <c r="K18" s="43"/>
-      <c r="L18" s="86"/>
+      <c r="L18" s="85"/>
     </row>
     <row r="19" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B19" s="89" t="s">
+      <c r="B19" s="88" t="s">
         <v>132</v>
       </c>
       <c r="C19" s="59">
@@ -3242,19 +3269,19 @@
         <v>15.476431300773848</v>
       </c>
       <c r="D19" s="59">
-        <f t="shared" ref="D19:G19" si="15">D58/D31 * 365</f>
+        <f t="shared" ref="D19:G19" si="17">D58/D31 * 365</f>
         <v>13.792712587076627</v>
       </c>
       <c r="E19" s="59">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.428786281718386</v>
       </c>
       <c r="F19" s="59">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>14.437136371153239</v>
       </c>
       <c r="G19" s="59">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.917384840660384</v>
       </c>
       <c r="H19" s="62">
@@ -3262,24 +3289,24 @@
         <v>13.610490276276497</v>
       </c>
       <c r="I19" s="60">
-        <f t="shared" ref="I19:L19" si="16">AVERAGE(D19:H19)</f>
+        <f t="shared" ref="I19:L19" si="18">AVERAGE(D19:H19)</f>
         <v>13.237302071377027</v>
       </c>
       <c r="J19" s="60">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>13.126219968237105</v>
       </c>
       <c r="K19" s="60">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>13.26570670554085</v>
       </c>
-      <c r="L19" s="90">
-        <f t="shared" si="16"/>
+      <c r="L19" s="89">
+        <f t="shared" si="18"/>
         <v>13.031420772418375</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B20" s="89" t="s">
+      <c r="B20" s="88" t="s">
         <v>133</v>
       </c>
       <c r="C20" s="59">
@@ -3287,15 +3314,15 @@
         <v>485.68285024562351</v>
       </c>
       <c r="D20" s="59">
-        <f t="shared" ref="D20:F20" si="17">D61/D32 *365</f>
+        <f t="shared" ref="D20:F20" si="19">D61/D32 *365</f>
         <v>452.21971210247631</v>
       </c>
       <c r="E20" s="59">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>415.37698016269445</v>
       </c>
       <c r="F20" s="59">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>466.45282302796755</v>
       </c>
       <c r="G20" s="59">
@@ -3307,24 +3334,24 @@
         <v>414.90285242351518</v>
       </c>
       <c r="I20" s="59">
-        <f t="shared" ref="I20:L20" si="18">AVERAGE(F20:H20)</f>
+        <f t="shared" ref="I20:L20" si="20">AVERAGE(F20:H20)</f>
         <v>414.74480984378874</v>
       </c>
       <c r="J20" s="59">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>397.50880544906249</v>
       </c>
       <c r="K20" s="59">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>409.05215590545549</v>
       </c>
-      <c r="L20" s="91">
-        <f t="shared" si="18"/>
+      <c r="L20" s="90">
+        <f t="shared" si="20"/>
         <v>407.10192373276891</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="88" t="s">
         <v>134</v>
       </c>
       <c r="C21" s="59">
@@ -3332,44 +3359,44 @@
         <v>57.063406316997828</v>
       </c>
       <c r="D21" s="59">
-        <f t="shared" ref="D21:G21" si="19">D72/D32 *365</f>
+        <f t="shared" ref="D21:G21" si="21">D72/D32 *365</f>
         <v>59.022163036240848</v>
       </c>
       <c r="E21" s="59">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>62.321392892821464</v>
       </c>
       <c r="F21" s="59">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>60.545629707479421</v>
       </c>
       <c r="G21" s="59">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>56.176591448094491</v>
       </c>
       <c r="H21" s="61">
-        <f t="shared" ref="H21:L21" si="20">AVERAGE(C21:G21)</f>
+        <f t="shared" ref="H21:L21" si="22">AVERAGE(C21:G21)</f>
         <v>59.025836680326805</v>
       </c>
       <c r="I21" s="59">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>59.418322752992609</v>
       </c>
       <c r="J21" s="59">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>59.497554696342959</v>
       </c>
       <c r="K21" s="59">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>58.932787057047257</v>
       </c>
-      <c r="L21" s="91">
-        <f t="shared" si="20"/>
+      <c r="L21" s="90">
+        <f t="shared" si="22"/>
         <v>58.610218526960828</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B22" s="89" t="s">
+      <c r="B22" s="88" t="s">
         <v>122</v>
       </c>
       <c r="C22" s="43">
@@ -3377,29 +3404,44 @@
         <v>0.85059242847509875</v>
       </c>
       <c r="D22" s="43">
-        <f t="shared" ref="D22:G22" si="21">D74/D31</f>
+        <f t="shared" ref="D22:G22" si="23">D74/D31</f>
         <v>0.79691628633197209</v>
       </c>
       <c r="E22" s="43">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.72406612335141529</v>
       </c>
       <c r="F22" s="43">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.90703128523535337</v>
       </c>
       <c r="G22" s="43">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.66400634899343858</v>
       </c>
-      <c r="H22" s="56"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="86"/>
+      <c r="H22" s="56">
+        <f>H108/H31</f>
+        <v>5.7467003972676803E-2</v>
+      </c>
+      <c r="I22" s="43">
+        <f t="shared" ref="I22:L22" si="24">I108/I31</f>
+        <v>6.101004181497427E-2</v>
+      </c>
+      <c r="J22" s="43">
+        <f t="shared" si="24"/>
+        <v>5.2071502281176504E-2</v>
+      </c>
+      <c r="K22" s="43">
+        <f t="shared" si="24"/>
+        <v>8.7458892036223645E-2</v>
+      </c>
+      <c r="L22" s="85">
+        <f t="shared" si="24"/>
+        <v>6.465916515497741E-2</v>
+      </c>
     </row>
     <row r="23" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B23" s="82" t="s">
+      <c r="B23" s="81" t="s">
         <v>106</v>
       </c>
       <c r="C23" s="43"/>
@@ -3411,10 +3453,10 @@
       <c r="I23" s="43"/>
       <c r="J23" s="43"/>
       <c r="K23" s="43"/>
-      <c r="L23" s="86"/>
+      <c r="L23" s="85"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B24" s="89" t="s">
+      <c r="B24" s="88" t="s">
         <v>107</v>
       </c>
       <c r="C24" s="46">
@@ -3422,19 +3464,19 @@
         <v>41858</v>
       </c>
       <c r="D24" s="46">
-        <f t="shared" ref="D24:G24" si="22">D81+D75-D56-D57</f>
+        <f t="shared" ref="D24:G24" si="25">D81+D75-D56-D57</f>
         <v>39781</v>
       </c>
       <c r="E24" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>36342</v>
       </c>
       <c r="F24" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>27582</v>
       </c>
       <c r="G24" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>24698</v>
       </c>
       <c r="H24" s="65">
@@ -3442,32 +3484,32 @@
         <v>29540.666666666668</v>
       </c>
       <c r="I24" s="46">
-        <f t="shared" ref="I24:L24" si="23">AVERAGE(F24:H24)</f>
+        <f t="shared" ref="I24:L24" si="26">AVERAGE(F24:H24)</f>
         <v>27273.555555555558</v>
       </c>
       <c r="J24" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>27170.740740740745</v>
       </c>
       <c r="K24" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>27994.987654320994</v>
       </c>
-      <c r="L24" s="92">
-        <f t="shared" si="23"/>
+      <c r="L24" s="91">
+        <f t="shared" si="26"/>
         <v>27479.761316872435</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B25" s="89" t="s">
+      <c r="B25" s="88" t="s">
         <v>108</v>
       </c>
       <c r="C25" s="47" t="str">
-        <f t="shared" ref="C25:D25" si="24">IF(C24/(C38+C99)&lt;0,"nm",C24/(C38+C99))</f>
+        <f t="shared" ref="C25:D25" si="27">IF(C24/(C38+C99)&lt;0,"nm",C24/(C38+C99))</f>
         <v>nm</v>
       </c>
       <c r="D25" s="47" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>nm</v>
       </c>
       <c r="E25" s="47">
@@ -3475,21 +3517,36 @@
         <v>34.944230769230771</v>
       </c>
       <c r="F25" s="47" t="str">
-        <f t="shared" ref="F25" si="25">IF(F24/(F38+F99)&lt;0,"nm",F24/(F38+F99))</f>
+        <f t="shared" ref="F25" si="28">IF(F24/(F38+F99)&lt;0,"nm",F24/(F38+F99))</f>
         <v>nm</v>
       </c>
-      <c r="G25" s="47" t="str">
-        <f t="shared" ref="G25" si="26">IF(G24/(G38+G99)&lt;0,"nm",G24/(G38+G99))</f>
+      <c r="G25" s="92" t="str">
+        <f t="shared" ref="G25:L25" si="29">IF(G24/(G38+G99)&lt;0,"nm",G24/(G38+G99))</f>
         <v>nm</v>
       </c>
-      <c r="H25" s="78"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="93"/>
+      <c r="H25" s="47" t="str">
+        <f t="shared" si="29"/>
+        <v>nm</v>
+      </c>
+      <c r="I25" s="47" t="str">
+        <f t="shared" si="29"/>
+        <v>nm</v>
+      </c>
+      <c r="J25" s="47" t="str">
+        <f t="shared" si="29"/>
+        <v>nm</v>
+      </c>
+      <c r="K25" s="47" t="str">
+        <f t="shared" si="29"/>
+        <v>nm</v>
+      </c>
+      <c r="L25" s="92" t="str">
+        <f t="shared" si="29"/>
+        <v>nm</v>
+      </c>
     </row>
     <row r="26" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B26" s="89" t="s">
+      <c r="B26" s="88" t="s">
         <v>109</v>
       </c>
       <c r="C26" s="47" t="str">
@@ -3497,29 +3554,44 @@
         <v>nm</v>
       </c>
       <c r="D26" s="47" t="str">
-        <f t="shared" ref="D26:G26" si="27">IF(D42/(D81+D75)&lt;0,"nm",D42/(D81+D75))</f>
+        <f t="shared" ref="D26:L26" si="30">IF(D42/(D81+D75)&lt;0,"nm",D42/(D81+D75))</f>
         <v>nm</v>
       </c>
       <c r="E26" s="47" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>nm</v>
       </c>
       <c r="F26" s="47" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>nm</v>
       </c>
-      <c r="G26" s="47" t="str">
-        <f t="shared" si="27"/>
+      <c r="G26" s="92" t="str">
+        <f t="shared" si="30"/>
         <v>nm</v>
       </c>
-      <c r="H26" s="56"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="86"/>
+      <c r="H26" s="47" t="str">
+        <f t="shared" si="30"/>
+        <v>nm</v>
+      </c>
+      <c r="I26" s="47" t="str">
+        <f t="shared" si="30"/>
+        <v>nm</v>
+      </c>
+      <c r="J26" s="47" t="str">
+        <f t="shared" si="30"/>
+        <v>nm</v>
+      </c>
+      <c r="K26" s="47" t="str">
+        <f t="shared" si="30"/>
+        <v>nm</v>
+      </c>
+      <c r="L26" s="92" t="str">
+        <f t="shared" si="30"/>
+        <v>nm</v>
+      </c>
     </row>
     <row r="27" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="B27" s="94" t="s">
+      <c r="B27" s="93" t="s">
         <v>110</v>
       </c>
       <c r="C27" s="52">
@@ -3527,19 +3599,19 @@
         <v>-4.6710956593576811E-2</v>
       </c>
       <c r="D27" s="52">
-        <f t="shared" ref="D27:G27" si="28">D42/(D75+D81)</f>
+        <f t="shared" ref="D27:G27" si="31">D42/(D75+D81)</f>
         <v>-4.4929036332695918E-2</v>
       </c>
       <c r="E27" s="52">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>-4.7010916320951307E-2</v>
       </c>
       <c r="F27" s="52">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>-5.0590375761176296E-2</v>
       </c>
       <c r="G27" s="52">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>-5.1221856630559358E-2</v>
       </c>
       <c r="H27" s="63">
@@ -3547,19 +3619,19 @@
         <v>-4.960771623756232E-2</v>
       </c>
       <c r="I27" s="52">
-        <f t="shared" ref="I27:L27" si="29">AVERAGE(F27:H27)</f>
+        <f t="shared" ref="I27:L27" si="32">AVERAGE(F27:H27)</f>
         <v>-5.0473316209765993E-2</v>
       </c>
       <c r="J27" s="52">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-5.0434296359295888E-2</v>
       </c>
       <c r="K27" s="52">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-5.0171776268874736E-2</v>
       </c>
-      <c r="L27" s="95">
-        <f t="shared" si="29"/>
+      <c r="L27" s="94">
+        <f t="shared" si="32"/>
         <v>-5.0359796279312204E-2</v>
       </c>
     </row>
@@ -3593,23 +3665,23 @@
         <v>2025</v>
       </c>
       <c r="H30" s="2">
-        <f t="shared" ref="H30" si="30">+G30+1</f>
+        <f t="shared" ref="H30" si="33">+G30+1</f>
         <v>2026</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" ref="I30" si="31">+H30+1</f>
+        <f t="shared" ref="I30" si="34">+H30+1</f>
         <v>2027</v>
       </c>
       <c r="J30" s="2">
-        <f t="shared" ref="J30" si="32">+I30+1</f>
+        <f t="shared" ref="J30" si="35">+I30+1</f>
         <v>2028</v>
       </c>
       <c r="K30" s="2">
-        <f t="shared" ref="K30" si="33">+J30+1</f>
+        <f t="shared" ref="K30" si="36">+J30+1</f>
         <v>2029</v>
       </c>
       <c r="L30" s="2">
-        <f t="shared" ref="L30" si="34">+K30+1</f>
+        <f t="shared" ref="L30" si="37">+K30+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -3637,19 +3709,19 @@
         <v>97939.235908870192</v>
       </c>
       <c r="I31" s="42">
-        <f t="shared" ref="I31:L31" si="35">H31*(1+I4)</f>
+        <f t="shared" ref="I31:L31" si="38">H31*(1+I4)</f>
         <v>107848.54514840148</v>
       </c>
       <c r="J31" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>117025.72437734834</v>
       </c>
       <c r="K31" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>134777.84533508398</v>
       </c>
       <c r="L31" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>149318.03705658542</v>
       </c>
     </row>
@@ -3669,27 +3741,27 @@
       <c r="F32" s="5">
         <v>68508</v>
       </c>
-      <c r="G32" s="96">
+      <c r="G32" s="95">
         <v>85174</v>
       </c>
       <c r="H32" s="66">
         <f>H31*G7</f>
         <v>93243.871536860039</v>
       </c>
-      <c r="I32" s="98">
-        <f t="shared" ref="I32:L32" si="36">I31*H7</f>
+      <c r="I32" s="97">
+        <f t="shared" ref="I32:L32" si="39">I31*H7</f>
         <v>102678.11256575285</v>
       </c>
-      <c r="J32" s="98">
-        <f t="shared" si="36"/>
+      <c r="J32" s="97">
+        <f t="shared" si="39"/>
         <v>111415.32307340764</v>
       </c>
-      <c r="K32" s="98">
-        <f t="shared" si="36"/>
+      <c r="K32" s="97">
+        <f t="shared" si="39"/>
         <v>128316.37882219961</v>
       </c>
-      <c r="L32" s="98">
-        <f t="shared" si="36"/>
+      <c r="L32" s="97">
+        <f t="shared" si="39"/>
         <v>142159.49038437798</v>
       </c>
     </row>
@@ -3717,24 +3789,24 @@
         <f>SUM(G31-G32)</f>
         <v>4289</v>
       </c>
-      <c r="H33" s="97">
-        <f t="shared" ref="H33:L33" si="37">SUM(H31-H32)</f>
+      <c r="H33" s="96">
+        <f t="shared" ref="H33:L33" si="40">SUM(H31-H32)</f>
         <v>4695.3643720101536</v>
       </c>
       <c r="I33" s="71">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>5170.4325826486311</v>
       </c>
       <c r="J33" s="71">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>5610.4013039407</v>
       </c>
       <c r="K33" s="71">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>6461.4665128843772</v>
       </c>
       <c r="L33" s="71">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>7158.5466722074489</v>
       </c>
     </row>
@@ -3777,15 +3849,15 @@
         <v>7341.5561735439787</v>
       </c>
       <c r="J35" s="42">
-        <f t="shared" ref="J35:L35" si="38">J31*I8</f>
+        <f t="shared" ref="J35:L35" si="41">J31*I8</f>
         <v>7966.2727771039572</v>
       </c>
       <c r="K35" s="42">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>9174.7099704979864</v>
       </c>
       <c r="L35" s="42">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>10164.502036312277</v>
       </c>
     </row>
@@ -3812,20 +3884,20 @@
         <f>H31*G9</f>
         <v>3957.5057600411988</v>
       </c>
-      <c r="I36" s="98">
-        <f t="shared" ref="I36:L36" si="39">I31*H9</f>
+      <c r="I36" s="97">
+        <f t="shared" ref="I36:L36" si="42">I31*H9</f>
         <v>4357.918812374628</v>
       </c>
-      <c r="J36" s="98">
-        <f t="shared" si="39"/>
+      <c r="J36" s="97">
+        <f t="shared" si="42"/>
         <v>4728.7481263104773</v>
       </c>
-      <c r="K36" s="98">
-        <f t="shared" si="39"/>
+      <c r="K36" s="97">
+        <f t="shared" si="42"/>
         <v>5446.0716819951112</v>
       </c>
-      <c r="L36" s="98">
-        <f t="shared" si="39"/>
+      <c r="L36" s="97">
+        <f t="shared" si="42"/>
         <v>6033.6083516040853</v>
       </c>
     </row>
@@ -3838,39 +3910,39 @@
         <v>6406</v>
       </c>
       <c r="D37" s="7">
-        <f t="shared" ref="D37:L37" si="40">SUM(D35:D36)</f>
+        <f t="shared" ref="D37:L37" si="43">SUM(D35:D36)</f>
         <v>7039</v>
       </c>
       <c r="E37" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>8545</v>
       </c>
       <c r="F37" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>8833</v>
       </c>
       <c r="G37" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>9705</v>
       </c>
-      <c r="H37" s="97">
-        <f t="shared" si="40"/>
+      <c r="H37" s="96">
+        <f t="shared" si="43"/>
         <v>10624.507164923882</v>
       </c>
       <c r="I37" s="71">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>11699.474985918607</v>
       </c>
       <c r="J37" s="71">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12695.020903414435</v>
       </c>
       <c r="K37" s="71">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>14620.781652493097</v>
       </c>
       <c r="L37" s="71">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>16198.110387916362</v>
       </c>
     </row>
@@ -3879,43 +3951,43 @@
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <f t="shared" ref="C38:H38" si="41">SUM(C33-C37)</f>
+        <f t="shared" ref="C38:H38" si="44">SUM(C33-C37)</f>
         <v>-3357</v>
       </c>
       <c r="D38" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>-3509</v>
       </c>
       <c r="E38" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>-821</v>
       </c>
       <c r="F38" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>-10824</v>
       </c>
       <c r="G38" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>-5416</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>-5929.142792913728</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" ref="I38:L38" si="42">SUM(I33-I37)</f>
+        <f t="shared" ref="I38:L38" si="45">SUM(I33-I37)</f>
         <v>-6529.0424032699757</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>-7084.6195994737354</v>
       </c>
       <c r="K38" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>-8159.3151396087196</v>
       </c>
       <c r="L38" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>-9039.5637157089132</v>
       </c>
     </row>
@@ -3943,19 +4015,19 @@
         <v>47.333333333333336</v>
       </c>
       <c r="I39" s="68">
-        <f t="shared" ref="I39:L39" si="43">AVERAGE(F39:H39)</f>
+        <f t="shared" ref="I39:L39" si="46">AVERAGE(F39:H39)</f>
         <v>47.777777777777779</v>
       </c>
       <c r="J39" s="68">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>40.037037037037038</v>
       </c>
       <c r="K39" s="68">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>45.049382716049386</v>
       </c>
       <c r="L39" s="68">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>44.288065843621403</v>
       </c>
     </row>
@@ -4018,19 +4090,19 @@
         <v>1191.3333333333333</v>
       </c>
       <c r="I41" s="68">
-        <f t="shared" ref="I41:L41" si="44">AVERAGE(F41:H41)</f>
+        <f t="shared" ref="I41:L41" si="47">AVERAGE(F41:H41)</f>
         <v>1179.4444444444443</v>
       </c>
       <c r="J41" s="68">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>1165.2592592592591</v>
       </c>
       <c r="K41" s="68">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>1178.6790123456788</v>
       </c>
       <c r="L41" s="68">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>1174.4609053497941</v>
       </c>
     </row>
@@ -4058,20 +4130,20 @@
         <f>H27*(H75+H81)</f>
         <v>-2683.6782330196465</v>
       </c>
-      <c r="I42" s="98">
-        <f t="shared" ref="I42:L42" si="45">I27*(I75+I81)</f>
+      <c r="I42" s="97">
+        <f t="shared" ref="I42:L42" si="48">I27*(I75+I81)</f>
         <v>-2730.5054603159206</v>
       </c>
-      <c r="J42" s="98">
-        <f t="shared" si="45"/>
+      <c r="J42" s="97">
+        <f t="shared" si="48"/>
         <v>-2728.3945644451887</v>
       </c>
-      <c r="K42" s="98">
-        <f t="shared" si="45"/>
+      <c r="K42" s="97">
+        <f t="shared" si="48"/>
         <v>-2714.1927525935853</v>
       </c>
-      <c r="L42" s="98">
-        <f t="shared" si="45"/>
+      <c r="L42" s="97">
+        <f t="shared" si="48"/>
         <v>-2724.3642591182315</v>
       </c>
     </row>
@@ -4084,39 +4156,39 @@
         <v>-5033</v>
       </c>
       <c r="D43" s="7">
-        <f t="shared" ref="D43:F43" si="46">SUM(D38:D42)</f>
+        <f t="shared" ref="D43:F43" si="49">SUM(D38:D42)</f>
         <v>-5022</v>
       </c>
       <c r="E43" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>-2005</v>
       </c>
       <c r="F43" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>-12210</v>
       </c>
       <c r="G43" s="7">
         <f>SUM(G38:G42)</f>
         <v>2635</v>
       </c>
-      <c r="H43" s="108">
+      <c r="H43" s="107">
         <f>SUM(H38:H42)</f>
         <v>-7374.1543592667085</v>
       </c>
-      <c r="I43" s="109">
-        <f t="shared" ref="I43:L43" si="47">SUM(I38:I42)</f>
+      <c r="I43" s="108">
+        <f t="shared" ref="I43:L43" si="50">SUM(I38:I42)</f>
         <v>-8032.3256413636745</v>
       </c>
-      <c r="J43" s="109">
-        <f t="shared" si="47"/>
+      <c r="J43" s="108">
+        <f t="shared" si="50"/>
         <v>-8607.7178676226285</v>
       </c>
-      <c r="K43" s="109">
-        <f t="shared" si="47"/>
+      <c r="K43" s="108">
+        <f t="shared" si="50"/>
         <v>-9649.7794971405783</v>
       </c>
-      <c r="L43" s="109">
-        <f t="shared" si="47"/>
+      <c r="L43" s="108">
+        <f t="shared" si="50"/>
         <v>-10545.17900363373</v>
       </c>
     </row>
@@ -4144,19 +4216,19 @@
         <v>-1548.5724154460088</v>
       </c>
       <c r="I44" s="68">
-        <f t="shared" ref="I44:L44" si="48">I43*I13</f>
+        <f t="shared" ref="I44:L44" si="51">I43*I13</f>
         <v>-1686.7883846863715</v>
       </c>
       <c r="J44" s="68">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>-1807.6207522007519</v>
       </c>
       <c r="K44" s="68">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>-2026.4536943995213</v>
       </c>
       <c r="L44" s="68">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>-2214.4875907630831</v>
       </c>
     </row>
@@ -4165,43 +4237,43 @@
         <v>50</v>
       </c>
       <c r="C45" s="13">
-        <f t="shared" ref="C45:L45" si="49">SUM(C43-C44)</f>
+        <f t="shared" ref="C45:L45" si="52">SUM(C43-C44)</f>
         <v>-4290</v>
       </c>
       <c r="D45" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>-5053</v>
       </c>
       <c r="E45" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>-2242</v>
       </c>
       <c r="F45" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>-11829</v>
       </c>
       <c r="G45" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>2238</v>
       </c>
       <c r="H45" s="75">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>-5825.5819438207</v>
       </c>
       <c r="I45" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>-6345.537256677303</v>
       </c>
       <c r="J45" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>-6800.0971154218769</v>
       </c>
       <c r="K45" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>-7623.3258027410575</v>
       </c>
       <c r="L45" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>-8330.6914128706467</v>
       </c>
     </row>
@@ -4229,19 +4301,19 @@
         <v>-9.6666666666666661</v>
       </c>
       <c r="I46" s="68">
-        <f t="shared" ref="I46:L46" si="50">AVERAGE(F46:H46)</f>
+        <f t="shared" ref="I46:L46" si="53">AVERAGE(F46:H46)</f>
         <v>-6.2222222222222214</v>
       </c>
       <c r="J46" s="68">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-4.2962962962962958</v>
       </c>
       <c r="K46" s="68">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-6.7283950617283947</v>
       </c>
       <c r="L46" s="68">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-5.7489711934156373</v>
       </c>
     </row>
@@ -4250,19 +4322,19 @@
         <v>118</v>
       </c>
       <c r="C47" s="17">
-        <f t="shared" ref="C47:F47" si="51">SUM(C45-C46)</f>
+        <f t="shared" ref="C47:F47" si="54">SUM(C45-C46)</f>
         <v>-4202</v>
       </c>
       <c r="D47" s="17">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>-4935</v>
       </c>
       <c r="E47" s="17">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>-2222</v>
       </c>
       <c r="F47" s="17">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>-11817</v>
       </c>
       <c r="G47" s="17">
@@ -4270,7 +4342,7 @@
         <v>2235</v>
       </c>
       <c r="H47" s="72">
-        <f t="shared" ref="H47:L47" si="52">SUM(H45-H46)</f>
+        <f t="shared" ref="H47:L47" si="55">SUM(H45-H46)</f>
         <v>-5815.915277154033</v>
       </c>
       <c r="I47" s="17">
@@ -4278,15 +4350,15 @@
         <v>-6339.3150344550804</v>
       </c>
       <c r="J47" s="17">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>-6795.8008191255803</v>
       </c>
       <c r="K47" s="17">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>-7616.5974076793291</v>
       </c>
       <c r="L47" s="17">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>-8324.9424416772308</v>
       </c>
     </row>
@@ -4330,15 +4402,15 @@
         <v>120</v>
       </c>
       <c r="C49" s="17">
-        <f t="shared" ref="C49:E49" si="53">SUM(C47-C48)</f>
+        <f t="shared" ref="C49:E49" si="56">SUM(C47-C48)</f>
         <v>-4202</v>
       </c>
       <c r="D49" s="17">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>-4935</v>
       </c>
       <c r="E49" s="17">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>-2222</v>
       </c>
       <c r="F49" s="17">
@@ -4350,23 +4422,23 @@
         <v>1890</v>
       </c>
       <c r="H49" s="71">
-        <f t="shared" ref="H49:L49" si="54">SUM(H47:H48)</f>
+        <f t="shared" ref="H49:L49" si="57">SUM(H47:H48)</f>
         <v>-6160.915277154033</v>
       </c>
       <c r="I49" s="71">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>-6512.3150344550804</v>
       </c>
       <c r="J49" s="71">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>-6795.8008191255803</v>
       </c>
       <c r="K49" s="71">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>-7616.5974076793291</v>
       </c>
       <c r="L49" s="71">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>-8324.9424416772308</v>
       </c>
     </row>
@@ -4394,19 +4466,19 @@
         <v>670.83333333333326</v>
       </c>
       <c r="I50" s="70">
-        <f t="shared" ref="I50:L50" si="55">AVERAGE(F50:H50)</f>
+        <f t="shared" ref="I50:L50" si="58">AVERAGE(F50:H50)</f>
         <v>692.51111111111095</v>
       </c>
       <c r="J50" s="70">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>707.71481481481476</v>
       </c>
       <c r="K50" s="70">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>690.35308641975291</v>
       </c>
       <c r="L50" s="70">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>696.85967078189287</v>
       </c>
     </row>
@@ -4419,15 +4491,15 @@
         <v>-7.1511232130701154</v>
       </c>
       <c r="D51" s="50">
-        <f t="shared" ref="D51:L51" si="56">D49/D50</f>
+        <f t="shared" ref="D51:L51" si="59">D49/D50</f>
         <v>-8.2955118507312164</v>
       </c>
       <c r="E51" s="50">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-3.6678771871904923</v>
       </c>
       <c r="F51" s="50">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-18.356778481991036</v>
       </c>
       <c r="G51" s="50">
@@ -4439,19 +4511,19 @@
         <v>-9.1839730839563227</v>
       </c>
       <c r="I51" s="50">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-9.4039141465994511</v>
       </c>
       <c r="J51" s="50">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-9.6024566348859235</v>
       </c>
       <c r="K51" s="50">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-11.032901217520214</v>
       </c>
       <c r="L51" s="50">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-11.946368531179958</v>
       </c>
     </row>
@@ -4479,19 +4551,19 @@
         <v>671.66666666666663</v>
       </c>
       <c r="I52" s="68">
-        <f t="shared" ref="I52:L52" si="57">AVERAGE(F52:H52)</f>
+        <f t="shared" ref="I52:L52" si="60">AVERAGE(F52:H52)</f>
         <v>693.62222222222215</v>
       </c>
       <c r="J52" s="68">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>709.19629629629628</v>
       </c>
       <c r="K52" s="68">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>691.49506172839494</v>
       </c>
       <c r="L52" s="68">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>698.10452674897113</v>
       </c>
     </row>
@@ -4504,39 +4576,39 @@
         <v>-7.1511232130701154</v>
       </c>
       <c r="D53" s="51">
-        <f t="shared" ref="D53:L53" si="58">D49/D52</f>
+        <f t="shared" ref="D53:L53" si="61">D49/D52</f>
         <v>-8.2955118507312164</v>
       </c>
       <c r="E53" s="51">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-3.6678771871904923</v>
       </c>
       <c r="F53" s="51">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-18.356778481991036</v>
       </c>
       <c r="G53" s="51">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>2.4793388429752068</v>
       </c>
       <c r="H53" s="74">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-9.1725785764079895</v>
       </c>
       <c r="I53" s="51">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-9.3888500480722339</v>
       </c>
       <c r="J53" s="51">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-9.5823975035063516</v>
       </c>
       <c r="K53" s="51">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-11.014680840441015</v>
       </c>
       <c r="L53" s="51">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-11.925065835693637</v>
       </c>
     </row>
@@ -4548,15 +4620,15 @@
         <v>2021</v>
       </c>
       <c r="D55" s="2">
-        <f t="shared" ref="D55:E55" si="59">+C55+1</f>
+        <f t="shared" ref="D55:E55" si="62">+C55+1</f>
         <v>2022</v>
       </c>
       <c r="E55" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>2023</v>
       </c>
       <c r="F55" s="2">
-        <f t="shared" ref="F55" si="60">+E55+1</f>
+        <f t="shared" ref="F55" si="63">+E55+1</f>
         <v>2024</v>
       </c>
       <c r="G55" s="2">
@@ -4564,23 +4636,23 @@
         <v>2025</v>
       </c>
       <c r="H55" s="2">
-        <f t="shared" ref="H55:L55" si="61">+G55+1</f>
+        <f t="shared" ref="H55:L55" si="64">+G55+1</f>
         <v>2026</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>2027</v>
       </c>
       <c r="J55" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>2028</v>
       </c>
       <c r="K55" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>2029</v>
       </c>
       <c r="L55" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>2030</v>
       </c>
     </row>
@@ -4608,19 +4680,19 @@
         <v>-7771.6140994320704</v>
       </c>
       <c r="I56" s="68">
-        <f t="shared" ref="I56:L56" si="62">I144</f>
+        <f t="shared" ref="I56:L56" si="65">I144</f>
         <v>-17843.033783791336</v>
       </c>
       <c r="J56" s="68">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>-24749.5122860181</v>
       </c>
       <c r="K56" s="68">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>-41729.38729102887</v>
       </c>
       <c r="L56" s="68">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>-53543.353101821362</v>
       </c>
     </row>
@@ -4648,19 +4720,19 @@
         <v>18479</v>
       </c>
       <c r="I57" s="42">
-        <f t="shared" ref="I57:L57" si="63">H57</f>
+        <f t="shared" ref="I57:L57" si="66">H57</f>
         <v>18479</v>
       </c>
       <c r="J57" s="42">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>18479</v>
       </c>
       <c r="K57" s="42">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>18479</v>
       </c>
       <c r="L57" s="42">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>18479</v>
       </c>
     </row>
@@ -4688,19 +4760,19 @@
         <v>3652.0575835715831</v>
       </c>
       <c r="I58" s="42">
-        <f t="shared" ref="I58:L58" si="64">(I19/365)*I31</f>
+        <f t="shared" ref="I58:L58" si="67">(I19/365)*I31</f>
         <v>3911.2980002409145</v>
       </c>
       <c r="J58" s="42">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>4208.5079455324976</v>
       </c>
       <c r="K58" s="42">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>4898.4201825204691</v>
       </c>
       <c r="L58" s="42">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5331.0306021806136</v>
       </c>
     </row>
@@ -4728,19 +4800,19 @@
         <v>8618.4</v>
       </c>
       <c r="I59" s="42">
-        <f t="shared" ref="I59:L59" si="65">AVERAGE(D59:H59)</f>
+        <f t="shared" ref="I59:L59" si="68">AVERAGE(D59:H59)</f>
         <v>8618.08</v>
       </c>
       <c r="J59" s="42">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>8614.8960000000006</v>
       </c>
       <c r="K59" s="42">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>8674.4752000000008</v>
       </c>
       <c r="L59" s="42">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>8736.7702400000016</v>
       </c>
     </row>
@@ -4763,24 +4835,24 @@
       <c r="G60" s="18">
         <v>0</v>
       </c>
-      <c r="H60" s="100">
+      <c r="H60" s="99">
         <f>G60</f>
         <v>0</v>
       </c>
-      <c r="I60" s="101">
+      <c r="I60" s="100">
         <f>H60</f>
         <v>0</v>
       </c>
-      <c r="J60" s="101">
-        <f t="shared" ref="J60:L60" si="66">I60</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="101">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="L60" s="101">
-        <f t="shared" si="66"/>
+      <c r="J60" s="100">
+        <f t="shared" ref="J60:L60" si="69">I60</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="100">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="L60" s="100">
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
     </row>
@@ -4808,19 +4880,19 @@
         <v>105992.18704563027</v>
       </c>
       <c r="I61" s="42">
-        <f t="shared" ref="I61:L61" si="67">(I20/365)*I32</f>
+        <f t="shared" ref="I61:L61" si="70">(I20/365)*I32</f>
         <v>116671.81992110219</v>
       </c>
       <c r="J61" s="42">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>121338.55337981271</v>
       </c>
       <c r="K61" s="42">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>143802.99012384078</v>
       </c>
       <c r="L61" s="42">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>158557.26578726122</v>
       </c>
     </row>
@@ -4843,24 +4915,24 @@
       <c r="G62" s="5">
         <v>2301</v>
       </c>
-      <c r="H62" s="111">
+      <c r="H62" s="110">
         <f>G62*(1+H4)</f>
         <v>2519.0098904162651</v>
       </c>
-      <c r="I62" s="112">
-        <f t="shared" ref="I62:L62" si="68">H62*(1+I4)</f>
+      <c r="I62" s="111">
+        <f t="shared" ref="I62:L62" si="71">H62*(1+I4)</f>
         <v>2773.8786133538088</v>
       </c>
-      <c r="J62" s="112">
-        <f t="shared" si="68"/>
+      <c r="J62" s="111">
+        <f t="shared" si="71"/>
         <v>3009.9168571619389</v>
       </c>
-      <c r="K62" s="112">
-        <f t="shared" si="68"/>
+      <c r="K62" s="111">
+        <f t="shared" si="71"/>
         <v>3466.5037179172205</v>
       </c>
-      <c r="L62" s="112">
-        <f t="shared" si="68"/>
+      <c r="L62" s="111">
+        <f t="shared" si="71"/>
         <v>3840.4793408135556</v>
       </c>
     </row>
@@ -4881,31 +4953,31 @@
         <v>109275</v>
       </c>
       <c r="F63" s="7">
-        <f t="shared" ref="F63" si="69">SUM(F56:F62)</f>
+        <f t="shared" ref="F63" si="72">SUM(F56:F62)</f>
         <v>127998</v>
       </c>
       <c r="G63" s="7">
         <f>SUM(G56:G62)</f>
         <v>128459</v>
       </c>
-      <c r="H63" s="102">
+      <c r="H63" s="101">
         <f>SUM(H56:H62)</f>
         <v>131489.04042018604</v>
       </c>
       <c r="I63" s="7">
-        <f t="shared" ref="H63:L63" si="70">SUM(I56:I62)</f>
+        <f t="shared" ref="I63:L63" si="73">SUM(I56:I62)</f>
         <v>132611.04275090556</v>
       </c>
       <c r="J63" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>130901.36189648905</v>
       </c>
       <c r="K63" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>137592.00193324959</v>
       </c>
       <c r="L63" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>141401.19286843404</v>
       </c>
     </row>
@@ -4928,19 +5000,19 @@
       <c r="G64" s="18">
         <v>241</v>
       </c>
-      <c r="H64" s="103">
+      <c r="H64" s="102">
         <v>191</v>
       </c>
-      <c r="I64" s="104">
+      <c r="I64" s="103">
         <v>141</v>
       </c>
-      <c r="J64" s="104">
+      <c r="J64" s="103">
         <v>91</v>
       </c>
-      <c r="K64" s="104">
+      <c r="K64" s="103">
         <v>41</v>
       </c>
-      <c r="L64" s="104">
+      <c r="L64" s="103">
         <v>0</v>
       </c>
     </row>
@@ -4968,19 +5040,19 @@
         <v>14746.44289830964</v>
       </c>
       <c r="I65" s="68">
-        <f t="shared" ref="I65:L65" si="71">H65 - I119 - I99</f>
+        <f t="shared" ref="I65:L65" si="74">H65 - I119 - I99</f>
         <v>14030.600498989737</v>
       </c>
       <c r="J65" s="68">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>13348.405890570626</v>
       </c>
       <c r="K65" s="68">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>12276.841371532475</v>
       </c>
       <c r="L65" s="68">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>10856.488757429579</v>
       </c>
     </row>
@@ -5003,24 +5075,24 @@
       <c r="G66" s="18">
         <v>17275</v>
       </c>
-      <c r="H66" s="99">
+      <c r="H66" s="98">
         <f>G66</f>
         <v>17275</v>
       </c>
       <c r="I66" s="18">
-        <f t="shared" ref="I66:L66" si="72">H66</f>
+        <f t="shared" ref="I66:L66" si="75">H66</f>
         <v>17275</v>
       </c>
       <c r="J66" s="18">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>17275</v>
       </c>
       <c r="K66" s="18">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>17275</v>
       </c>
       <c r="L66" s="18">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>17275</v>
       </c>
     </row>
@@ -5048,19 +5120,19 @@
         <v>2098.1999999999998</v>
       </c>
       <c r="I67" s="68">
-        <f t="shared" ref="I67:L67" si="73">AVERAGE(D67:H67)</f>
+        <f t="shared" ref="I67:L67" si="76">AVERAGE(D67:H67)</f>
         <v>2005.44</v>
       </c>
       <c r="J67" s="68">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>1944.328</v>
       </c>
       <c r="K67" s="68">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>1914.3935999999999</v>
       </c>
       <c r="L67" s="68">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>1905.8723199999997</v>
       </c>
     </row>
@@ -5092,15 +5164,15 @@
         <v>107</v>
       </c>
       <c r="J68" s="68">
-        <f t="shared" ref="J68:L68" si="74">I68</f>
+        <f t="shared" ref="J68:L68" si="77">I68</f>
         <v>107</v>
       </c>
       <c r="K68" s="68">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>107</v>
       </c>
       <c r="L68" s="68">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>107</v>
       </c>
     </row>
@@ -5132,15 +5204,15 @@
         <v>1048</v>
       </c>
       <c r="J69" s="68">
-        <f t="shared" ref="J69:L69" si="75">I69</f>
+        <f t="shared" ref="J69:L69" si="78">I69</f>
         <v>1048</v>
       </c>
       <c r="K69" s="68">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>1048</v>
       </c>
       <c r="L69" s="68">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>1048</v>
       </c>
     </row>
@@ -5163,24 +5235,24 @@
       <c r="G70" s="18">
         <v>4177</v>
       </c>
-      <c r="H70" s="111">
+      <c r="H70" s="110">
         <f>G70*(1+H4)</f>
         <v>4572.7528519203561</v>
       </c>
-      <c r="I70" s="112">
-        <f t="shared" ref="I70:L70" si="76">H70*(1+I4)</f>
+      <c r="I70" s="111">
+        <f t="shared" ref="I70:L70" si="79">H70*(1+I4)</f>
         <v>5035.4154576179308</v>
       </c>
-      <c r="J70" s="112">
-        <f t="shared" si="76"/>
+      <c r="J70" s="111">
+        <f t="shared" si="79"/>
         <v>5463.8951379249966</v>
       </c>
-      <c r="K70" s="112">
-        <f t="shared" si="76"/>
+      <c r="K70" s="111">
+        <f t="shared" si="79"/>
         <v>6292.73621457637</v>
       </c>
-      <c r="L70" s="112">
-        <f t="shared" si="76"/>
+      <c r="L70" s="111">
+        <f t="shared" si="79"/>
         <v>6971.6133014246934</v>
       </c>
     </row>
@@ -5193,39 +5265,39 @@
         <v>138552</v>
       </c>
       <c r="D71" s="25">
-        <f t="shared" ref="D71:L71" si="77">SUM(D63:D70)</f>
+        <f t="shared" ref="D71:L71" si="80">SUM(D63:D70)</f>
         <v>137100</v>
       </c>
       <c r="E71" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>137012</v>
       </c>
       <c r="F71" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>156363</v>
       </c>
       <c r="G71" s="26">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>168235</v>
       </c>
       <c r="H71" s="71">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>171527.43617041604</v>
       </c>
       <c r="I71" s="71">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>172253.49870751324</v>
       </c>
       <c r="J71" s="71">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>170178.99092498468</v>
       </c>
       <c r="K71" s="71">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>176546.97311935844</v>
       </c>
       <c r="L71" s="71">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>179565.16724728831</v>
       </c>
     </row>
@@ -5253,19 +5325,19 @@
         <v>15078.897350071435</v>
       </c>
       <c r="I72" s="46">
-        <f t="shared" ref="I72:L72" si="78">(I21/365) *I32</f>
+        <f t="shared" ref="I72:L72" si="81">(I21/365) *I32</f>
         <v>16714.962279726053</v>
       </c>
       <c r="J72" s="46">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>18161.47747553642</v>
       </c>
       <c r="K72" s="46">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>20717.922819342733</v>
       </c>
       <c r="L72" s="46">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>22827.393964684325</v>
       </c>
     </row>
@@ -5293,19 +5365,19 @@
         <v>29712.493453188981</v>
       </c>
       <c r="I73" s="42">
-        <f t="shared" ref="I73:L73" si="79">H73*(1+I4)</f>
+        <f t="shared" ref="I73:L73" si="82">H73*(1+I4)</f>
         <v>32718.748129089839</v>
       </c>
       <c r="J73" s="42">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>35502.891534216506</v>
       </c>
       <c r="K73" s="42">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>40888.473449800644</v>
       </c>
       <c r="L73" s="42">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>45299.630503703047</v>
       </c>
     </row>
@@ -5333,19 +5405,19 @@
         <v>65032.274459055974</v>
       </c>
       <c r="I74" s="42">
-        <f t="shared" ref="I74:L74" si="80">H74*(1+I4)</f>
+        <f t="shared" ref="I74:L74" si="83">H74*(1+I4)</f>
         <v>71612.118708244088</v>
       </c>
       <c r="J74" s="42">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>77705.823982115515</v>
       </c>
       <c r="K74" s="42">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>89493.345006151474</v>
       </c>
       <c r="L74" s="42">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>99148.124624810269</v>
       </c>
     </row>
@@ -5368,24 +5440,24 @@
       <c r="G75" s="18">
         <v>8461</v>
       </c>
-      <c r="H75" s="105">
+      <c r="H75" s="104">
         <f>G75</f>
         <v>8461</v>
       </c>
-      <c r="I75" s="106">
+      <c r="I75" s="105">
         <f>H75</f>
         <v>8461</v>
       </c>
-      <c r="J75" s="106">
-        <f t="shared" ref="J75:L75" si="81">I75</f>
+      <c r="J75" s="105">
+        <f t="shared" ref="J75:L75" si="84">I75</f>
         <v>8461</v>
       </c>
-      <c r="K75" s="106">
-        <f t="shared" si="81"/>
+      <c r="K75" s="105">
+        <f t="shared" si="84"/>
         <v>8461</v>
       </c>
-      <c r="L75" s="106">
-        <f t="shared" si="81"/>
+      <c r="L75" s="105">
+        <f t="shared" si="84"/>
         <v>8461</v>
       </c>
     </row>
@@ -5394,43 +5466,43 @@
         <v>23</v>
       </c>
       <c r="C76" s="7">
-        <f t="shared" ref="C76:F76" si="82">SUM(C72:C75)</f>
+        <f t="shared" ref="C76:F76" si="85">SUM(C72:C75)</f>
         <v>81992</v>
       </c>
       <c r="D76" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>90052</v>
       </c>
       <c r="E76" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>95827</v>
       </c>
       <c r="F76" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>97078</v>
       </c>
       <c r="G76" s="7">
         <f>SUM(G72:G75)</f>
         <v>108115</v>
       </c>
-      <c r="H76" s="97">
-        <f t="shared" ref="H76:L76" si="83">SUM(H72:H75)</f>
+      <c r="H76" s="96">
+        <f t="shared" ref="H76:L76" si="86">SUM(H72:H75)</f>
         <v>118284.66526231638</v>
       </c>
       <c r="I76" s="71">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>129506.82911705998</v>
       </c>
       <c r="J76" s="71">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>139831.19299186845</v>
       </c>
       <c r="K76" s="71">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>159560.74127529486</v>
       </c>
       <c r="L76" s="71">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>175736.14909319766</v>
       </c>
     </row>
@@ -5458,19 +5530,19 @@
         <v>203</v>
       </c>
       <c r="I77" s="68">
-        <f t="shared" ref="I77:L77" si="84">AVERAGE(D77:H77)</f>
+        <f t="shared" ref="I77:L77" si="87">AVERAGE(D77:H77)</f>
         <v>200</v>
       </c>
       <c r="J77" s="68">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>194</v>
       </c>
       <c r="K77" s="68">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>187</v>
       </c>
       <c r="L77" s="68">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>200</v>
       </c>
     </row>
@@ -5493,7 +5565,7 @@
       <c r="G78" s="18">
         <v>2091</v>
       </c>
-      <c r="H78" s="99">
+      <c r="H78" s="98">
         <v>1900</v>
       </c>
       <c r="I78" s="18">
@@ -5528,7 +5600,7 @@
       <c r="G79" s="18">
         <v>4287</v>
       </c>
-      <c r="H79" s="99">
+      <c r="H79" s="98">
         <v>3990</v>
       </c>
       <c r="I79" s="18">
@@ -5572,15 +5644,15 @@
         <v>2432</v>
       </c>
       <c r="J80" s="68">
-        <f t="shared" ref="J80:L80" si="85">I80</f>
+        <f t="shared" ref="J80:L80" si="88">I80</f>
         <v>2432</v>
       </c>
       <c r="K80" s="68">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>2432</v>
       </c>
       <c r="L80" s="68">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>2432</v>
       </c>
     </row>
@@ -5612,15 +5684,15 @@
         <v>45637</v>
       </c>
       <c r="J81" s="68">
-        <f t="shared" ref="J81:L81" si="86">I81</f>
+        <f t="shared" ref="J81:L81" si="89">I81</f>
         <v>45637</v>
       </c>
       <c r="K81" s="68">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>45637</v>
       </c>
       <c r="L81" s="68">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>45637</v>
       </c>
     </row>
@@ -5629,15 +5701,15 @@
         <v>22</v>
       </c>
       <c r="C82" s="25">
-        <f t="shared" ref="C82:E82" si="87">SUM(C76:C81)</f>
+        <f t="shared" ref="C82:E82" si="90">SUM(C76:C81)</f>
         <v>153398</v>
       </c>
       <c r="D82" s="25">
-        <f t="shared" si="87"/>
+        <f t="shared" si="90"/>
         <v>152948</v>
       </c>
       <c r="E82" s="25">
-        <f t="shared" si="87"/>
+        <f t="shared" si="90"/>
         <v>154240</v>
       </c>
       <c r="F82" s="25">
@@ -5649,23 +5721,23 @@
         <v>162778</v>
       </c>
       <c r="H82" s="25">
-        <f t="shared" ref="H82:L82" si="88">SUM(H76:H81)</f>
+        <f t="shared" ref="H82:L82" si="91">SUM(H76:H81)</f>
         <v>172446.66526231638</v>
       </c>
       <c r="I82" s="25">
-        <f t="shared" si="88"/>
+        <f t="shared" si="91"/>
         <v>183165.82911706</v>
       </c>
       <c r="J82" s="25">
-        <f t="shared" si="88"/>
+        <f t="shared" si="91"/>
         <v>192984.19299186845</v>
       </c>
       <c r="K82" s="25">
-        <f t="shared" si="88"/>
+        <f t="shared" si="91"/>
         <v>212206.74127529486</v>
       </c>
       <c r="L82" s="25">
-        <f t="shared" si="88"/>
+        <f t="shared" si="91"/>
         <v>227895.14909319766</v>
       </c>
     </row>
@@ -5688,7 +5760,7 @@
       <c r="G83" s="18">
         <v>5061</v>
       </c>
-      <c r="H83" s="107">
+      <c r="H83" s="106">
         <f>G83</f>
         <v>5061</v>
       </c>
@@ -5697,15 +5769,15 @@
         <v>5061</v>
       </c>
       <c r="J83" s="5">
-        <f t="shared" ref="J83:L83" si="89">I83</f>
+        <f t="shared" ref="J83:L83" si="92">I83</f>
         <v>5061</v>
       </c>
       <c r="K83" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="92"/>
         <v>5061</v>
       </c>
       <c r="L83" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="92"/>
         <v>5061</v>
       </c>
     </row>
@@ -5733,19 +5805,19 @@
         <v>22057.200000000001</v>
       </c>
       <c r="I84" s="68">
-        <f t="shared" ref="I84:L84" si="90">H84+I97</f>
+        <f t="shared" ref="I84:L84" si="93">H84+I97</f>
         <v>22630.04</v>
       </c>
       <c r="J84" s="68">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>23172.448</v>
       </c>
       <c r="K84" s="68">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>23685.337599999999</v>
       </c>
       <c r="L84" s="68">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>24219.405119999999</v>
       </c>
     </row>
@@ -5773,19 +5845,19 @@
         <v>-26610.2</v>
       </c>
       <c r="I85" s="68">
-        <f t="shared" ref="I85:L85" si="91">H85+I98</f>
+        <f t="shared" ref="I85:L85" si="94">H85+I98</f>
         <v>-25154.240000000002</v>
       </c>
       <c r="J85" s="68">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>-23650.088000000003</v>
       </c>
       <c r="K85" s="68">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>-22148.105600000003</v>
       </c>
       <c r="L85" s="68">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>-20665.926720000003</v>
       </c>
     </row>
@@ -5813,19 +5885,19 @@
         <v>11426.4180561793</v>
       </c>
       <c r="I86" s="68">
-        <f t="shared" ref="I86:L86" si="92">H86+I45</f>
+        <f t="shared" ref="I86:L86" si="95">H86+I45</f>
         <v>5080.880799501997</v>
       </c>
       <c r="J86" s="68">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>-1719.2163159198799</v>
       </c>
       <c r="K86" s="68">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>-9342.5421186609383</v>
       </c>
       <c r="L86" s="68">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>-17673.233531531587</v>
       </c>
     </row>
@@ -5857,15 +5929,15 @@
         <v>-10277</v>
       </c>
       <c r="J87" s="5">
-        <f t="shared" ref="J87:L87" si="93">H87</f>
+        <f t="shared" ref="J87:L87" si="96">H87</f>
         <v>-10277</v>
       </c>
       <c r="K87" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>-10277</v>
       </c>
       <c r="L87" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>-10277</v>
       </c>
     </row>
@@ -5894,23 +5966,23 @@
         <v>5448</v>
       </c>
       <c r="H88" s="7">
-        <f t="shared" ref="H88:L88" si="94">SUM(H83:H87)</f>
+        <f t="shared" ref="H88:L88" si="97">SUM(H83:H87)</f>
         <v>1657.4180561793</v>
       </c>
       <c r="I88" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>-2659.3192004980037</v>
       </c>
       <c r="J88" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>-7412.8563159198829</v>
       </c>
       <c r="K88" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>-13021.310118660942</v>
       </c>
       <c r="L88" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>-19335.75513153159</v>
       </c>
     </row>
@@ -5969,7 +6041,7 @@
       <c r="G90" s="18">
         <v>3</v>
       </c>
-      <c r="H90" s="105">
+      <c r="H90" s="104">
         <f>G90</f>
         <v>3</v>
       </c>
@@ -5978,15 +6050,15 @@
         <v>3</v>
       </c>
       <c r="J90" s="18">
-        <f t="shared" ref="J90:L90" si="95">I90</f>
+        <f t="shared" ref="J90:L90" si="98">I90</f>
         <v>3</v>
       </c>
       <c r="K90" s="18">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
       <c r="L90" s="18">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
     </row>
@@ -5999,39 +6071,39 @@
         <v>-14846</v>
       </c>
       <c r="D91" s="25">
-        <f t="shared" ref="D91:L91" si="96">SUM(D88:D90)</f>
+        <f t="shared" ref="D91:L91" si="99">SUM(D88:D90)</f>
         <v>-15848</v>
       </c>
       <c r="E91" s="25">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-17228</v>
       </c>
       <c r="F91" s="25">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-3914</v>
       </c>
       <c r="G91" s="29">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>5457</v>
       </c>
       <c r="H91" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>1666.4180561793</v>
       </c>
       <c r="I91" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-2656.3192004980037</v>
       </c>
       <c r="J91" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-7409.8563159198829</v>
       </c>
       <c r="K91" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-13018.310118660942</v>
       </c>
       <c r="L91" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-19332.75513153159</v>
       </c>
     </row>
@@ -6040,43 +6112,43 @@
         <v>44</v>
       </c>
       <c r="C92" s="13">
-        <f t="shared" ref="C92:H92" si="97">SUM(C82+C91)</f>
+        <f t="shared" ref="C92:H92" si="100">SUM(C82+C91)</f>
         <v>138552</v>
       </c>
       <c r="D92" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" si="100"/>
         <v>137100</v>
       </c>
       <c r="E92" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" si="100"/>
         <v>137012</v>
       </c>
       <c r="F92" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" si="100"/>
         <v>156363</v>
       </c>
       <c r="G92" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" si="100"/>
         <v>168235</v>
       </c>
       <c r="H92" s="75">
-        <f t="shared" si="97"/>
+        <f t="shared" si="100"/>
         <v>174113.08331849569</v>
       </c>
       <c r="I92" s="13">
-        <f t="shared" ref="I92:L92" si="98">SUM(I82+I91)</f>
+        <f t="shared" ref="I92:L92" si="101">SUM(I82+I91)</f>
         <v>180509.509916562</v>
       </c>
       <c r="J92" s="13">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>185574.33667594855</v>
       </c>
       <c r="K92" s="13">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>199188.43115663392</v>
       </c>
       <c r="L92" s="13">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>208562.39396166606</v>
       </c>
     </row>
@@ -6089,49 +6161,49 @@
         <v>✓</v>
       </c>
       <c r="D93" s="39" t="str">
-        <f t="shared" ref="D93:L93" si="99">IF(D92=D71, "✓", "✗")</f>
+        <f t="shared" ref="D93:L93" si="102">IF(D92=D71, "✓", "✗")</f>
         <v>✓</v>
       </c>
       <c r="E93" s="39" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>✓</v>
       </c>
       <c r="F93" s="39" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>✓</v>
       </c>
       <c r="G93" s="39" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>✓</v>
       </c>
-      <c r="H93" s="113" t="str">
-        <f t="shared" si="99"/>
+      <c r="H93" s="112" t="str">
+        <f t="shared" si="102"/>
         <v>✗</v>
       </c>
-      <c r="I93" s="113" t="str">
-        <f t="shared" si="99"/>
+      <c r="I93" s="112" t="str">
+        <f t="shared" si="102"/>
         <v>✗</v>
       </c>
-      <c r="J93" s="113" t="str">
-        <f t="shared" si="99"/>
+      <c r="J93" s="112" t="str">
+        <f t="shared" si="102"/>
         <v>✗</v>
       </c>
-      <c r="K93" s="113" t="str">
-        <f t="shared" si="99"/>
+      <c r="K93" s="112" t="str">
+        <f t="shared" si="102"/>
         <v>✗</v>
       </c>
-      <c r="L93" s="113" t="str">
-        <f t="shared" si="99"/>
+      <c r="L93" s="112" t="str">
+        <f t="shared" si="102"/>
         <v>✗</v>
       </c>
     </row>
     <row r="94" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B94" s="10"/>
-      <c r="H94" s="110"/>
-      <c r="I94" s="110"/>
-      <c r="J94" s="110"/>
-      <c r="K94" s="110"/>
-      <c r="L94" s="110"/>
+      <c r="H94" s="109"/>
+      <c r="I94" s="109"/>
+      <c r="J94" s="109"/>
+      <c r="K94" s="109"/>
+      <c r="L94" s="109"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
@@ -6141,15 +6213,15 @@
         <v>2021</v>
       </c>
       <c r="D95" s="2">
-        <f t="shared" ref="D95" si="100">+C95+1</f>
+        <f t="shared" ref="D95" si="103">+C95+1</f>
         <v>2022</v>
       </c>
       <c r="E95" s="2">
-        <f t="shared" ref="E95" si="101">+D95+1</f>
+        <f t="shared" ref="E95" si="104">+D95+1</f>
         <v>2023</v>
       </c>
       <c r="F95" s="2">
-        <f t="shared" ref="F95" si="102">+E95+1</f>
+        <f t="shared" ref="F95" si="105">+E95+1</f>
         <v>2024</v>
       </c>
       <c r="G95" s="2">
@@ -6157,23 +6229,23 @@
         <v>2025</v>
       </c>
       <c r="H95" s="2">
-        <f t="shared" ref="H95" si="103">+G95+1</f>
+        <f t="shared" ref="H95" si="106">+G95+1</f>
         <v>2026</v>
       </c>
       <c r="I95" s="2">
-        <f t="shared" ref="I95" si="104">+H95+1</f>
+        <f t="shared" ref="I95" si="107">+H95+1</f>
         <v>2027</v>
       </c>
       <c r="J95" s="2">
-        <f t="shared" ref="J95" si="105">+I95+1</f>
+        <f t="shared" ref="J95" si="108">+I95+1</f>
         <v>2028</v>
       </c>
       <c r="K95" s="2">
-        <f t="shared" ref="K95" si="106">+J95+1</f>
+        <f t="shared" ref="K95" si="109">+J95+1</f>
         <v>2029</v>
       </c>
       <c r="L95" s="2">
-        <f t="shared" ref="L95" si="107">+K95+1</f>
+        <f t="shared" ref="L95" si="110">+K95+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -6202,23 +6274,23 @@
         <v>2238</v>
       </c>
       <c r="H96" s="20">
-        <f t="shared" ref="H96:L96" si="108">H45</f>
+        <f t="shared" ref="H96:L96" si="111">H45</f>
         <v>-5825.5819438207</v>
       </c>
       <c r="I96" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>-6345.537256677303</v>
       </c>
       <c r="J96" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>-6800.0971154218769</v>
       </c>
       <c r="K96" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>-7623.3258027410575</v>
       </c>
       <c r="L96" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>-8330.6914128706467</v>
       </c>
     </row>
@@ -6246,19 +6318,19 @@
         <v>616.20000000000005</v>
       </c>
       <c r="I97" s="68">
-        <f t="shared" ref="I97:L97" si="109">AVERAGE(D97:H97)</f>
+        <f t="shared" ref="I97:L97" si="112">AVERAGE(D97:H97)</f>
         <v>572.83999999999992</v>
       </c>
       <c r="J97" s="68">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>542.40800000000002</v>
       </c>
       <c r="K97" s="68">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>512.88959999999997</v>
       </c>
       <c r="L97" s="68">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>534.06751999999994</v>
       </c>
     </row>
@@ -6286,19 +6358,19 @@
         <v>1418.8</v>
       </c>
       <c r="I98" s="68">
-        <f t="shared" ref="I98:L98" si="110">AVERAGE(D98:H98)</f>
+        <f t="shared" ref="I98:L98" si="113">AVERAGE(D98:H98)</f>
         <v>1455.96</v>
       </c>
       <c r="J98" s="68">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>1504.152</v>
       </c>
       <c r="K98" s="68">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>1501.9824000000001</v>
       </c>
       <c r="L98" s="68">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>1482.1788799999999</v>
       </c>
     </row>
@@ -6326,19 +6398,19 @@
         <v>2394.7571016903594</v>
       </c>
       <c r="I99" s="68">
-        <f t="shared" ref="I99:L99" si="111">I17*I31</f>
+        <f t="shared" ref="I99:L99" si="114">I17*I31</f>
         <v>2656.0823993199037</v>
       </c>
       <c r="J99" s="68">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>2766.0826084191112</v>
       </c>
       <c r="K99" s="68">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>3266.8301190381508</v>
       </c>
       <c r="L99" s="68">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>3608.6713341028963</v>
       </c>
     </row>
@@ -6501,24 +6573,24 @@
       <c r="G104" s="5">
         <v>264</v>
       </c>
-      <c r="H104" s="111">
+      <c r="H104" s="110">
         <f>AVERAGE(E104:G104)</f>
         <v>265</v>
       </c>
-      <c r="I104" s="112">
-        <f t="shared" ref="I104:L104" si="112">AVERAGE(F104:H104)</f>
+      <c r="I104" s="111">
+        <f t="shared" ref="I104:L104" si="115">AVERAGE(F104:H104)</f>
         <v>352.33333333333331</v>
       </c>
-      <c r="J104" s="112">
-        <f t="shared" si="112"/>
+      <c r="J104" s="111">
+        <f t="shared" si="115"/>
         <v>293.77777777777777</v>
       </c>
-      <c r="K104" s="112">
-        <f t="shared" si="112"/>
+      <c r="K104" s="111">
+        <f t="shared" si="115"/>
         <v>303.7037037037037</v>
       </c>
-      <c r="L104" s="112">
-        <f t="shared" si="112"/>
+      <c r="L104" s="111">
+        <f t="shared" si="115"/>
         <v>316.60493827160491</v>
       </c>
     </row>
@@ -6531,11 +6603,11 @@
       <c r="E105" s="27"/>
       <c r="F105" s="27"/>
       <c r="G105" s="32"/>
-      <c r="H105" s="110"/>
-      <c r="I105" s="110"/>
-      <c r="J105" s="110"/>
-      <c r="K105" s="110"/>
-      <c r="L105" s="110"/>
+      <c r="H105" s="109"/>
+      <c r="I105" s="109"/>
+      <c r="J105" s="109"/>
+      <c r="K105" s="109"/>
+      <c r="L105" s="109"/>
     </row>
     <row r="106" spans="2:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="B106" s="14" t="s">
@@ -6561,19 +6633,19 @@
         <v>-731.05758357158311</v>
       </c>
       <c r="I106" s="68">
-        <f t="shared" ref="I106:L106" si="113">-(I58-H58)</f>
+        <f t="shared" ref="I106:L106" si="116">-(I58-H58)</f>
         <v>-259.24041666933135</v>
       </c>
       <c r="J106" s="68">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>-297.20994529158315</v>
       </c>
       <c r="K106" s="68">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>-689.91223698797148</v>
       </c>
       <c r="L106" s="68">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>-432.61041966014454</v>
       </c>
     </row>
@@ -6601,19 +6673,19 @@
         <v>539.60000000000036</v>
       </c>
       <c r="I107" s="68">
-        <f t="shared" ref="I107:L107" si="114">-(I59-H59)</f>
+        <f t="shared" ref="I107:L107" si="117">-(I59-H59)</f>
         <v>0.31999999999970896</v>
       </c>
       <c r="J107" s="68">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>3.183999999999287</v>
       </c>
       <c r="K107" s="68">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>-59.579200000000128</v>
       </c>
       <c r="L107" s="68">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>-62.295040000000881</v>
       </c>
     </row>
@@ -6641,19 +6713,19 @@
         <v>5628.2744590559741</v>
       </c>
       <c r="I108" s="68">
-        <f t="shared" ref="I108:L108" si="115">I74-H74</f>
+        <f t="shared" ref="I108:L108" si="118">I74-H74</f>
         <v>6579.8442491881142</v>
       </c>
       <c r="J108" s="68">
-        <f t="shared" si="115"/>
+        <f t="shared" si="118"/>
         <v>6093.7052738714265</v>
       </c>
       <c r="K108" s="68">
-        <f t="shared" si="115"/>
+        <f t="shared" si="118"/>
         <v>11787.521024035959</v>
       </c>
       <c r="L108" s="68">
-        <f t="shared" si="115"/>
+        <f t="shared" si="118"/>
         <v>9654.7796186587948</v>
       </c>
     </row>
@@ -6681,19 +6753,19 @@
         <v>-21313.187045630271</v>
       </c>
       <c r="I109" s="68">
-        <f t="shared" ref="I109:L109" si="116">(H61-I61)</f>
+        <f t="shared" ref="I109:L109" si="119">(H61-I61)</f>
         <v>-10679.632875471914</v>
       </c>
       <c r="J109" s="68">
-        <f t="shared" si="116"/>
+        <f t="shared" si="119"/>
         <v>-4666.7334587105288</v>
       </c>
       <c r="K109" s="68">
-        <f t="shared" si="116"/>
+        <f t="shared" si="119"/>
         <v>-22464.436744028062</v>
       </c>
       <c r="L109" s="68">
-        <f t="shared" si="116"/>
+        <f t="shared" si="119"/>
         <v>-14754.275663420442</v>
       </c>
     </row>
@@ -6721,19 +6793,19 @@
         <v>-218.00989041626508</v>
       </c>
       <c r="I110" s="68">
-        <f t="shared" ref="I110:L110" si="117">(H62-I62)</f>
+        <f t="shared" ref="I110:L110" si="120">(H62-I62)</f>
         <v>-254.86872293754368</v>
       </c>
       <c r="J110" s="68">
-        <f t="shared" si="117"/>
+        <f t="shared" si="120"/>
         <v>-236.03824380813012</v>
       </c>
       <c r="K110" s="68">
-        <f t="shared" si="117"/>
+        <f t="shared" si="120"/>
         <v>-456.58686075528158</v>
       </c>
       <c r="L110" s="68">
-        <f t="shared" si="117"/>
+        <f t="shared" si="120"/>
         <v>-373.97562289633515</v>
       </c>
     </row>
@@ -6765,15 +6837,15 @@
         <v>1636.064929654618</v>
       </c>
       <c r="J111" s="68">
-        <f t="shared" ref="J111:L111" si="118">(J72-I72)</f>
+        <f t="shared" ref="J111:L111" si="121">(J72-I72)</f>
         <v>1446.515195810367</v>
       </c>
       <c r="K111" s="68">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>2556.4453438063138</v>
       </c>
       <c r="L111" s="68">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>2109.4711453415912</v>
       </c>
     </row>
@@ -6801,19 +6873,19 @@
         <v>2571.4934531889812</v>
       </c>
       <c r="I112" s="68">
-        <f t="shared" ref="I112:L112" si="119">I73-H73</f>
+        <f t="shared" ref="I112:L112" si="122">I73-H73</f>
         <v>3006.2546759008583</v>
       </c>
       <c r="J112" s="68">
-        <f t="shared" si="119"/>
+        <f t="shared" si="122"/>
         <v>2784.143405126666</v>
       </c>
       <c r="K112" s="68">
-        <f t="shared" si="119"/>
+        <f t="shared" si="122"/>
         <v>5385.5819155841382</v>
       </c>
       <c r="L112" s="68">
-        <f t="shared" si="119"/>
+        <f t="shared" si="122"/>
         <v>4411.1570539024033</v>
       </c>
     </row>
@@ -6841,19 +6913,19 @@
         <v>0</v>
       </c>
       <c r="I113" s="68">
-        <f t="shared" ref="I113:L113" si="120">I68-H68</f>
+        <f t="shared" ref="I113:L113" si="123">I68-H68</f>
         <v>0</v>
       </c>
       <c r="J113" s="68">
-        <f t="shared" si="120"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="K113" s="68">
-        <f t="shared" si="120"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="L113" s="68">
-        <f t="shared" si="120"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
     </row>
@@ -6881,19 +6953,19 @@
         <v>0</v>
       </c>
       <c r="I114" s="68">
-        <f t="shared" ref="I114:L114" si="121">I80-H80</f>
+        <f t="shared" ref="I114:L114" si="124">I80-H80</f>
         <v>0</v>
       </c>
       <c r="J114" s="68">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="K114" s="68">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="L114" s="68">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
     </row>
@@ -6921,19 +6993,19 @@
         <v>-867</v>
       </c>
       <c r="I115" s="68">
-        <f t="shared" ref="I115:L115" si="122">AVERAGE(F115:H115)</f>
+        <f t="shared" ref="I115:L115" si="125">AVERAGE(F115:H115)</f>
         <v>-806.33333333333337</v>
       </c>
       <c r="J115" s="68">
-        <f t="shared" si="122"/>
+        <f t="shared" si="125"/>
         <v>-755.44444444444446</v>
       </c>
       <c r="K115" s="68">
-        <f t="shared" si="122"/>
+        <f t="shared" si="125"/>
         <v>-809.59259259259261</v>
       </c>
       <c r="L115" s="68">
-        <f t="shared" si="122"/>
+        <f t="shared" si="125"/>
         <v>-790.45679012345681</v>
       </c>
     </row>
@@ -6961,19 +7033,19 @@
         <v>50</v>
       </c>
       <c r="I116" s="68">
-        <f t="shared" ref="I116:L116" si="123">-(I64-H64)</f>
+        <f t="shared" ref="I116:L116" si="126">-(I64-H64)</f>
         <v>50</v>
       </c>
       <c r="J116" s="68">
-        <f t="shared" si="123"/>
+        <f t="shared" si="126"/>
         <v>50</v>
       </c>
       <c r="K116" s="68">
-        <f t="shared" si="123"/>
+        <f t="shared" si="126"/>
         <v>50</v>
       </c>
       <c r="L116" s="68">
-        <f t="shared" si="123"/>
+        <f t="shared" si="126"/>
         <v>41</v>
       </c>
     </row>
@@ -7001,19 +7073,19 @@
         <v>215</v>
       </c>
       <c r="I117" s="68">
-        <f t="shared" ref="I117:L117" si="124">AVERAGE(F117:H117)</f>
+        <f t="shared" ref="I117:L117" si="127">AVERAGE(F117:H117)</f>
         <v>247</v>
       </c>
       <c r="J117" s="68">
-        <f t="shared" si="124"/>
+        <f t="shared" si="127"/>
         <v>262</v>
       </c>
       <c r="K117" s="68">
-        <f t="shared" si="124"/>
+        <f t="shared" si="127"/>
         <v>241.33333333333334</v>
       </c>
       <c r="L117" s="68">
-        <f t="shared" si="124"/>
+        <f t="shared" si="127"/>
         <v>250.11111111111111</v>
       </c>
     </row>
@@ -7042,23 +7114,23 @@
         <v>1065</v>
       </c>
       <c r="H118" s="25">
-        <f t="shared" ref="H118:L118" si="125">SUM(H96:H117)</f>
+        <f t="shared" ref="H118:L118" si="128">SUM(H96:H117)</f>
         <v>-13285.814099432071</v>
       </c>
       <c r="I118" s="25">
-        <f t="shared" si="125"/>
+        <f t="shared" si="128"/>
         <v>-1788.9130176925987</v>
       </c>
       <c r="J118" s="25">
-        <f t="shared" si="125"/>
+        <f t="shared" si="128"/>
         <v>2990.445053328785</v>
       </c>
       <c r="K118" s="25">
-        <f t="shared" si="125"/>
+        <f t="shared" si="128"/>
         <v>-6497.1459976033684</v>
       </c>
       <c r="L118" s="25">
-        <f t="shared" si="125"/>
+        <f t="shared" si="128"/>
         <v>-2336.2633475826224</v>
       </c>
     </row>
@@ -7086,19 +7158,19 @@
         <v>-1780.2</v>
       </c>
       <c r="I119" s="68">
-        <f t="shared" ref="I119:L119" si="126">AVERAGE(D119:H119)</f>
+        <f t="shared" ref="I119:L119" si="129">AVERAGE(D119:H119)</f>
         <v>-1940.2400000000002</v>
       </c>
       <c r="J119" s="68">
-        <f t="shared" si="126"/>
+        <f t="shared" si="129"/>
         <v>-2083.8879999999999</v>
       </c>
       <c r="K119" s="68">
-        <f t="shared" si="126"/>
+        <f t="shared" si="129"/>
         <v>-2195.2656000000002</v>
       </c>
       <c r="L119" s="68">
-        <f t="shared" si="126"/>
+        <f t="shared" si="129"/>
         <v>-2188.3187200000002</v>
       </c>
     </row>
@@ -7126,19 +7198,19 @@
         <v>144.4</v>
       </c>
       <c r="I120" s="68">
-        <f t="shared" ref="I120:L120" si="127">AVERAGE(F120:H120)</f>
+        <f t="shared" ref="I120:L120" si="130">AVERAGE(F120:H120)</f>
         <v>91.8</v>
       </c>
       <c r="J120" s="68">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>106.06666666666666</v>
       </c>
       <c r="K120" s="68">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>114.08888888888889</v>
       </c>
       <c r="L120" s="68">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>103.98518518518519</v>
       </c>
     </row>
@@ -7236,19 +7308,19 @@
         <v>-24601.200000000001</v>
       </c>
       <c r="I123" s="68">
-        <f t="shared" ref="I123:L123" si="128">AVERAGE(D123:H123)</f>
+        <f t="shared" ref="I123:L123" si="131">AVERAGE(D123:H123)</f>
         <v>-22378.84</v>
       </c>
       <c r="J123" s="68">
-        <f t="shared" si="128"/>
+        <f t="shared" si="131"/>
         <v>-25844.407999999999</v>
       </c>
       <c r="K123" s="68">
-        <f t="shared" si="128"/>
+        <f t="shared" si="131"/>
         <v>-27723.689600000002</v>
       </c>
       <c r="L123" s="68">
-        <f t="shared" si="128"/>
+        <f t="shared" si="131"/>
         <v>-30497.227519999997</v>
       </c>
     </row>
@@ -7276,19 +7348,19 @@
         <v>24643.599999999999</v>
       </c>
       <c r="I124" s="68">
-        <f t="shared" ref="I124:L124" si="129">AVERAGE(D124:H124)</f>
+        <f t="shared" ref="I124:L124" si="132">AVERAGE(D124:H124)</f>
         <v>20474.52</v>
       </c>
       <c r="J124" s="68">
-        <f t="shared" si="129"/>
+        <f t="shared" si="132"/>
         <v>22445.624000000003</v>
       </c>
       <c r="K124" s="68">
-        <f t="shared" si="129"/>
+        <f t="shared" si="132"/>
         <v>23786.948800000002</v>
       </c>
       <c r="L124" s="68">
-        <f t="shared" si="129"/>
+        <f t="shared" si="132"/>
         <v>27595.738560000005</v>
       </c>
     </row>
@@ -7317,19 +7389,19 @@
         <v>-506</v>
       </c>
       <c r="I125" s="68">
-        <f t="shared" ref="I125:L125" si="130">AVERAGE(F125:H125)</f>
+        <f t="shared" ref="I125:L125" si="133">AVERAGE(F125:H125)</f>
         <v>-620.66666666666663</v>
       </c>
       <c r="J125" s="68">
-        <f t="shared" si="130"/>
+        <f t="shared" si="133"/>
         <v>-596.22222222222217</v>
       </c>
       <c r="K125" s="68">
-        <f t="shared" si="130"/>
+        <f t="shared" si="133"/>
         <v>-574.29629629629619</v>
       </c>
       <c r="L125" s="68">
-        <f t="shared" si="130"/>
+        <f t="shared" si="133"/>
         <v>-597.06172839506155</v>
       </c>
     </row>
@@ -7423,19 +7495,19 @@
         <v>-2.4</v>
       </c>
       <c r="I128" s="68">
-        <f t="shared" ref="I128:L128" si="131">AVERAGE(D128:H128)</f>
+        <f t="shared" ref="I128:L128" si="134">AVERAGE(D128:H128)</f>
         <v>-3.88</v>
       </c>
       <c r="J128" s="68">
-        <f t="shared" si="131"/>
+        <f t="shared" si="134"/>
         <v>-2.4560000000000004</v>
       </c>
       <c r="K128" s="68">
-        <f t="shared" si="131"/>
+        <f t="shared" si="134"/>
         <v>-3.7472000000000003</v>
       </c>
       <c r="L128" s="68">
-        <f t="shared" si="131"/>
+        <f t="shared" si="134"/>
         <v>-2.29664</v>
       </c>
     </row>
@@ -7448,39 +7520,39 @@
         <v>9324</v>
       </c>
       <c r="D129" s="25">
-        <f t="shared" ref="D129:L129" si="132">SUM(D119:D128)</f>
+        <f t="shared" ref="D129:L129" si="135">SUM(D119:D128)</f>
         <v>4370</v>
       </c>
       <c r="E129" s="25">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>-2437</v>
       </c>
       <c r="F129" s="25">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>-11973</v>
       </c>
       <c r="G129" s="26">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>499</v>
       </c>
       <c r="H129" s="25">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>-2101.8000000000015</v>
       </c>
       <c r="I129" s="25">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>-4377.3066666666655</v>
       </c>
       <c r="J129" s="25">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>-5975.2835555555521</v>
       </c>
       <c r="K129" s="25">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>-6595.9610074074071</v>
       </c>
       <c r="L129" s="25">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>-5585.1808632098664</v>
       </c>
     </row>
@@ -7508,19 +7580,19 @@
         <v>165</v>
       </c>
       <c r="I130" s="68">
-        <f t="shared" ref="I130:L130" si="133">H130</f>
+        <f t="shared" ref="I130:L130" si="136">H130</f>
         <v>165</v>
       </c>
       <c r="J130" s="68">
-        <f t="shared" si="133"/>
+        <f t="shared" si="136"/>
         <v>165</v>
       </c>
       <c r="K130" s="68">
-        <f t="shared" si="133"/>
+        <f t="shared" si="136"/>
         <v>165</v>
       </c>
       <c r="L130" s="68">
-        <f t="shared" si="133"/>
+        <f t="shared" si="136"/>
         <v>165</v>
       </c>
     </row>
@@ -7548,19 +7620,19 @@
         <v>-3621</v>
       </c>
       <c r="I131" s="68">
-        <f t="shared" ref="I131:L131" si="134">H131</f>
+        <f t="shared" ref="I131:L131" si="137">H131</f>
         <v>-3621</v>
       </c>
       <c r="J131" s="68">
-        <f t="shared" si="134"/>
+        <f t="shared" si="137"/>
         <v>-3621</v>
       </c>
       <c r="K131" s="68">
-        <f t="shared" si="134"/>
+        <f t="shared" si="137"/>
         <v>-3621</v>
       </c>
       <c r="L131" s="68">
-        <f t="shared" si="134"/>
+        <f t="shared" si="137"/>
         <v>-3621</v>
       </c>
     </row>
@@ -7658,19 +7730,19 @@
         <v>0</v>
       </c>
       <c r="I134" s="68">
-        <f t="shared" ref="I134:L134" si="135">H134</f>
+        <f t="shared" ref="I134:L134" si="138">H134</f>
         <v>0</v>
       </c>
       <c r="J134" s="68">
-        <f t="shared" si="135"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="K134" s="68">
-        <f t="shared" si="135"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="L134" s="68">
-        <f t="shared" si="135"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
     </row>
@@ -7698,19 +7770,19 @@
         <v>-126.2</v>
       </c>
       <c r="I135" s="68">
-        <f t="shared" ref="I135:L135" si="136">AVERAGE(D135:H135)</f>
+        <f t="shared" ref="I135:L135" si="139">AVERAGE(D135:H135)</f>
         <v>-138.24</v>
       </c>
       <c r="J135" s="68">
-        <f t="shared" si="136"/>
+        <f t="shared" si="139"/>
         <v>-157.88800000000001</v>
       </c>
       <c r="K135" s="68">
-        <f t="shared" si="136"/>
+        <f t="shared" si="139"/>
         <v>-107.8656</v>
       </c>
       <c r="L135" s="68">
-        <f t="shared" si="136"/>
+        <f t="shared" si="139"/>
         <v>-112.83872</v>
       </c>
     </row>
@@ -7738,19 +7810,19 @@
         <v>-331</v>
       </c>
       <c r="I136" s="68">
-        <f t="shared" ref="I136:L137" si="137">H136</f>
+        <f t="shared" ref="I136:L137" si="140">H136</f>
         <v>-331</v>
       </c>
       <c r="J136" s="68">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>-331</v>
       </c>
       <c r="K136" s="68">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>-331</v>
       </c>
       <c r="L136" s="68">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>-331</v>
       </c>
     </row>
@@ -7773,24 +7845,24 @@
       <c r="G137" s="33">
         <v>58</v>
       </c>
-      <c r="H137" s="111">
+      <c r="H137" s="110">
         <f>G137</f>
         <v>58</v>
       </c>
       <c r="I137" s="68">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>58</v>
       </c>
       <c r="J137" s="68">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>58</v>
       </c>
       <c r="K137" s="68">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>58</v>
       </c>
       <c r="L137" s="68">
-        <f t="shared" si="137"/>
+        <f t="shared" si="140"/>
         <v>58</v>
       </c>
     </row>
@@ -7799,15 +7871,15 @@
         <v>58</v>
       </c>
       <c r="C138" s="25">
-        <f t="shared" ref="C138:E138" si="138">SUM(C130:C137)</f>
+        <f t="shared" ref="C138:E138" si="141">SUM(C130:C137)</f>
         <v>-5600</v>
       </c>
       <c r="D138" s="25">
-        <f t="shared" si="138"/>
+        <f t="shared" si="141"/>
         <v>-1266</v>
       </c>
       <c r="E138" s="25">
-        <f t="shared" si="138"/>
+        <f t="shared" si="141"/>
         <v>-5487</v>
       </c>
       <c r="F138" s="25">
@@ -7819,23 +7891,23 @@
         <v>-3763</v>
       </c>
       <c r="H138" s="25">
-        <f t="shared" ref="H138:L138" si="139">SUM(H130:H137)</f>
+        <f t="shared" ref="H138:L138" si="142">SUM(H130:H137)</f>
         <v>-3855.2</v>
       </c>
       <c r="I138" s="25">
-        <f t="shared" si="139"/>
+        <f t="shared" si="142"/>
         <v>-3867.24</v>
       </c>
       <c r="J138" s="25">
-        <f t="shared" si="139"/>
+        <f t="shared" si="142"/>
         <v>-3886.8879999999999</v>
       </c>
       <c r="K138" s="25">
-        <f t="shared" si="139"/>
+        <f t="shared" si="142"/>
         <v>-3836.8656000000001</v>
       </c>
       <c r="L138" s="25">
-        <f t="shared" si="139"/>
+        <f t="shared" si="142"/>
         <v>-3841.8387200000002</v>
       </c>
     </row>
@@ -7858,24 +7930,24 @@
       <c r="G139" s="34">
         <v>40</v>
       </c>
-      <c r="H139" s="114">
+      <c r="H139" s="113">
         <f>AVERAGE(C139:G139)</f>
         <v>-17.8</v>
       </c>
       <c r="I139" s="70">
-        <f t="shared" ref="I139:L139" si="140">AVERAGE(D139:H139)</f>
+        <f t="shared" ref="I139:L139" si="143">AVERAGE(D139:H139)</f>
         <v>-13.559999999999999</v>
       </c>
       <c r="J139" s="70">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>-1.6719999999999999</v>
       </c>
       <c r="K139" s="70">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>-8.0063999999999993</v>
       </c>
       <c r="L139" s="70">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>-0.2076799999999997</v>
       </c>
     </row>
@@ -7904,23 +7976,23 @@
         <v>-2159</v>
       </c>
       <c r="H140" s="13">
-        <f t="shared" ref="H140:L140" si="141">SUM(H138,H129,H118,H139)</f>
+        <f t="shared" ref="H140:L140" si="144">SUM(H138,H129,H118,H139)</f>
         <v>-19260.61409943207</v>
       </c>
       <c r="I140" s="13">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-10047.019684359264</v>
       </c>
       <c r="J140" s="13">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-6873.3985022267671</v>
       </c>
       <c r="K140" s="13">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-16937.979005010773</v>
       </c>
       <c r="L140" s="13">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-11763.490610792489</v>
       </c>
     </row>
@@ -7948,19 +8020,19 @@
         <v>11663</v>
       </c>
       <c r="I141" s="68">
-        <f t="shared" ref="I141:L141" si="142">H142</f>
+        <f t="shared" ref="I141:L141" si="145">H142</f>
         <v>-7597.6140994320704</v>
       </c>
       <c r="J141" s="68">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>-17644.633783791334</v>
       </c>
       <c r="K141" s="68">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>-24518.0322860181</v>
       </c>
       <c r="L141" s="68">
-        <f t="shared" si="142"/>
+        <f t="shared" si="145"/>
         <v>-41456.011291028874</v>
       </c>
     </row>
@@ -7988,19 +8060,19 @@
         <v>-7597.6140994320704</v>
       </c>
       <c r="I142" s="68">
-        <f t="shared" ref="I142:L142" si="143">I141+I140</f>
+        <f t="shared" ref="I142:L142" si="146">I141+I140</f>
         <v>-17644.633783791334</v>
       </c>
       <c r="J142" s="68">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>-24518.0322860181</v>
       </c>
       <c r="K142" s="68">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>-41456.011291028874</v>
       </c>
       <c r="L142" s="68">
-        <f t="shared" si="143"/>
+        <f t="shared" si="146"/>
         <v>-53219.501901821364</v>
       </c>
     </row>
@@ -8023,24 +8095,24 @@
       <c r="G143" s="33">
         <v>742</v>
       </c>
-      <c r="H143" s="111">
+      <c r="H143" s="110">
         <f>AVERAGE(C143:G143)</f>
         <v>174</v>
       </c>
       <c r="I143" s="68">
-        <f t="shared" ref="I143:L143" si="144">AVERAGE(D143:H143)</f>
+        <f t="shared" ref="I143:L143" si="147">AVERAGE(D143:H143)</f>
         <v>198.4</v>
       </c>
       <c r="J143" s="68">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>231.48000000000002</v>
       </c>
       <c r="K143" s="68">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>273.37600000000003</v>
       </c>
       <c r="L143" s="68">
-        <f t="shared" si="144"/>
+        <f t="shared" si="147"/>
         <v>323.85120000000001</v>
       </c>
     </row>
@@ -8069,23 +8141,23 @@
         <v>10921</v>
       </c>
       <c r="H144" s="37">
-        <f t="shared" ref="H144:L144" si="145">SUM(H142-H143)</f>
+        <f t="shared" ref="H144:L144" si="148">SUM(H142-H143)</f>
         <v>-7771.6140994320704</v>
       </c>
       <c r="I144" s="37">
-        <f t="shared" si="145"/>
+        <f t="shared" si="148"/>
         <v>-17843.033783791336</v>
       </c>
       <c r="J144" s="37">
-        <f t="shared" si="145"/>
+        <f t="shared" si="148"/>
         <v>-24749.5122860181</v>
       </c>
       <c r="K144" s="37">
-        <f t="shared" si="145"/>
+        <f t="shared" si="148"/>
         <v>-41729.38729102887</v>
       </c>
       <c r="L144" s="37">
-        <f t="shared" si="145"/>
+        <f t="shared" si="148"/>
         <v>-53543.353101821362</v>
       </c>
     </row>
@@ -8098,19 +8170,19 @@
         <v>✓</v>
       </c>
       <c r="D145" s="39" t="str">
-        <f t="shared" ref="D145:L145" si="146">IF(D144=D56, "✓", "✗")</f>
+        <f t="shared" ref="D145:L145" si="149">IF(D144=D56, "✓", "✗")</f>
         <v>✓</v>
       </c>
       <c r="E145" s="39" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="149"/>
         <v>✓</v>
       </c>
       <c r="F145" s="39" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="149"/>
         <v>✓</v>
       </c>
       <c r="G145" s="39" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="149"/>
         <v>✓</v>
       </c>
       <c r="H145" s="39" t="str">
@@ -8118,19 +8190,19 @@
         <v>✓</v>
       </c>
       <c r="I145" s="39" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="149"/>
         <v>✓</v>
       </c>
       <c r="J145" s="39" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="149"/>
         <v>✓</v>
       </c>
       <c r="K145" s="39" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="149"/>
         <v>✓</v>
       </c>
       <c r="L145" s="39" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="149"/>
         <v>✓</v>
       </c>
     </row>
@@ -8139,7 +8211,7 @@
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="C63 C118 H46 H41 H39 H52 H50 H104 H115:L115 H117:L117" formulaRange="1"/>
-    <ignoredError sqref="H51 I51:L51" formula="1"/>
+    <ignoredError sqref="H51 I51:L51 H20:L20" formula="1"/>
     <ignoredError sqref="H116 I116:L116" formula="1" formulaRange="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
